--- a/build/oneshot/Investeringskalkyl_v2.xlsx
+++ b/build/oneshot/Investeringskalkyl_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaki\Documents\GitHub\investeringskalkyl\build\oneshot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E9C4CD-F60B-42D7-8063-58FB8E2C6E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53774B03-CC2C-4953-9660-CBF61CF32018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="345" yWindow="345" windowWidth="28800" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3098,7 +3098,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-733A-4FAB-A948-4C7F32C921FE}"/>
+              <c16:uniqueId val="{00000000-ADD1-46F7-9AEF-1AE39D97D7A7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3349,7 +3349,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B7B7-4FE9-A896-E274BA52FBD9}"/>
+              <c16:uniqueId val="{00000000-302C-4D76-8516-FBF4F1C370A4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3511,7 +3511,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-B7B7-4FE9-A896-E274BA52FBD9}"/>
+              <c16:uniqueId val="{00000001-302C-4D76-8516-FBF4F1C370A4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3672,7 +3672,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-CFAC-4A2C-942F-39E826F4D054}"/>
+              <c16:uniqueId val="{00000000-33B2-432D-8F02-AB7C983860A7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -15797,66 +15797,21 @@
         <f>IF(OR(Indata!$K$26="",M$29&lt;Indata!$K$26),0,(Indata!$R$26/Indata!$R$31)*M$16)</f>
         <v>13181563.602194397</v>
       </c>
-      <c r="N30" s="20">
-        <f>IF(OR(Indata!$K$26="",N$29&lt;Indata!$K$26),0,(Indata!$R$26/Indata!$R$31)*N$16)</f>
-        <v>0</v>
-      </c>
-      <c r="O30" s="20">
-        <f>IF(OR(Indata!$K$26="",O$29&lt;Indata!$K$26),0,(Indata!$R$26/Indata!$R$31)*O$16)</f>
-        <v>0</v>
-      </c>
-      <c r="P30" s="20">
-        <f>IF(OR(Indata!$K$26="",P$29&lt;Indata!$K$26),0,(Indata!$R$26/Indata!$R$31)*P$16)</f>
-        <v>0</v>
-      </c>
-      <c r="Q30" s="20">
-        <f>IF(OR(Indata!$K$26="",Q$29&lt;Indata!$K$26),0,(Indata!$R$26/Indata!$R$31)*Q$16)</f>
-        <v>0</v>
-      </c>
-      <c r="R30" s="20">
-        <f>IF(OR(Indata!$K$26="",R$29&lt;Indata!$K$26),0,(Indata!$R$26/Indata!$R$31)*R$16)</f>
-        <v>0</v>
-      </c>
-      <c r="S30" s="20">
-        <f>IF(OR(Indata!$K$26="",S$29&lt;Indata!$K$26),0,(Indata!$R$26/Indata!$R$31)*S$16)</f>
-        <v>0</v>
-      </c>
-      <c r="T30" s="20">
-        <f>IF(OR(Indata!$K$26="",T$29&lt;Indata!$K$26),0,(Indata!$R$26/Indata!$R$31)*T$16)</f>
-        <v>0</v>
-      </c>
-      <c r="U30" s="20">
-        <f>IF(OR(Indata!$K$26="",U$29&lt;Indata!$K$26),0,(Indata!$R$26/Indata!$R$31)*U$16)</f>
-        <v>0</v>
-      </c>
-      <c r="V30" s="20">
-        <f>IF(OR(Indata!$K$26="",V$29&lt;Indata!$K$26),0,(Indata!$R$26/Indata!$R$31)*V$16)</f>
-        <v>0</v>
-      </c>
-      <c r="W30" s="20">
-        <f>IF(OR(Indata!$K$26="",W$29&lt;Indata!$K$26),0,(Indata!$R$26/Indata!$R$31)*W$16)</f>
-        <v>0</v>
-      </c>
-      <c r="X30" s="20">
-        <f>IF(OR(Indata!$K$26="",X$29&lt;Indata!$K$26),0,(Indata!$R$26/Indata!$R$31)*X$16)</f>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="20">
-        <f>IF(OR(Indata!$K$26="",Y$29&lt;Indata!$K$26),0,(Indata!$R$26/Indata!$R$31)*Y$16)</f>
-        <v>0</v>
-      </c>
-      <c r="Z30" s="20">
-        <f>IF(OR(Indata!$K$26="",Z$29&lt;Indata!$K$26),0,(Indata!$R$26/Indata!$R$31)*Z$16)</f>
-        <v>0</v>
-      </c>
-      <c r="AA30" s="20">
-        <f>IF(OR(Indata!$K$26="",AA$29&lt;Indata!$K$26),0,(Indata!$R$26/Indata!$R$31)*AA$16)</f>
-        <v>0</v>
-      </c>
-      <c r="AB30" s="20">
-        <f>IF(OR(Indata!$K$26="",AB$29&lt;Indata!$K$26),0,(Indata!$R$26/Indata!$R$31)*AB$16)</f>
-        <v>0</v>
-      </c>
+      <c r="N30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="20"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="20"/>
+      <c r="X30" s="20"/>
+      <c r="Y30" s="20"/>
+      <c r="Z30" s="20"/>
+      <c r="AA30" s="20"/>
+      <c r="AB30" s="20"/>
     </row>
     <row r="31" spans="1:28" ht="15" customHeight="1">
       <c r="A31" s="19"/>
@@ -15905,66 +15860,21 @@
         <f>IF(OR(Indata!$K$27="",M$29&lt;Indata!$K$27),0,(Indata!$R$27/Indata!$R$31)*M$16)</f>
         <v>0</v>
       </c>
-      <c r="N31" s="20">
-        <f>IF(OR(Indata!$K$27="",N$29&lt;Indata!$K$27),0,(Indata!$R$27/Indata!$R$31)*N$16)</f>
-        <v>0</v>
-      </c>
-      <c r="O31" s="20">
-        <f>IF(OR(Indata!$K$27="",O$29&lt;Indata!$K$27),0,(Indata!$R$27/Indata!$R$31)*O$16)</f>
-        <v>0</v>
-      </c>
-      <c r="P31" s="20">
-        <f>IF(OR(Indata!$K$27="",P$29&lt;Indata!$K$27),0,(Indata!$R$27/Indata!$R$31)*P$16)</f>
-        <v>0</v>
-      </c>
-      <c r="Q31" s="20">
-        <f>IF(OR(Indata!$K$27="",Q$29&lt;Indata!$K$27),0,(Indata!$R$27/Indata!$R$31)*Q$16)</f>
-        <v>0</v>
-      </c>
-      <c r="R31" s="20">
-        <f>IF(OR(Indata!$K$27="",R$29&lt;Indata!$K$27),0,(Indata!$R$27/Indata!$R$31)*R$16)</f>
-        <v>0</v>
-      </c>
-      <c r="S31" s="20">
-        <f>IF(OR(Indata!$K$27="",S$29&lt;Indata!$K$27),0,(Indata!$R$27/Indata!$R$31)*S$16)</f>
-        <v>0</v>
-      </c>
-      <c r="T31" s="20">
-        <f>IF(OR(Indata!$K$27="",T$29&lt;Indata!$K$27),0,(Indata!$R$27/Indata!$R$31)*T$16)</f>
-        <v>0</v>
-      </c>
-      <c r="U31" s="20">
-        <f>IF(OR(Indata!$K$27="",U$29&lt;Indata!$K$27),0,(Indata!$R$27/Indata!$R$31)*U$16)</f>
-        <v>0</v>
-      </c>
-      <c r="V31" s="20">
-        <f>IF(OR(Indata!$K$27="",V$29&lt;Indata!$K$27),0,(Indata!$R$27/Indata!$R$31)*V$16)</f>
-        <v>0</v>
-      </c>
-      <c r="W31" s="20">
-        <f>IF(OR(Indata!$K$27="",W$29&lt;Indata!$K$27),0,(Indata!$R$27/Indata!$R$31)*W$16)</f>
-        <v>0</v>
-      </c>
-      <c r="X31" s="20">
-        <f>IF(OR(Indata!$K$27="",X$29&lt;Indata!$K$27),0,(Indata!$R$27/Indata!$R$31)*X$16)</f>
-        <v>0</v>
-      </c>
-      <c r="Y31" s="20">
-        <f>IF(OR(Indata!$K$27="",Y$29&lt;Indata!$K$27),0,(Indata!$R$27/Indata!$R$31)*Y$16)</f>
-        <v>0</v>
-      </c>
-      <c r="Z31" s="20">
-        <f>IF(OR(Indata!$K$27="",Z$29&lt;Indata!$K$27),0,(Indata!$R$27/Indata!$R$31)*Z$16)</f>
-        <v>0</v>
-      </c>
-      <c r="AA31" s="20">
-        <f>IF(OR(Indata!$K$27="",AA$29&lt;Indata!$K$27),0,(Indata!$R$27/Indata!$R$31)*AA$16)</f>
-        <v>0</v>
-      </c>
-      <c r="AB31" s="20">
-        <f>IF(OR(Indata!$K$27="",AB$29&lt;Indata!$K$27),0,(Indata!$R$27/Indata!$R$31)*AB$16)</f>
-        <v>0</v>
-      </c>
+      <c r="N31" s="20"/>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="20"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="20"/>
+      <c r="Z31" s="20"/>
+      <c r="AA31" s="20"/>
+      <c r="AB31" s="20"/>
     </row>
     <row r="32" spans="1:28" ht="21.75" customHeight="1">
       <c r="A32" s="19"/>
@@ -16013,66 +15923,21 @@
         <f>IF(OR(Indata!$K$28="",M$29&lt;Indata!$K$28),0,(Indata!$R$28/Indata!$R$31)*M$16)</f>
         <v>0</v>
       </c>
-      <c r="N32" s="20">
-        <f>IF(OR(Indata!$K$28="",N$29&lt;Indata!$K$28),0,(Indata!$R$28/Indata!$R$31)*N$16)</f>
-        <v>0</v>
-      </c>
-      <c r="O32" s="20">
-        <f>IF(OR(Indata!$K$28="",O$29&lt;Indata!$K$28),0,(Indata!$R$28/Indata!$R$31)*O$16)</f>
-        <v>0</v>
-      </c>
-      <c r="P32" s="20">
-        <f>IF(OR(Indata!$K$28="",P$29&lt;Indata!$K$28),0,(Indata!$R$28/Indata!$R$31)*P$16)</f>
-        <v>0</v>
-      </c>
-      <c r="Q32" s="20">
-        <f>IF(OR(Indata!$K$28="",Q$29&lt;Indata!$K$28),0,(Indata!$R$28/Indata!$R$31)*Q$16)</f>
-        <v>0</v>
-      </c>
-      <c r="R32" s="20">
-        <f>IF(OR(Indata!$K$28="",R$29&lt;Indata!$K$28),0,(Indata!$R$28/Indata!$R$31)*R$16)</f>
-        <v>0</v>
-      </c>
-      <c r="S32" s="20">
-        <f>IF(OR(Indata!$K$28="",S$29&lt;Indata!$K$28),0,(Indata!$R$28/Indata!$R$31)*S$16)</f>
-        <v>0</v>
-      </c>
-      <c r="T32" s="20">
-        <f>IF(OR(Indata!$K$28="",T$29&lt;Indata!$K$28),0,(Indata!$R$28/Indata!$R$31)*T$16)</f>
-        <v>0</v>
-      </c>
-      <c r="U32" s="20">
-        <f>IF(OR(Indata!$K$28="",U$29&lt;Indata!$K$28),0,(Indata!$R$28/Indata!$R$31)*U$16)</f>
-        <v>0</v>
-      </c>
-      <c r="V32" s="20">
-        <f>IF(OR(Indata!$K$28="",V$29&lt;Indata!$K$28),0,(Indata!$R$28/Indata!$R$31)*V$16)</f>
-        <v>0</v>
-      </c>
-      <c r="W32" s="20">
-        <f>IF(OR(Indata!$K$28="",W$29&lt;Indata!$K$28),0,(Indata!$R$28/Indata!$R$31)*W$16)</f>
-        <v>0</v>
-      </c>
-      <c r="X32" s="20">
-        <f>IF(OR(Indata!$K$28="",X$29&lt;Indata!$K$28),0,(Indata!$R$28/Indata!$R$31)*X$16)</f>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="20">
-        <f>IF(OR(Indata!$K$28="",Y$29&lt;Indata!$K$28),0,(Indata!$R$28/Indata!$R$31)*Y$16)</f>
-        <v>0</v>
-      </c>
-      <c r="Z32" s="20">
-        <f>IF(OR(Indata!$K$28="",Z$29&lt;Indata!$K$28),0,(Indata!$R$28/Indata!$R$31)*Z$16)</f>
-        <v>0</v>
-      </c>
-      <c r="AA32" s="20">
-        <f>IF(OR(Indata!$K$28="",AA$29&lt;Indata!$K$28),0,(Indata!$R$28/Indata!$R$31)*AA$16)</f>
-        <v>0</v>
-      </c>
-      <c r="AB32" s="20">
-        <f>IF(OR(Indata!$K$28="",AB$29&lt;Indata!$K$28),0,(Indata!$R$28/Indata!$R$31)*AB$16)</f>
-        <v>0</v>
-      </c>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="20"/>
+      <c r="S32" s="20"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="20"/>
+      <c r="V32" s="20"/>
+      <c r="W32" s="20"/>
+      <c r="X32" s="20"/>
+      <c r="Y32" s="20"/>
+      <c r="Z32" s="20"/>
+      <c r="AA32" s="20"/>
+      <c r="AB32" s="20"/>
     </row>
     <row r="33" spans="1:28" ht="15" customHeight="1">
       <c r="A33" s="19"/>
@@ -16121,66 +15986,21 @@
         <f>IF(OR(Indata!$K$29="",M$29&lt;Indata!$K$29),0,(Indata!$R$29/Indata!$R$31)*M$16)</f>
         <v>0</v>
       </c>
-      <c r="N33" s="20">
-        <f>IF(OR(Indata!$K$29="",N$29&lt;Indata!$K$29),0,(Indata!$R$29/Indata!$R$31)*N$16)</f>
-        <v>0</v>
-      </c>
-      <c r="O33" s="20">
-        <f>IF(OR(Indata!$K$29="",O$29&lt;Indata!$K$29),0,(Indata!$R$29/Indata!$R$31)*O$16)</f>
-        <v>0</v>
-      </c>
-      <c r="P33" s="20">
-        <f>IF(OR(Indata!$K$29="",P$29&lt;Indata!$K$29),0,(Indata!$R$29/Indata!$R$31)*P$16)</f>
-        <v>0</v>
-      </c>
-      <c r="Q33" s="20">
-        <f>IF(OR(Indata!$K$29="",Q$29&lt;Indata!$K$29),0,(Indata!$R$29/Indata!$R$31)*Q$16)</f>
-        <v>0</v>
-      </c>
-      <c r="R33" s="20">
-        <f>IF(OR(Indata!$K$29="",R$29&lt;Indata!$K$29),0,(Indata!$R$29/Indata!$R$31)*R$16)</f>
-        <v>0</v>
-      </c>
-      <c r="S33" s="20">
-        <f>IF(OR(Indata!$K$29="",S$29&lt;Indata!$K$29),0,(Indata!$R$29/Indata!$R$31)*S$16)</f>
-        <v>0</v>
-      </c>
-      <c r="T33" s="20">
-        <f>IF(OR(Indata!$K$29="",T$29&lt;Indata!$K$29),0,(Indata!$R$29/Indata!$R$31)*T$16)</f>
-        <v>0</v>
-      </c>
-      <c r="U33" s="20">
-        <f>IF(OR(Indata!$K$29="",U$29&lt;Indata!$K$29),0,(Indata!$R$29/Indata!$R$31)*U$16)</f>
-        <v>0</v>
-      </c>
-      <c r="V33" s="20">
-        <f>IF(OR(Indata!$K$29="",V$29&lt;Indata!$K$29),0,(Indata!$R$29/Indata!$R$31)*V$16)</f>
-        <v>0</v>
-      </c>
-      <c r="W33" s="20">
-        <f>IF(OR(Indata!$K$29="",W$29&lt;Indata!$K$29),0,(Indata!$R$29/Indata!$R$31)*W$16)</f>
-        <v>0</v>
-      </c>
-      <c r="X33" s="20">
-        <f>IF(OR(Indata!$K$29="",X$29&lt;Indata!$K$29),0,(Indata!$R$29/Indata!$R$31)*X$16)</f>
-        <v>0</v>
-      </c>
-      <c r="Y33" s="20">
-        <f>IF(OR(Indata!$K$29="",Y$29&lt;Indata!$K$29),0,(Indata!$R$29/Indata!$R$31)*Y$16)</f>
-        <v>0</v>
-      </c>
-      <c r="Z33" s="20">
-        <f>IF(OR(Indata!$K$29="",Z$29&lt;Indata!$K$29),0,(Indata!$R$29/Indata!$R$31)*Z$16)</f>
-        <v>0</v>
-      </c>
-      <c r="AA33" s="20">
-        <f>IF(OR(Indata!$K$29="",AA$29&lt;Indata!$K$29),0,(Indata!$R$29/Indata!$R$31)*AA$16)</f>
-        <v>0</v>
-      </c>
-      <c r="AB33" s="20">
-        <f>IF(OR(Indata!$K$29="",AB$29&lt;Indata!$K$29),0,(Indata!$R$29/Indata!$R$31)*AB$16)</f>
-        <v>0</v>
-      </c>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="20"/>
+      <c r="V33" s="20"/>
+      <c r="W33" s="20"/>
+      <c r="X33" s="20"/>
+      <c r="Y33" s="20"/>
+      <c r="Z33" s="20"/>
+      <c r="AA33" s="20"/>
+      <c r="AB33" s="20"/>
     </row>
     <row r="34" spans="1:28" ht="15" customHeight="1">
       <c r="A34" s="19"/>
@@ -16229,66 +16049,21 @@
         <f>IF(OR(Indata!$K$30="",M$29&lt;Indata!$K$30),0,(Indata!$R$30/Indata!$R$31)*M$16)</f>
         <v>0</v>
       </c>
-      <c r="N34" s="20">
-        <f>IF(OR(Indata!$K$30="",N$29&lt;Indata!$K$30),0,(Indata!$R$30/Indata!$R$31)*N$16)</f>
-        <v>0</v>
-      </c>
-      <c r="O34" s="20">
-        <f>IF(OR(Indata!$K$30="",O$29&lt;Indata!$K$30),0,(Indata!$R$30/Indata!$R$31)*O$16)</f>
-        <v>0</v>
-      </c>
-      <c r="P34" s="20">
-        <f>IF(OR(Indata!$K$30="",P$29&lt;Indata!$K$30),0,(Indata!$R$30/Indata!$R$31)*P$16)</f>
-        <v>0</v>
-      </c>
-      <c r="Q34" s="20">
-        <f>IF(OR(Indata!$K$30="",Q$29&lt;Indata!$K$30),0,(Indata!$R$30/Indata!$R$31)*Q$16)</f>
-        <v>0</v>
-      </c>
-      <c r="R34" s="20">
-        <f>IF(OR(Indata!$K$30="",R$29&lt;Indata!$K$30),0,(Indata!$R$30/Indata!$R$31)*R$16)</f>
-        <v>0</v>
-      </c>
-      <c r="S34" s="20">
-        <f>IF(OR(Indata!$K$30="",S$29&lt;Indata!$K$30),0,(Indata!$R$30/Indata!$R$31)*S$16)</f>
-        <v>0</v>
-      </c>
-      <c r="T34" s="20">
-        <f>IF(OR(Indata!$K$30="",T$29&lt;Indata!$K$30),0,(Indata!$R$30/Indata!$R$31)*T$16)</f>
-        <v>0</v>
-      </c>
-      <c r="U34" s="20">
-        <f>IF(OR(Indata!$K$30="",U$29&lt;Indata!$K$30),0,(Indata!$R$30/Indata!$R$31)*U$16)</f>
-        <v>0</v>
-      </c>
-      <c r="V34" s="20">
-        <f>IF(OR(Indata!$K$30="",V$29&lt;Indata!$K$30),0,(Indata!$R$30/Indata!$R$31)*V$16)</f>
-        <v>0</v>
-      </c>
-      <c r="W34" s="20">
-        <f>IF(OR(Indata!$K$30="",W$29&lt;Indata!$K$30),0,(Indata!$R$30/Indata!$R$31)*W$16)</f>
-        <v>0</v>
-      </c>
-      <c r="X34" s="20">
-        <f>IF(OR(Indata!$K$30="",X$29&lt;Indata!$K$30),0,(Indata!$R$30/Indata!$R$31)*X$16)</f>
-        <v>0</v>
-      </c>
-      <c r="Y34" s="20">
-        <f>IF(OR(Indata!$K$30="",Y$29&lt;Indata!$K$30),0,(Indata!$R$30/Indata!$R$31)*Y$16)</f>
-        <v>0</v>
-      </c>
-      <c r="Z34" s="20">
-        <f>IF(OR(Indata!$K$30="",Z$29&lt;Indata!$K$30),0,(Indata!$R$30/Indata!$R$31)*Z$16)</f>
-        <v>0</v>
-      </c>
-      <c r="AA34" s="20">
-        <f>IF(OR(Indata!$K$30="",AA$29&lt;Indata!$K$30),0,(Indata!$R$30/Indata!$R$31)*AA$16)</f>
-        <v>0</v>
-      </c>
-      <c r="AB34" s="20">
-        <f>IF(OR(Indata!$K$30="",AB$29&lt;Indata!$K$30),0,(Indata!$R$30/Indata!$R$31)*AB$16)</f>
-        <v>0</v>
-      </c>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="20"/>
+      <c r="S34" s="20"/>
+      <c r="T34" s="20"/>
+      <c r="U34" s="20"/>
+      <c r="V34" s="20"/>
+      <c r="W34" s="20"/>
+      <c r="X34" s="20"/>
+      <c r="Y34" s="20"/>
+      <c r="Z34" s="20"/>
+      <c r="AA34" s="20"/>
+      <c r="AB34" s="20"/>
     </row>
     <row r="35" spans="1:28" ht="15" customHeight="1">
       <c r="A35" s="19"/>
@@ -16359,7 +16134,7 @@
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="89">
-        <f t="shared" ref="D36:AB36" si="2">IFERROR(D35/D16,0)</f>
+        <f t="shared" ref="D36:M36" si="2">IFERROR(D35/D16,0)</f>
         <v>1</v>
       </c>
       <c r="E36" s="89">
@@ -16398,66 +16173,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="N36" s="20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="O36" s="20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="P36" s="20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q36" s="20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R36" s="20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S36" s="20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T36" s="20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="U36" s="20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="V36" s="20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="W36" s="20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="X36" s="20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Y36" s="20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Z36" s="20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AA36" s="20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AB36" s="20">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="N36" s="20"/>
+      <c r="O36" s="20"/>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20"/>
+      <c r="R36" s="20"/>
+      <c r="S36" s="20"/>
+      <c r="T36" s="20"/>
+      <c r="U36" s="20"/>
+      <c r="V36" s="20"/>
+      <c r="W36" s="20"/>
+      <c r="X36" s="20"/>
+      <c r="Y36" s="20"/>
+      <c r="Z36" s="20"/>
+      <c r="AA36" s="20"/>
+      <c r="AB36" s="20"/>
     </row>
     <row r="37" spans="1:28" ht="15" customHeight="1">
       <c r="A37" s="19"/>

--- a/build/oneshot/Investeringskalkyl_v2.xlsx
+++ b/build/oneshot/Investeringskalkyl_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaki\Documents\GitHub\investeringskalkyl\build\oneshot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53774B03-CC2C-4953-9660-CBF61CF32018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441E4916-F637-437A-8199-07B29D35CFF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="345" windowWidth="28800" windowHeight="16065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Översikt" sheetId="1" r:id="rId1"/>
@@ -25,15 +25,18 @@
     <sheet name="Dokumentation" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">Beräkningslogik!$B$1:$AB$230</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">Dokumentation!$B$1:$E$169</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">Beräkningslogik!$B$1:$K$230</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">Dokumentation!$B$1:$B$169</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">Finansiering!$B$1:$W$18</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">Grafer!$B$1:$N$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Försättsblad!$B$1:$I$92</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">Grafer!$B$1:$V$53</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Indata!$A$1:$R$81</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">Kassaflöde!$B$1:$W$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">Lönsamhetskontroll!$B$1:$G$87</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">Lönsamhetskontroll!$B$1:$H$87</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">Resultat!$B$1:$F$41</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Översikt!$B$1:$L$29</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">Finansiering!$B:$C</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">Kassaflöde!$B:$C</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1341,7 +1344,7 @@
     <t>TEKNISKA BERÄKNINGSBLOCK — BELOPP I TKR</t>
   </si>
   <si>
-    <t>Rådata bakom kravhyrorna. Block A/B ger NPV-kravet, D/E ger IRR-kravet, F ger MV-kravet. Belopp i tkr.</t>
+    <t>Rådata bakom kravhyrorna. Block A/B ger NPV-kravet, D/E ger IRR-kravet, F ger MV-kravet. Belopp i tkr. Blocket är kollapsat — expandera med +-symbolen i vänstermarginalen. Kollapsade rader skrivs inte ut.</t>
   </si>
   <si>
     <t>BLOCK A — Bas-kassaflöde vid årshyra = 0 · tkr</t>
@@ -2180,10 +2183,6 @@
       <name val="Segoe UI"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Segoe UI"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <name val="Segoe UI"/>
@@ -2263,6 +2262,10 @@
       <sz val="22"/>
       <color rgb="FF10313E"/>
       <name val="Segoe UI Light"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Segoe UI"/>
     </font>
   </fonts>
   <fills count="13">
@@ -2406,53 +2409,53 @@
   <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="182" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="50" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="185" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="185" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="173" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="50" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2647,11 +2650,11 @@
     <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="174" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="36" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2718,38 +2721,41 @@
     <xf numFmtId="186" fontId="33" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="181" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="52" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="51" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="52" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="53" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="45" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2852,7 +2858,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2870,9 +2878,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3098,7 +3103,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-ADD1-46F7-9AEF-1AE39D97D7A7}"/>
+              <c16:uniqueId val="{00000000-1CA9-4D5E-A208-49BFEAB06AB6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3349,7 +3354,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-302C-4D76-8516-FBF4F1C370A4}"/>
+              <c16:uniqueId val="{00000000-4CF5-4F55-8878-CEB7FD3FA1B6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3511,7 +3516,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-302C-4D76-8516-FBF4F1C370A4}"/>
+              <c16:uniqueId val="{00000001-4CF5-4F55-8878-CEB7FD3FA1B6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3672,7 +3677,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-33B2-432D-8F02-AB7C983860A7}"/>
+              <c16:uniqueId val="{00000000-6999-4FAD-AC00-046D4D7AB7C4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7493,36 +7498,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="30" customHeight="1">
+    <row r="3" spans="1:11" ht="48" customHeight="1">
       <c r="A3" s="1"/>
-      <c r="B3" s="153" t="s">
+      <c r="B3" s="154" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="152"/>
-      <c r="D3" s="152"/>
-      <c r="E3" s="152"/>
-      <c r="F3" s="152"/>
-      <c r="G3" s="152"/>
-      <c r="H3" s="152"/>
-      <c r="I3" s="152"/>
-      <c r="J3" s="152"/>
+      <c r="C3" s="153"/>
+      <c r="D3" s="153"/>
+      <c r="E3" s="153"/>
+      <c r="F3" s="153"/>
+      <c r="G3" s="153"/>
+      <c r="H3" s="153"/>
+      <c r="I3" s="153"/>
+      <c r="J3" s="153"/>
     </row>
     <row r="4" spans="1:11" ht="30" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="157" t="str">
+      <c r="B4" s="158" t="str">
         <f>Indata!B26&amp;" · Kalkylstart "&amp;Indata!C5</f>
         <v>Skola · Kalkylstart 2026</v>
       </c>
-      <c r="C4" s="152"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="152"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="152"/>
-      <c r="H4" s="152"/>
-      <c r="I4" s="152"/>
-      <c r="J4" s="152"/>
+      <c r="C4" s="153"/>
+      <c r="D4" s="153"/>
+      <c r="E4" s="153"/>
+      <c r="F4" s="153"/>
+      <c r="G4" s="153"/>
+      <c r="H4" s="153"/>
+      <c r="I4" s="153"/>
+      <c r="J4" s="153"/>
     </row>
     <row r="5" spans="1:11" ht="30" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -7562,21 +7567,21 @@
       <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="159">
+      <c r="B8" s="160">
         <f>Resultat!D14</f>
         <v>11631221.719457014</v>
       </c>
-      <c r="C8" s="152"/>
-      <c r="E8" s="159">
+      <c r="C8" s="153"/>
+      <c r="E8" s="160">
         <f>Resultat!D16</f>
         <v>2326.2443438914029</v>
       </c>
-      <c r="F8" s="152"/>
-      <c r="H8" s="158">
+      <c r="F8" s="153"/>
+      <c r="H8" s="159">
         <f>Lönsamhetskontroll!C45</f>
         <v>7.6451715426456346E-2</v>
       </c>
-      <c r="I8" s="152"/>
+      <c r="I8" s="153"/>
     </row>
     <row r="9" spans="1:11" ht="30" customHeight="1">
       <c r="A9" s="1" t="s">
@@ -7722,15 +7727,15 @@
         <f>Indata!C64</f>
         <v>0.37</v>
       </c>
-      <c r="E17" s="155" t="s">
+      <c r="E17" s="156" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="152"/>
-      <c r="H17" s="155" t="s">
+      <c r="F17" s="153"/>
+      <c r="H17" s="156" t="s">
         <v>29</v>
       </c>
-      <c r="I17" s="152"/>
-      <c r="J17" s="152"/>
+      <c r="I17" s="153"/>
+      <c r="J17" s="153"/>
     </row>
     <row r="18" spans="1:11" ht="18" customHeight="1">
       <c r="A18" s="1"/>
@@ -7741,11 +7746,11 @@
         <f>Indata!C65</f>
         <v>6.3E-2</v>
       </c>
-      <c r="E18" s="152"/>
-      <c r="F18" s="152"/>
-      <c r="H18" s="152"/>
-      <c r="I18" s="152"/>
-      <c r="J18" s="152"/>
+      <c r="E18" s="153"/>
+      <c r="F18" s="153"/>
+      <c r="H18" s="153"/>
+      <c r="I18" s="153"/>
+      <c r="J18" s="153"/>
     </row>
     <row r="19" spans="1:11" ht="18" customHeight="1">
       <c r="A19" s="1"/>
@@ -7756,11 +7761,11 @@
         <f>Indata!C7</f>
         <v>0.04</v>
       </c>
-      <c r="E19" s="152"/>
-      <c r="F19" s="152"/>
-      <c r="H19" s="152"/>
-      <c r="I19" s="152"/>
-      <c r="J19" s="152"/>
+      <c r="E19" s="153"/>
+      <c r="F19" s="153"/>
+      <c r="H19" s="153"/>
+      <c r="I19" s="153"/>
+      <c r="J19" s="153"/>
     </row>
     <row r="20" spans="1:11" ht="8.1" customHeight="1">
       <c r="A20" s="1"/>
@@ -7793,22 +7798,22 @@
     </row>
     <row r="24" spans="1:11" ht="30" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="151">
+      <c r="B24" s="152">
         <f>Resultat!C14</f>
         <v>10726244.343891403</v>
       </c>
-      <c r="C24" s="152"/>
-      <c r="E24" s="154">
+      <c r="C24" s="153"/>
+      <c r="E24" s="155">
         <f>Resultat!D14</f>
         <v>11631221.719457014</v>
       </c>
-      <c r="F24" s="152"/>
-      <c r="H24" s="151">
+      <c r="F24" s="153"/>
+      <c r="H24" s="152">
         <f>Resultat!E14</f>
         <v>12536199.095022624</v>
       </c>
-      <c r="I24" s="152"/>
-      <c r="J24" s="152"/>
+      <c r="I24" s="153"/>
+      <c r="J24" s="153"/>
     </row>
     <row r="25" spans="1:11" ht="15.95" customHeight="1">
       <c r="A25" s="1"/>
@@ -7826,17 +7831,17 @@
     </row>
     <row r="26" spans="1:11" ht="18" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="156" t="s">
+      <c r="B26" s="157" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="152"/>
-      <c r="D26" s="152"/>
-      <c r="E26" s="152"/>
-      <c r="F26" s="152"/>
-      <c r="G26" s="152"/>
-      <c r="H26" s="152"/>
-      <c r="I26" s="152"/>
-      <c r="J26" s="152"/>
+      <c r="C26" s="153"/>
+      <c r="D26" s="153"/>
+      <c r="E26" s="153"/>
+      <c r="F26" s="153"/>
+      <c r="G26" s="153"/>
+      <c r="H26" s="153"/>
+      <c r="I26" s="153"/>
+      <c r="J26" s="153"/>
     </row>
     <row r="27" spans="1:11" ht="8.1" customHeight="1">
       <c r="A27" s="1"/>
@@ -7908,7 +7913,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="100" customWidth="1"/>
+    <col min="2" max="2" width="152" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.1" customHeight="1">
@@ -7952,12 +7957,9 @@
       <c r="A4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="195" t="s">
+      <c r="B4" s="43" t="s">
         <v>491</v>
       </c>
-      <c r="C4" s="164"/>
-      <c r="D4" s="164"/>
-      <c r="E4" s="164"/>
       <c r="F4" s="147"/>
       <c r="G4" s="147"/>
     </row>
@@ -7989,12 +7991,9 @@
       <c r="A7" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="195" t="s">
+      <c r="B7" s="43" t="s">
         <v>493</v>
       </c>
-      <c r="C7" s="164"/>
-      <c r="D7" s="164"/>
-      <c r="E7" s="164"/>
       <c r="F7" s="147"/>
       <c r="G7" s="147"/>
     </row>
@@ -8026,12 +8025,9 @@
       <c r="A10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="195" t="s">
+      <c r="B10" s="43" t="s">
         <v>495</v>
       </c>
-      <c r="C10" s="164"/>
-      <c r="D10" s="164"/>
-      <c r="E10" s="164"/>
       <c r="F10" s="147"/>
       <c r="G10" s="147"/>
     </row>
@@ -8044,7 +8040,7 @@
       <c r="F11" s="40"/>
       <c r="G11" s="40"/>
     </row>
-    <row r="12" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="12" spans="1:7" ht="14.25" customHeight="1">
       <c r="A12" s="19"/>
       <c r="B12" s="148" t="s">
         <v>496</v>
@@ -8055,7 +8051,7 @@
       <c r="F12" s="40"/>
       <c r="G12" s="40"/>
     </row>
-    <row r="13" spans="1:7" ht="16.5" customHeight="1">
+    <row r="13" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A13" s="19"/>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -8064,7 +8060,7 @@
       <c r="F13" s="40"/>
       <c r="G13" s="40"/>
     </row>
-    <row r="14" spans="1:7" ht="21.95" customHeight="1">
+    <row r="14" spans="1:7" ht="16.5" customHeight="1">
       <c r="A14" s="19"/>
       <c r="B14" s="43" t="s">
         <v>497</v>
@@ -8075,7 +8071,7 @@
       <c r="F14" s="147"/>
       <c r="G14" s="147"/>
     </row>
-    <row r="15" spans="1:7" ht="33" customHeight="1">
+    <row r="15" spans="1:7" ht="14.25" customHeight="1">
       <c r="A15" s="19"/>
       <c r="B15" s="148" t="s">
         <v>498</v>
@@ -8086,7 +8082,7 @@
       <c r="F15" s="40"/>
       <c r="G15" s="40"/>
     </row>
-    <row r="16" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="16" spans="1:7" ht="14.25" customHeight="1">
       <c r="A16" s="19"/>
       <c r="B16" s="148" t="s">
         <v>499</v>
@@ -8097,7 +8093,7 @@
       <c r="F16" s="40"/>
       <c r="G16" s="40"/>
     </row>
-    <row r="17" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="17" spans="1:7" ht="14.25" customHeight="1">
       <c r="A17" s="19"/>
       <c r="B17" s="148" t="s">
         <v>500</v>
@@ -8108,7 +8104,7 @@
       <c r="F17" s="40"/>
       <c r="G17" s="40"/>
     </row>
-    <row r="18" spans="1:7" ht="16.5" customHeight="1">
+    <row r="18" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A18" s="19"/>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
@@ -8117,7 +8113,7 @@
       <c r="F18" s="40"/>
       <c r="G18" s="40"/>
     </row>
-    <row r="19" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="19" spans="1:7" ht="18" customHeight="1">
       <c r="A19" s="19"/>
       <c r="B19" s="149" t="s">
         <v>501</v>
@@ -8128,7 +8124,7 @@
       <c r="F19" s="40"/>
       <c r="G19" s="40"/>
     </row>
-    <row r="20" spans="1:7" ht="47.45" customHeight="1">
+    <row r="20" spans="1:7" ht="26.65" customHeight="1">
       <c r="A20" s="19"/>
       <c r="B20" s="148" t="s">
         <v>502</v>
@@ -8139,7 +8135,7 @@
       <c r="F20" s="40"/>
       <c r="G20" s="40"/>
     </row>
-    <row r="21" spans="1:7" ht="16.5" customHeight="1">
+    <row r="21" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A21" s="19"/>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -8148,7 +8144,7 @@
       <c r="F21" s="40"/>
       <c r="G21" s="40"/>
     </row>
-    <row r="22" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="22" spans="1:7" ht="14.25" customHeight="1">
       <c r="A22" s="19"/>
       <c r="B22" s="148" t="s">
         <v>503</v>
@@ -8159,7 +8155,7 @@
       <c r="F22" s="40"/>
       <c r="G22" s="40"/>
     </row>
-    <row r="23" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="23" spans="1:7" ht="14.25" customHeight="1">
       <c r="A23" s="19"/>
       <c r="B23" s="148" t="s">
         <v>504</v>
@@ -8170,7 +8166,7 @@
       <c r="F23" s="40"/>
       <c r="G23" s="40"/>
     </row>
-    <row r="24" spans="1:7" ht="16.5" customHeight="1">
+    <row r="24" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A24" s="19"/>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
@@ -8179,7 +8175,7 @@
       <c r="F24" s="40"/>
       <c r="G24" s="40"/>
     </row>
-    <row r="25" spans="1:7" ht="33" customHeight="1">
+    <row r="25" spans="1:7" ht="14.25" customHeight="1">
       <c r="A25" s="19"/>
       <c r="B25" s="148" t="s">
         <v>505</v>
@@ -8190,7 +8186,7 @@
       <c r="F25" s="40"/>
       <c r="G25" s="40"/>
     </row>
-    <row r="26" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="26" spans="1:7" ht="14.25" customHeight="1">
       <c r="A26" s="19"/>
       <c r="B26" s="148" t="s">
         <v>506</v>
@@ -8201,7 +8197,7 @@
       <c r="F26" s="40"/>
       <c r="G26" s="40"/>
     </row>
-    <row r="27" spans="1:7" ht="16.5" customHeight="1">
+    <row r="27" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A27" s="19"/>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
@@ -8210,7 +8206,7 @@
       <c r="F27" s="40"/>
       <c r="G27" s="40"/>
     </row>
-    <row r="28" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="28" spans="1:7" ht="18" customHeight="1">
       <c r="A28" s="19"/>
       <c r="B28" s="149" t="s">
         <v>507</v>
@@ -8221,7 +8217,7 @@
       <c r="F28" s="40"/>
       <c r="G28" s="40"/>
     </row>
-    <row r="29" spans="1:7" ht="33" customHeight="1">
+    <row r="29" spans="1:7" ht="26.65" customHeight="1">
       <c r="A29" s="19"/>
       <c r="B29" s="148" t="s">
         <v>508</v>
@@ -8232,7 +8228,7 @@
       <c r="F29" s="40"/>
       <c r="G29" s="40"/>
     </row>
-    <row r="30" spans="1:7" ht="16.5" customHeight="1">
+    <row r="30" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A30" s="19"/>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
@@ -8241,7 +8237,7 @@
       <c r="F30" s="40"/>
       <c r="G30" s="40"/>
     </row>
-    <row r="31" spans="1:7" ht="33" customHeight="1">
+    <row r="31" spans="1:7" ht="14.25" customHeight="1">
       <c r="A31" s="19"/>
       <c r="B31" s="148" t="s">
         <v>509</v>
@@ -8252,7 +8248,7 @@
       <c r="F31" s="40"/>
       <c r="G31" s="40"/>
     </row>
-    <row r="32" spans="1:7" ht="16.5" customHeight="1">
+    <row r="32" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A32" s="19"/>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
@@ -8261,7 +8257,7 @@
       <c r="F32" s="40"/>
       <c r="G32" s="40"/>
     </row>
-    <row r="33" spans="1:7" ht="47.45" customHeight="1">
+    <row r="33" spans="1:7" ht="26.65" customHeight="1">
       <c r="A33" s="19"/>
       <c r="B33" s="148" t="s">
         <v>510</v>
@@ -8272,7 +8268,7 @@
       <c r="F33" s="40"/>
       <c r="G33" s="40"/>
     </row>
-    <row r="34" spans="1:7" ht="16.5" customHeight="1">
+    <row r="34" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A34" s="19"/>
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
@@ -8281,7 +8277,7 @@
       <c r="F34" s="40"/>
       <c r="G34" s="40"/>
     </row>
-    <row r="35" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="35" spans="1:7" ht="14.25" customHeight="1">
       <c r="A35" s="19"/>
       <c r="B35" s="148" t="s">
         <v>511</v>
@@ -8292,7 +8288,7 @@
       <c r="F35" s="40"/>
       <c r="G35" s="40"/>
     </row>
-    <row r="36" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="36" spans="1:7" ht="14.25" customHeight="1">
       <c r="A36" s="19"/>
       <c r="B36" s="148" t="s">
         <v>512</v>
@@ -8303,7 +8299,7 @@
       <c r="F36" s="40"/>
       <c r="G36" s="40"/>
     </row>
-    <row r="37" spans="1:7" ht="16.5" customHeight="1">
+    <row r="37" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A37" s="19"/>
       <c r="B37" s="20"/>
       <c r="C37" s="20"/>
@@ -8312,7 +8308,7 @@
       <c r="F37" s="40"/>
       <c r="G37" s="40"/>
     </row>
-    <row r="38" spans="1:7" ht="33" customHeight="1">
+    <row r="38" spans="1:7" ht="29.45" customHeight="1">
       <c r="A38" s="19"/>
       <c r="B38" s="150" t="s">
         <v>513</v>
@@ -8323,7 +8319,7 @@
       <c r="F38" s="40"/>
       <c r="G38" s="40"/>
     </row>
-    <row r="39" spans="1:7" ht="16.5" customHeight="1">
+    <row r="39" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A39" s="19"/>
       <c r="B39" s="20"/>
       <c r="C39" s="20"/>
@@ -8332,18 +8328,15 @@
       <c r="F39" s="40"/>
       <c r="G39" s="40"/>
     </row>
-    <row r="40" spans="1:7" ht="21.95" customHeight="1">
+    <row r="40" spans="1:7" ht="16.5" customHeight="1">
       <c r="A40" s="19"/>
-      <c r="B40" s="195" t="s">
+      <c r="B40" s="43" t="s">
         <v>514</v>
       </c>
-      <c r="C40" s="164"/>
-      <c r="D40" s="164"/>
-      <c r="E40" s="164"/>
       <c r="F40" s="147"/>
       <c r="G40" s="147"/>
     </row>
-    <row r="41" spans="1:7" ht="33" customHeight="1">
+    <row r="41" spans="1:7" ht="14.25" customHeight="1">
       <c r="A41" s="19"/>
       <c r="B41" s="148" t="s">
         <v>515</v>
@@ -8354,7 +8347,7 @@
       <c r="F41" s="40"/>
       <c r="G41" s="40"/>
     </row>
-    <row r="42" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="42" spans="1:7" ht="14.25" customHeight="1">
       <c r="A42" s="19"/>
       <c r="B42" s="148" t="s">
         <v>516</v>
@@ -8365,7 +8358,7 @@
       <c r="F42" s="40"/>
       <c r="G42" s="40"/>
     </row>
-    <row r="43" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="43" spans="1:7" ht="14.25" customHeight="1">
       <c r="A43" s="19"/>
       <c r="B43" s="148" t="s">
         <v>517</v>
@@ -8376,7 +8369,7 @@
       <c r="F43" s="40"/>
       <c r="G43" s="40"/>
     </row>
-    <row r="44" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="44" spans="1:7" ht="14.25" customHeight="1">
       <c r="A44" s="19"/>
       <c r="B44" s="148" t="s">
         <v>518</v>
@@ -8387,7 +8380,7 @@
       <c r="F44" s="40"/>
       <c r="G44" s="40"/>
     </row>
-    <row r="45" spans="1:7" ht="16.5" customHeight="1">
+    <row r="45" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A45" s="19"/>
       <c r="B45" s="20"/>
       <c r="C45" s="20"/>
@@ -8396,7 +8389,7 @@
       <c r="F45" s="40"/>
       <c r="G45" s="40"/>
     </row>
-    <row r="46" spans="1:7" ht="33" customHeight="1">
+    <row r="46" spans="1:7" ht="14.25" customHeight="1">
       <c r="A46" s="19"/>
       <c r="B46" s="148" t="s">
         <v>519</v>
@@ -8407,7 +8400,7 @@
       <c r="F46" s="40"/>
       <c r="G46" s="40"/>
     </row>
-    <row r="47" spans="1:7" ht="16.5" customHeight="1">
+    <row r="47" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A47" s="19"/>
       <c r="B47" s="20"/>
       <c r="C47" s="20"/>
@@ -8416,7 +8409,7 @@
       <c r="F47" s="40"/>
       <c r="G47" s="40"/>
     </row>
-    <row r="48" spans="1:7" ht="47.45" customHeight="1">
+    <row r="48" spans="1:7" ht="26.65" customHeight="1">
       <c r="A48" s="19"/>
       <c r="B48" s="148" t="s">
         <v>520</v>
@@ -8427,7 +8420,7 @@
       <c r="F48" s="40"/>
       <c r="G48" s="40"/>
     </row>
-    <row r="49" spans="1:7" ht="16.5" customHeight="1">
+    <row r="49" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A49" s="19"/>
       <c r="B49" s="20"/>
       <c r="C49" s="20"/>
@@ -8436,18 +8429,15 @@
       <c r="F49" s="40"/>
       <c r="G49" s="40"/>
     </row>
-    <row r="50" spans="1:7" ht="21.95" customHeight="1">
+    <row r="50" spans="1:7" ht="16.5" customHeight="1">
       <c r="A50" s="19"/>
-      <c r="B50" s="195" t="s">
+      <c r="B50" s="43" t="s">
         <v>521</v>
       </c>
-      <c r="C50" s="164"/>
-      <c r="D50" s="164"/>
-      <c r="E50" s="164"/>
       <c r="F50" s="147"/>
       <c r="G50" s="147"/>
     </row>
-    <row r="51" spans="1:7" ht="33" customHeight="1">
+    <row r="51" spans="1:7" ht="26.65" customHeight="1">
       <c r="A51" s="19"/>
       <c r="B51" s="148" t="s">
         <v>522</v>
@@ -8458,7 +8448,7 @@
       <c r="F51" s="40"/>
       <c r="G51" s="40"/>
     </row>
-    <row r="52" spans="1:7" ht="16.5" customHeight="1">
+    <row r="52" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A52" s="19"/>
       <c r="B52" s="20"/>
       <c r="C52" s="20"/>
@@ -8467,7 +8457,7 @@
       <c r="F52" s="40"/>
       <c r="G52" s="40"/>
     </row>
-    <row r="53" spans="1:7" ht="33" customHeight="1">
+    <row r="53" spans="1:7" ht="14.25" customHeight="1">
       <c r="A53" s="19"/>
       <c r="B53" s="148" t="s">
         <v>523</v>
@@ -8478,7 +8468,7 @@
       <c r="F53" s="40"/>
       <c r="G53" s="40"/>
     </row>
-    <row r="54" spans="1:7" ht="16.5" customHeight="1">
+    <row r="54" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A54" s="19"/>
       <c r="B54" s="20"/>
       <c r="C54" s="20"/>
@@ -8487,7 +8477,7 @@
       <c r="F54" s="40"/>
       <c r="G54" s="40"/>
     </row>
-    <row r="55" spans="1:7" ht="33" customHeight="1">
+    <row r="55" spans="1:7" ht="26.65" customHeight="1">
       <c r="A55" s="19"/>
       <c r="B55" s="148" t="s">
         <v>524</v>
@@ -8498,7 +8488,7 @@
       <c r="F55" s="40"/>
       <c r="G55" s="40"/>
     </row>
-    <row r="56" spans="1:7" ht="16.5" customHeight="1">
+    <row r="56" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A56" s="19"/>
       <c r="B56" s="20"/>
       <c r="C56" s="20"/>
@@ -8507,18 +8497,15 @@
       <c r="F56" s="40"/>
       <c r="G56" s="40"/>
     </row>
-    <row r="57" spans="1:7" ht="21.95" customHeight="1">
+    <row r="57" spans="1:7" ht="16.5" customHeight="1">
       <c r="A57" s="19"/>
-      <c r="B57" s="195" t="s">
+      <c r="B57" s="43" t="s">
         <v>525</v>
       </c>
-      <c r="C57" s="164"/>
-      <c r="D57" s="164"/>
-      <c r="E57" s="164"/>
       <c r="F57" s="147"/>
       <c r="G57" s="147"/>
     </row>
-    <row r="58" spans="1:7" ht="33" customHeight="1">
+    <row r="58" spans="1:7" ht="14.25" customHeight="1">
       <c r="A58" s="19"/>
       <c r="B58" s="148" t="s">
         <v>526</v>
@@ -8529,7 +8516,7 @@
       <c r="F58" s="40"/>
       <c r="G58" s="40"/>
     </row>
-    <row r="59" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="59" spans="1:7" ht="14.25" customHeight="1">
       <c r="A59" s="19"/>
       <c r="B59" s="148" t="s">
         <v>527</v>
@@ -8540,7 +8527,7 @@
       <c r="F59" s="40"/>
       <c r="G59" s="40"/>
     </row>
-    <row r="60" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="60" spans="1:7" ht="14.25" customHeight="1">
       <c r="A60" s="19"/>
       <c r="B60" s="148" t="s">
         <v>528</v>
@@ -8551,7 +8538,7 @@
       <c r="F60" s="40"/>
       <c r="G60" s="40"/>
     </row>
-    <row r="61" spans="1:7" ht="16.5" customHeight="1">
+    <row r="61" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A61" s="19"/>
       <c r="B61" s="20"/>
       <c r="C61" s="20"/>
@@ -8560,7 +8547,7 @@
       <c r="F61" s="40"/>
       <c r="G61" s="40"/>
     </row>
-    <row r="62" spans="1:7" ht="47.45" customHeight="1">
+    <row r="62" spans="1:7" ht="26.65" customHeight="1">
       <c r="A62" s="19"/>
       <c r="B62" s="148" t="s">
         <v>529</v>
@@ -8571,7 +8558,7 @@
       <c r="F62" s="40"/>
       <c r="G62" s="40"/>
     </row>
-    <row r="63" spans="1:7" ht="16.5" customHeight="1">
+    <row r="63" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A63" s="19"/>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
@@ -8580,18 +8567,15 @@
       <c r="F63" s="40"/>
       <c r="G63" s="40"/>
     </row>
-    <row r="64" spans="1:7" ht="21.95" customHeight="1">
+    <row r="64" spans="1:7" ht="16.5" customHeight="1">
       <c r="A64" s="19"/>
-      <c r="B64" s="195" t="s">
+      <c r="B64" s="43" t="s">
         <v>530</v>
       </c>
-      <c r="C64" s="164"/>
-      <c r="D64" s="164"/>
-      <c r="E64" s="164"/>
       <c r="F64" s="147"/>
       <c r="G64" s="147"/>
     </row>
-    <row r="65" spans="1:7" ht="33" customHeight="1">
+    <row r="65" spans="1:7" ht="26.65" customHeight="1">
       <c r="A65" s="19"/>
       <c r="B65" s="148" t="s">
         <v>531</v>
@@ -8602,7 +8586,7 @@
       <c r="F65" s="40"/>
       <c r="G65" s="40"/>
     </row>
-    <row r="66" spans="1:7" ht="16.5" customHeight="1">
+    <row r="66" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A66" s="19"/>
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
@@ -8611,7 +8595,7 @@
       <c r="F66" s="40"/>
       <c r="G66" s="40"/>
     </row>
-    <row r="67" spans="1:7" ht="33" customHeight="1">
+    <row r="67" spans="1:7" ht="26.65" customHeight="1">
       <c r="A67" s="19"/>
       <c r="B67" s="148" t="s">
         <v>532</v>
@@ -8622,7 +8606,7 @@
       <c r="F67" s="40"/>
       <c r="G67" s="40"/>
     </row>
-    <row r="68" spans="1:7" ht="16.5" customHeight="1">
+    <row r="68" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A68" s="19"/>
       <c r="B68" s="20"/>
       <c r="C68" s="20"/>
@@ -8631,7 +8615,7 @@
       <c r="F68" s="40"/>
       <c r="G68" s="40"/>
     </row>
-    <row r="69" spans="1:7" ht="33" customHeight="1">
+    <row r="69" spans="1:7" ht="14.25" customHeight="1">
       <c r="A69" s="19"/>
       <c r="B69" s="148" t="s">
         <v>533</v>
@@ -8642,7 +8626,7 @@
       <c r="F69" s="40"/>
       <c r="G69" s="40"/>
     </row>
-    <row r="70" spans="1:7" ht="16.5" customHeight="1">
+    <row r="70" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A70" s="19"/>
       <c r="B70" s="20"/>
       <c r="C70" s="20"/>
@@ -8651,18 +8635,15 @@
       <c r="F70" s="40"/>
       <c r="G70" s="40"/>
     </row>
-    <row r="71" spans="1:7" ht="21.95" customHeight="1">
+    <row r="71" spans="1:7" ht="16.5" customHeight="1">
       <c r="A71" s="19"/>
-      <c r="B71" s="195" t="s">
+      <c r="B71" s="43" t="s">
         <v>534</v>
       </c>
-      <c r="C71" s="164"/>
-      <c r="D71" s="164"/>
-      <c r="E71" s="164"/>
       <c r="F71" s="147"/>
       <c r="G71" s="147"/>
     </row>
-    <row r="72" spans="1:7" ht="33" customHeight="1">
+    <row r="72" spans="1:7" ht="14.25" customHeight="1">
       <c r="A72" s="19"/>
       <c r="B72" s="148" t="s">
         <v>535</v>
@@ -8673,7 +8654,7 @@
       <c r="F72" s="40"/>
       <c r="G72" s="40"/>
     </row>
-    <row r="73" spans="1:7" ht="16.5" customHeight="1">
+    <row r="73" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A73" s="19"/>
       <c r="B73" s="20"/>
       <c r="C73" s="20"/>
@@ -8682,7 +8663,7 @@
       <c r="F73" s="40"/>
       <c r="G73" s="40"/>
     </row>
-    <row r="74" spans="1:7" ht="33" customHeight="1">
+    <row r="74" spans="1:7" ht="18" customHeight="1">
       <c r="A74" s="19"/>
       <c r="B74" s="149" t="s">
         <v>536</v>
@@ -8693,7 +8674,7 @@
       <c r="F74" s="40"/>
       <c r="G74" s="40"/>
     </row>
-    <row r="75" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="75" spans="1:7" ht="14.25" customHeight="1">
       <c r="A75" s="19"/>
       <c r="B75" s="148" t="s">
         <v>537</v>
@@ -8704,7 +8685,7 @@
       <c r="F75" s="40"/>
       <c r="G75" s="40"/>
     </row>
-    <row r="76" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="76" spans="1:7" ht="14.25" customHeight="1">
       <c r="A76" s="19"/>
       <c r="B76" s="148" t="s">
         <v>538</v>
@@ -8715,7 +8696,7 @@
       <c r="F76" s="40"/>
       <c r="G76" s="40"/>
     </row>
-    <row r="77" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="77" spans="1:7" ht="14.25" customHeight="1">
       <c r="A77" s="19"/>
       <c r="B77" s="148" t="s">
         <v>539</v>
@@ -8726,7 +8707,7 @@
       <c r="F77" s="40"/>
       <c r="G77" s="40"/>
     </row>
-    <row r="78" spans="1:7" ht="16.5" customHeight="1">
+    <row r="78" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A78" s="19"/>
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
@@ -8735,18 +8716,15 @@
       <c r="F78" s="40"/>
       <c r="G78" s="40"/>
     </row>
-    <row r="79" spans="1:7" ht="21.95" customHeight="1">
+    <row r="79" spans="1:7" ht="16.5" customHeight="1">
       <c r="A79" s="19"/>
-      <c r="B79" s="195" t="s">
+      <c r="B79" s="43" t="s">
         <v>540</v>
       </c>
-      <c r="C79" s="164"/>
-      <c r="D79" s="164"/>
-      <c r="E79" s="164"/>
       <c r="F79" s="147"/>
       <c r="G79" s="147"/>
     </row>
-    <row r="80" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="80" spans="1:7" ht="14.25" customHeight="1">
       <c r="A80" s="19"/>
       <c r="B80" s="148" t="s">
         <v>541</v>
@@ -8757,7 +8735,7 @@
       <c r="F80" s="40"/>
       <c r="G80" s="40"/>
     </row>
-    <row r="81" spans="1:7" ht="16.5" customHeight="1">
+    <row r="81" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A81" s="19"/>
       <c r="B81" s="20"/>
       <c r="C81" s="20"/>
@@ -8766,7 +8744,7 @@
       <c r="F81" s="40"/>
       <c r="G81" s="40"/>
     </row>
-    <row r="82" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="82" spans="1:7" ht="18" customHeight="1">
       <c r="A82" s="19"/>
       <c r="B82" s="149" t="s">
         <v>542</v>
@@ -8777,7 +8755,7 @@
       <c r="F82" s="40"/>
       <c r="G82" s="40"/>
     </row>
-    <row r="83" spans="1:7" ht="33" customHeight="1">
+    <row r="83" spans="1:7" ht="26.65" customHeight="1">
       <c r="A83" s="19"/>
       <c r="B83" s="148" t="s">
         <v>543</v>
@@ -8788,7 +8766,7 @@
       <c r="F83" s="40"/>
       <c r="G83" s="40"/>
     </row>
-    <row r="84" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="84" spans="1:7" ht="14.25" customHeight="1">
       <c r="A84" s="19"/>
       <c r="B84" s="148" t="s">
         <v>544</v>
@@ -8799,7 +8777,7 @@
       <c r="F84" s="40"/>
       <c r="G84" s="40"/>
     </row>
-    <row r="85" spans="1:7" ht="16.5" customHeight="1">
+    <row r="85" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A85" s="19"/>
       <c r="B85" s="20"/>
       <c r="C85" s="20"/>
@@ -8808,7 +8786,7 @@
       <c r="F85" s="40"/>
       <c r="G85" s="40"/>
     </row>
-    <row r="86" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="86" spans="1:7" ht="18" customHeight="1">
       <c r="A86" s="19"/>
       <c r="B86" s="149" t="s">
         <v>545</v>
@@ -8819,7 +8797,7 @@
       <c r="F86" s="40"/>
       <c r="G86" s="40"/>
     </row>
-    <row r="87" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="87" spans="1:7" ht="14.25" customHeight="1">
       <c r="A87" s="19"/>
       <c r="B87" s="148" t="s">
         <v>546</v>
@@ -8830,7 +8808,7 @@
       <c r="F87" s="40"/>
       <c r="G87" s="40"/>
     </row>
-    <row r="88" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="88" spans="1:7" ht="14.25" customHeight="1">
       <c r="A88" s="19"/>
       <c r="B88" s="148" t="s">
         <v>547</v>
@@ -8841,7 +8819,7 @@
       <c r="F88" s="40"/>
       <c r="G88" s="40"/>
     </row>
-    <row r="89" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="89" spans="1:7" ht="14.25" customHeight="1">
       <c r="A89" s="19"/>
       <c r="B89" s="148" t="s">
         <v>548</v>
@@ -8852,7 +8830,7 @@
       <c r="F89" s="40"/>
       <c r="G89" s="40"/>
     </row>
-    <row r="90" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="90" spans="1:7" ht="14.25" customHeight="1">
       <c r="A90" s="19"/>
       <c r="B90" s="148" t="s">
         <v>549</v>
@@ -8863,7 +8841,7 @@
       <c r="F90" s="40"/>
       <c r="G90" s="40"/>
     </row>
-    <row r="91" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="91" spans="1:7" ht="14.25" customHeight="1">
       <c r="A91" s="19"/>
       <c r="B91" s="148" t="s">
         <v>550</v>
@@ -8874,7 +8852,7 @@
       <c r="F91" s="40"/>
       <c r="G91" s="40"/>
     </row>
-    <row r="92" spans="1:7" ht="16.5" customHeight="1">
+    <row r="92" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A92" s="19"/>
       <c r="B92" s="20"/>
       <c r="C92" s="20"/>
@@ -8883,7 +8861,7 @@
       <c r="F92" s="40"/>
       <c r="G92" s="40"/>
     </row>
-    <row r="93" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="93" spans="1:7" ht="18" customHeight="1">
       <c r="A93" s="19"/>
       <c r="B93" s="149" t="s">
         <v>551</v>
@@ -8894,7 +8872,7 @@
       <c r="F93" s="40"/>
       <c r="G93" s="40"/>
     </row>
-    <row r="94" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="94" spans="1:7" ht="14.25" customHeight="1">
       <c r="A94" s="19"/>
       <c r="B94" s="148" t="s">
         <v>552</v>
@@ -8905,7 +8883,7 @@
       <c r="F94" s="40"/>
       <c r="G94" s="40"/>
     </row>
-    <row r="95" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="95" spans="1:7" ht="14.25" customHeight="1">
       <c r="A95" s="19"/>
       <c r="B95" s="148" t="s">
         <v>553</v>
@@ -8916,7 +8894,7 @@
       <c r="F95" s="40"/>
       <c r="G95" s="40"/>
     </row>
-    <row r="96" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="96" spans="1:7" ht="14.25" customHeight="1">
       <c r="A96" s="19"/>
       <c r="B96" s="148" t="s">
         <v>554</v>
@@ -8927,7 +8905,7 @@
       <c r="F96" s="40"/>
       <c r="G96" s="40"/>
     </row>
-    <row r="97" spans="1:7" ht="16.5" customHeight="1">
+    <row r="97" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A97" s="19"/>
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
@@ -8936,18 +8914,15 @@
       <c r="F97" s="40"/>
       <c r="G97" s="40"/>
     </row>
-    <row r="98" spans="1:7" ht="21.95" customHeight="1">
+    <row r="98" spans="1:7" ht="16.5" customHeight="1">
       <c r="A98" s="19"/>
-      <c r="B98" s="195" t="s">
+      <c r="B98" s="43" t="s">
         <v>555</v>
       </c>
-      <c r="C98" s="164"/>
-      <c r="D98" s="164"/>
-      <c r="E98" s="164"/>
       <c r="F98" s="147"/>
       <c r="G98" s="147"/>
     </row>
-    <row r="99" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="99" spans="1:7" ht="14.25" customHeight="1">
       <c r="A99" s="19"/>
       <c r="B99" s="148" t="s">
         <v>556</v>
@@ -8958,7 +8933,7 @@
       <c r="F99" s="40"/>
       <c r="G99" s="40"/>
     </row>
-    <row r="100" spans="1:7" ht="16.5" customHeight="1">
+    <row r="100" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A100" s="19"/>
       <c r="B100" s="20"/>
       <c r="C100" s="20"/>
@@ -8967,7 +8942,7 @@
       <c r="F100" s="40"/>
       <c r="G100" s="40"/>
     </row>
-    <row r="101" spans="1:7" ht="33" customHeight="1">
+    <row r="101" spans="1:7" ht="26.65" customHeight="1">
       <c r="A101" s="19"/>
       <c r="B101" s="148" t="s">
         <v>557</v>
@@ -8978,7 +8953,7 @@
       <c r="F101" s="40"/>
       <c r="G101" s="40"/>
     </row>
-    <row r="102" spans="1:7" ht="16.5" customHeight="1">
+    <row r="102" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A102" s="19"/>
       <c r="B102" s="20"/>
       <c r="C102" s="20"/>
@@ -8987,7 +8962,7 @@
       <c r="F102" s="40"/>
       <c r="G102" s="40"/>
     </row>
-    <row r="103" spans="1:7" ht="33" customHeight="1">
+    <row r="103" spans="1:7" ht="26.65" customHeight="1">
       <c r="A103" s="19"/>
       <c r="B103" s="148" t="s">
         <v>558</v>
@@ -8998,7 +8973,7 @@
       <c r="F103" s="40"/>
       <c r="G103" s="40"/>
     </row>
-    <row r="104" spans="1:7" ht="16.5" customHeight="1">
+    <row r="104" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A104" s="19"/>
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
@@ -9007,7 +8982,7 @@
       <c r="F104" s="40"/>
       <c r="G104" s="40"/>
     </row>
-    <row r="105" spans="1:7" ht="33" customHeight="1">
+    <row r="105" spans="1:7" ht="14.25" customHeight="1">
       <c r="A105" s="19"/>
       <c r="B105" s="148" t="s">
         <v>559</v>
@@ -9018,7 +8993,7 @@
       <c r="F105" s="40"/>
       <c r="G105" s="40"/>
     </row>
-    <row r="106" spans="1:7" ht="16.5" customHeight="1">
+    <row r="106" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A106" s="19"/>
       <c r="B106" s="20"/>
       <c r="C106" s="20"/>
@@ -9027,7 +9002,7 @@
       <c r="F106" s="40"/>
       <c r="G106" s="40"/>
     </row>
-    <row r="107" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="107" spans="1:7" ht="14.25" customHeight="1">
       <c r="A107" s="19"/>
       <c r="B107" s="148" t="s">
         <v>560</v>
@@ -9038,7 +9013,7 @@
       <c r="F107" s="40"/>
       <c r="G107" s="40"/>
     </row>
-    <row r="108" spans="1:7" ht="16.5" customHeight="1">
+    <row r="108" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A108" s="19"/>
       <c r="B108" s="20"/>
       <c r="C108" s="20"/>
@@ -9047,7 +9022,7 @@
       <c r="F108" s="40"/>
       <c r="G108" s="40"/>
     </row>
-    <row r="109" spans="1:7" ht="47.45" customHeight="1">
+    <row r="109" spans="1:7" ht="26.65" customHeight="1">
       <c r="A109" s="19"/>
       <c r="B109" s="148" t="s">
         <v>561</v>
@@ -9058,7 +9033,7 @@
       <c r="F109" s="40"/>
       <c r="G109" s="40"/>
     </row>
-    <row r="110" spans="1:7" ht="16.5" customHeight="1">
+    <row r="110" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A110" s="19"/>
       <c r="B110" s="20"/>
       <c r="C110" s="20"/>
@@ -9067,18 +9042,15 @@
       <c r="F110" s="40"/>
       <c r="G110" s="40"/>
     </row>
-    <row r="111" spans="1:7" ht="21.95" customHeight="1">
+    <row r="111" spans="1:7" ht="16.5" customHeight="1">
       <c r="A111" s="19"/>
-      <c r="B111" s="195" t="s">
+      <c r="B111" s="43" t="s">
         <v>562</v>
       </c>
-      <c r="C111" s="164"/>
-      <c r="D111" s="164"/>
-      <c r="E111" s="164"/>
       <c r="F111" s="147"/>
       <c r="G111" s="147"/>
     </row>
-    <row r="112" spans="1:7" ht="47.45" customHeight="1">
+    <row r="112" spans="1:7" ht="26.65" customHeight="1">
       <c r="A112" s="19"/>
       <c r="B112" s="148" t="s">
         <v>563</v>
@@ -9089,7 +9061,7 @@
       <c r="F112" s="40"/>
       <c r="G112" s="40"/>
     </row>
-    <row r="113" spans="1:7" ht="16.5" customHeight="1">
+    <row r="113" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A113" s="19"/>
       <c r="B113" s="20"/>
       <c r="C113" s="20"/>
@@ -9098,18 +9070,15 @@
       <c r="F113" s="40"/>
       <c r="G113" s="40"/>
     </row>
-    <row r="114" spans="1:7" ht="21.95" customHeight="1">
+    <row r="114" spans="1:7" ht="16.5" customHeight="1">
       <c r="A114" s="19"/>
-      <c r="B114" s="195" t="s">
+      <c r="B114" s="43" t="s">
         <v>564</v>
       </c>
-      <c r="C114" s="164"/>
-      <c r="D114" s="164"/>
-      <c r="E114" s="164"/>
       <c r="F114" s="147"/>
       <c r="G114" s="147"/>
     </row>
-    <row r="115" spans="1:7" ht="62.1" customHeight="1">
+    <row r="115" spans="1:7" ht="39" customHeight="1">
       <c r="A115" s="19"/>
       <c r="B115" s="148" t="s">
         <v>565</v>
@@ -9120,7 +9089,7 @@
       <c r="F115" s="40"/>
       <c r="G115" s="40"/>
     </row>
-    <row r="116" spans="1:7" ht="16.5" customHeight="1">
+    <row r="116" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A116" s="19"/>
       <c r="B116" s="20"/>
       <c r="C116" s="20"/>
@@ -9129,7 +9098,7 @@
       <c r="F116" s="40"/>
       <c r="G116" s="40"/>
     </row>
-    <row r="117" spans="1:7" ht="33" customHeight="1">
+    <row r="117" spans="1:7" ht="14.25" customHeight="1">
       <c r="A117" s="19"/>
       <c r="B117" s="148" t="s">
         <v>566</v>
@@ -9140,7 +9109,7 @@
       <c r="F117" s="40"/>
       <c r="G117" s="40"/>
     </row>
-    <row r="118" spans="1:7" ht="16.5" customHeight="1">
+    <row r="118" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A118" s="19"/>
       <c r="B118" s="20"/>
       <c r="C118" s="20"/>
@@ -9149,18 +9118,15 @@
       <c r="F118" s="40"/>
       <c r="G118" s="40"/>
     </row>
-    <row r="119" spans="1:7" ht="21.95" customHeight="1">
+    <row r="119" spans="1:7" ht="16.5" customHeight="1">
       <c r="A119" s="19"/>
-      <c r="B119" s="195" t="s">
+      <c r="B119" s="43" t="s">
         <v>567</v>
       </c>
-      <c r="C119" s="164"/>
-      <c r="D119" s="164"/>
-      <c r="E119" s="164"/>
       <c r="F119" s="147"/>
       <c r="G119" s="147"/>
     </row>
-    <row r="120" spans="1:7" ht="47.45" customHeight="1">
+    <row r="120" spans="1:7" ht="26.65" customHeight="1">
       <c r="A120" s="19"/>
       <c r="B120" s="148" t="s">
         <v>568</v>
@@ -9171,7 +9137,7 @@
       <c r="F120" s="40"/>
       <c r="G120" s="40"/>
     </row>
-    <row r="121" spans="1:7" ht="16.5" customHeight="1">
+    <row r="121" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A121" s="19"/>
       <c r="B121" s="20"/>
       <c r="C121" s="20"/>
@@ -9180,7 +9146,7 @@
       <c r="F121" s="40"/>
       <c r="G121" s="40"/>
     </row>
-    <row r="122" spans="1:7" ht="47.45" customHeight="1">
+    <row r="122" spans="1:7" ht="26.65" customHeight="1">
       <c r="A122" s="19"/>
       <c r="B122" s="148" t="s">
         <v>569</v>
@@ -9191,7 +9157,7 @@
       <c r="F122" s="40"/>
       <c r="G122" s="40"/>
     </row>
-    <row r="123" spans="1:7" ht="16.5" customHeight="1">
+    <row r="123" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A123" s="19"/>
       <c r="B123" s="20"/>
       <c r="C123" s="20"/>
@@ -9200,7 +9166,7 @@
       <c r="F123" s="40"/>
       <c r="G123" s="40"/>
     </row>
-    <row r="124" spans="1:7" ht="33" customHeight="1">
+    <row r="124" spans="1:7" ht="26.65" customHeight="1">
       <c r="A124" s="19"/>
       <c r="B124" s="148" t="s">
         <v>570</v>
@@ -9211,7 +9177,7 @@
       <c r="F124" s="40"/>
       <c r="G124" s="40"/>
     </row>
-    <row r="125" spans="1:7" ht="16.5" customHeight="1">
+    <row r="125" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A125" s="19"/>
       <c r="B125" s="20"/>
       <c r="C125" s="20"/>
@@ -9220,18 +9186,15 @@
       <c r="F125" s="40"/>
       <c r="G125" s="40"/>
     </row>
-    <row r="126" spans="1:7" ht="21.95" customHeight="1">
+    <row r="126" spans="1:7" ht="16.5" customHeight="1">
       <c r="A126" s="19"/>
-      <c r="B126" s="195" t="s">
+      <c r="B126" s="43" t="s">
         <v>571</v>
       </c>
-      <c r="C126" s="164"/>
-      <c r="D126" s="164"/>
-      <c r="E126" s="164"/>
       <c r="F126" s="147"/>
       <c r="G126" s="147"/>
     </row>
-    <row r="127" spans="1:7" ht="16.5" customHeight="1">
+    <row r="127" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A127" s="19"/>
       <c r="B127" s="20"/>
       <c r="C127" s="20"/>
@@ -9240,7 +9203,7 @@
       <c r="F127" s="40"/>
       <c r="G127" s="40"/>
     </row>
-    <row r="128" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="128" spans="1:7" ht="14.25" customHeight="1">
       <c r="A128" s="19"/>
       <c r="B128" s="148" t="s">
         <v>572</v>
@@ -9251,7 +9214,7 @@
       <c r="F128" s="40"/>
       <c r="G128" s="40"/>
     </row>
-    <row r="129" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="129" spans="1:7" ht="14.25" customHeight="1">
       <c r="A129" s="19"/>
       <c r="B129" s="148" t="s">
         <v>573</v>
@@ -9262,7 +9225,7 @@
       <c r="F129" s="40"/>
       <c r="G129" s="40"/>
     </row>
-    <row r="130" spans="1:7" ht="16.5" customHeight="1">
+    <row r="130" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A130" s="19"/>
       <c r="B130" s="20"/>
       <c r="C130" s="20"/>
@@ -9271,7 +9234,7 @@
       <c r="F130" s="40"/>
       <c r="G130" s="40"/>
     </row>
-    <row r="131" spans="1:7" ht="47.45" customHeight="1">
+    <row r="131" spans="1:7" ht="26.65" customHeight="1">
       <c r="A131" s="19"/>
       <c r="B131" s="148" t="s">
         <v>574</v>
@@ -9282,7 +9245,7 @@
       <c r="F131" s="40"/>
       <c r="G131" s="40"/>
     </row>
-    <row r="132" spans="1:7" ht="16.5" customHeight="1">
+    <row r="132" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A132" s="19"/>
       <c r="B132" s="20"/>
       <c r="C132" s="20"/>
@@ -9291,7 +9254,7 @@
       <c r="F132" s="40"/>
       <c r="G132" s="40"/>
     </row>
-    <row r="133" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="133" spans="1:7" ht="18" customHeight="1">
       <c r="A133" s="19"/>
       <c r="B133" s="149" t="s">
         <v>575</v>
@@ -9302,7 +9265,7 @@
       <c r="F133" s="40"/>
       <c r="G133" s="40"/>
     </row>
-    <row r="134" spans="1:7" ht="62.1" customHeight="1">
+    <row r="134" spans="1:7" ht="39" customHeight="1">
       <c r="A134" s="19"/>
       <c r="B134" s="148" t="s">
         <v>576</v>
@@ -9313,7 +9276,7 @@
       <c r="F134" s="40"/>
       <c r="G134" s="40"/>
     </row>
-    <row r="135" spans="1:7" ht="16.5" customHeight="1">
+    <row r="135" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A135" s="19"/>
       <c r="B135" s="20"/>
       <c r="C135" s="20"/>
@@ -9322,7 +9285,7 @@
       <c r="F135" s="40"/>
       <c r="G135" s="40"/>
     </row>
-    <row r="136" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="136" spans="1:7" ht="18" customHeight="1">
       <c r="A136" s="19"/>
       <c r="B136" s="149" t="s">
         <v>577</v>
@@ -9333,7 +9296,7 @@
       <c r="F136" s="40"/>
       <c r="G136" s="40"/>
     </row>
-    <row r="137" spans="1:7" ht="62.1" customHeight="1">
+    <row r="137" spans="1:7" ht="26.65" customHeight="1">
       <c r="A137" s="19"/>
       <c r="B137" s="148" t="s">
         <v>578</v>
@@ -9344,7 +9307,7 @@
       <c r="F137" s="40"/>
       <c r="G137" s="40"/>
     </row>
-    <row r="138" spans="1:7" ht="16.5" customHeight="1">
+    <row r="138" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A138" s="19"/>
       <c r="B138" s="20"/>
       <c r="C138" s="20"/>
@@ -9353,7 +9316,7 @@
       <c r="F138" s="40"/>
       <c r="G138" s="40"/>
     </row>
-    <row r="139" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="139" spans="1:7" ht="18" customHeight="1">
       <c r="A139" s="19"/>
       <c r="B139" s="149" t="s">
         <v>579</v>
@@ -9364,7 +9327,7 @@
       <c r="F139" s="40"/>
       <c r="G139" s="40"/>
     </row>
-    <row r="140" spans="1:7" ht="33" customHeight="1">
+    <row r="140" spans="1:7" ht="14.25" customHeight="1">
       <c r="A140" s="19"/>
       <c r="B140" s="148" t="s">
         <v>580</v>
@@ -9375,7 +9338,7 @@
       <c r="F140" s="40"/>
       <c r="G140" s="40"/>
     </row>
-    <row r="141" spans="1:7" ht="16.5" customHeight="1">
+    <row r="141" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A141" s="19"/>
       <c r="B141" s="20"/>
       <c r="C141" s="20"/>
@@ -9384,7 +9347,7 @@
       <c r="F141" s="40"/>
       <c r="G141" s="40"/>
     </row>
-    <row r="142" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="142" spans="1:7" ht="14.25" customHeight="1">
       <c r="A142" s="19"/>
       <c r="B142" s="148" t="s">
         <v>581</v>
@@ -9395,7 +9358,7 @@
       <c r="F142" s="40"/>
       <c r="G142" s="40"/>
     </row>
-    <row r="143" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="143" spans="1:7" ht="14.25" customHeight="1">
       <c r="A143" s="19"/>
       <c r="B143" s="148" t="s">
         <v>582</v>
@@ -9406,7 +9369,7 @@
       <c r="F143" s="40"/>
       <c r="G143" s="40"/>
     </row>
-    <row r="144" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="144" spans="1:7" ht="14.25" customHeight="1">
       <c r="A144" s="19"/>
       <c r="B144" s="148" t="s">
         <v>583</v>
@@ -9417,7 +9380,7 @@
       <c r="F144" s="40"/>
       <c r="G144" s="40"/>
     </row>
-    <row r="145" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="145" spans="1:7" ht="14.25" customHeight="1">
       <c r="A145" s="19"/>
       <c r="B145" s="148" t="s">
         <v>584</v>
@@ -9428,7 +9391,7 @@
       <c r="F145" s="40"/>
       <c r="G145" s="40"/>
     </row>
-    <row r="146" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="146" spans="1:7" ht="14.25" customHeight="1">
       <c r="A146" s="19"/>
       <c r="B146" s="148" t="s">
         <v>585</v>
@@ -9439,7 +9402,7 @@
       <c r="F146" s="40"/>
       <c r="G146" s="40"/>
     </row>
-    <row r="147" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="147" spans="1:7" ht="14.25" customHeight="1">
       <c r="A147" s="19"/>
       <c r="B147" s="148" t="s">
         <v>586</v>
@@ -9450,7 +9413,7 @@
       <c r="F147" s="40"/>
       <c r="G147" s="40"/>
     </row>
-    <row r="148" spans="1:7" ht="16.5" customHeight="1">
+    <row r="148" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A148" s="19"/>
       <c r="B148" s="20"/>
       <c r="C148" s="20"/>
@@ -9459,7 +9422,7 @@
       <c r="F148" s="40"/>
       <c r="G148" s="40"/>
     </row>
-    <row r="149" spans="1:7" ht="62.1" customHeight="1">
+    <row r="149" spans="1:7" ht="39" customHeight="1">
       <c r="A149" s="19"/>
       <c r="B149" s="148" t="s">
         <v>587</v>
@@ -9470,7 +9433,7 @@
       <c r="F149" s="40"/>
       <c r="G149" s="40"/>
     </row>
-    <row r="150" spans="1:7" ht="16.5" customHeight="1">
+    <row r="150" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A150" s="19"/>
       <c r="B150" s="20"/>
       <c r="C150" s="20"/>
@@ -9479,7 +9442,7 @@
       <c r="F150" s="40"/>
       <c r="G150" s="40"/>
     </row>
-    <row r="151" spans="1:7" ht="47.45" customHeight="1">
+    <row r="151" spans="1:7" ht="26.65" customHeight="1">
       <c r="A151" s="19"/>
       <c r="B151" s="148" t="s">
         <v>588</v>
@@ -9490,7 +9453,7 @@
       <c r="F151" s="40"/>
       <c r="G151" s="40"/>
     </row>
-    <row r="152" spans="1:7" ht="16.5" customHeight="1">
+    <row r="152" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A152" s="19"/>
       <c r="B152" s="20"/>
       <c r="C152" s="20"/>
@@ -9499,7 +9462,7 @@
       <c r="F152" s="40"/>
       <c r="G152" s="40"/>
     </row>
-    <row r="153" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="153" spans="1:7" ht="18" customHeight="1">
       <c r="A153" s="19"/>
       <c r="B153" s="149" t="s">
         <v>589</v>
@@ -9510,7 +9473,7 @@
       <c r="F153" s="40"/>
       <c r="G153" s="40"/>
     </row>
-    <row r="154" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="154" spans="1:7" ht="14.25" customHeight="1">
       <c r="A154" s="19"/>
       <c r="B154" s="148" t="s">
         <v>590</v>
@@ -9521,7 +9484,7 @@
       <c r="F154" s="40"/>
       <c r="G154" s="40"/>
     </row>
-    <row r="155" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="155" spans="1:7" ht="14.25" customHeight="1">
       <c r="A155" s="19"/>
       <c r="B155" s="148" t="s">
         <v>591</v>
@@ -9532,7 +9495,7 @@
       <c r="F155" s="40"/>
       <c r="G155" s="40"/>
     </row>
-    <row r="156" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="156" spans="1:7" ht="14.25" customHeight="1">
       <c r="A156" s="19"/>
       <c r="B156" s="148" t="s">
         <v>592</v>
@@ -9543,7 +9506,7 @@
       <c r="F156" s="40"/>
       <c r="G156" s="40"/>
     </row>
-    <row r="157" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="157" spans="1:7" ht="14.25" customHeight="1">
       <c r="A157" s="19"/>
       <c r="B157" s="148" t="s">
         <v>593</v>
@@ -9554,7 +9517,7 @@
       <c r="F157" s="40"/>
       <c r="G157" s="40"/>
     </row>
-    <row r="158" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="158" spans="1:7" ht="14.25" customHeight="1">
       <c r="A158" s="19"/>
       <c r="B158" s="148" t="s">
         <v>594</v>
@@ -9565,7 +9528,7 @@
       <c r="F158" s="40"/>
       <c r="G158" s="40"/>
     </row>
-    <row r="159" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="159" spans="1:7" ht="14.25" customHeight="1">
       <c r="A159" s="19"/>
       <c r="B159" s="148" t="s">
         <v>595</v>
@@ -9576,7 +9539,7 @@
       <c r="F159" s="40"/>
       <c r="G159" s="40"/>
     </row>
-    <row r="160" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="160" spans="1:7" ht="14.25" customHeight="1">
       <c r="A160" s="19"/>
       <c r="B160" s="148" t="s">
         <v>596</v>
@@ -9587,7 +9550,7 @@
       <c r="F160" s="40"/>
       <c r="G160" s="40"/>
     </row>
-    <row r="161" spans="1:7" ht="16.5" customHeight="1">
+    <row r="161" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A161" s="19"/>
       <c r="B161" s="20"/>
       <c r="C161" s="20"/>
@@ -9596,7 +9559,7 @@
       <c r="F161" s="40"/>
       <c r="G161" s="40"/>
     </row>
-    <row r="162" spans="1:7" ht="47.45" customHeight="1">
+    <row r="162" spans="1:7" ht="26.65" customHeight="1">
       <c r="A162" s="19"/>
       <c r="B162" s="148" t="s">
         <v>597</v>
@@ -9607,7 +9570,7 @@
       <c r="F162" s="40"/>
       <c r="G162" s="40"/>
     </row>
-    <row r="163" spans="1:7" ht="16.5" customHeight="1">
+    <row r="163" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A163" s="19"/>
       <c r="B163" s="20"/>
       <c r="C163" s="20"/>
@@ -9616,7 +9579,7 @@
       <c r="F163" s="40"/>
       <c r="G163" s="40"/>
     </row>
-    <row r="164" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="164" spans="1:7" ht="18" customHeight="1">
       <c r="A164" s="19"/>
       <c r="B164" s="149" t="s">
         <v>598</v>
@@ -9627,7 +9590,7 @@
       <c r="F164" s="40"/>
       <c r="G164" s="40"/>
     </row>
-    <row r="165" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="165" spans="1:7" ht="14.25" customHeight="1">
       <c r="A165" s="19"/>
       <c r="B165" s="148" t="s">
         <v>599</v>
@@ -9638,29 +9601,23 @@
       <c r="F165" s="40"/>
       <c r="G165" s="40"/>
     </row>
-    <row r="166" spans="1:7" ht="47.45" customHeight="1">
+    <row r="166" spans="1:7" ht="33.950000000000003" customHeight="1">
       <c r="A166" s="19"/>
-      <c r="B166" s="203" t="s">
+      <c r="B166" s="151" t="s">
         <v>600</v>
       </c>
-      <c r="C166" s="152"/>
-      <c r="D166" s="152"/>
-      <c r="E166" s="152"/>
       <c r="F166" s="40"/>
       <c r="G166" s="40"/>
     </row>
-    <row r="167" spans="1:7" ht="62.1" customHeight="1">
+    <row r="167" spans="1:7" ht="49.9" customHeight="1">
       <c r="A167" s="19"/>
-      <c r="B167" s="203" t="s">
+      <c r="B167" s="151" t="s">
         <v>601</v>
       </c>
-      <c r="C167" s="152"/>
-      <c r="D167" s="152"/>
-      <c r="E167" s="152"/>
       <c r="F167" s="40"/>
       <c r="G167" s="40"/>
     </row>
-    <row r="168" spans="1:7" ht="16.5" customHeight="1">
+    <row r="168" spans="1:7" ht="2.4500000000000002" customHeight="1">
       <c r="A168" s="19"/>
       <c r="B168" s="20"/>
       <c r="C168" s="20"/>
@@ -9669,7 +9626,7 @@
       <c r="F168" s="40"/>
       <c r="G168" s="40"/>
     </row>
-    <row r="169" spans="1:7" ht="47.45" customHeight="1">
+    <row r="169" spans="1:7" ht="26.65" customHeight="1">
       <c r="A169" s="19"/>
       <c r="B169" s="148" t="s">
         <v>602</v>
@@ -9741,24 +9698,6 @@
       <c r="A179" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="B166:E166"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B119:E119"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B167:E167"/>
-    <mergeCell ref="B64:E64"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B114:E114"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B79:E79"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="B126:E126"/>
-  </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" location="'Försättsblad'!A1" display="Försättsblad" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
     <hyperlink ref="A3" location="'Översikt'!A1" display="Översikt" xr:uid="{00000000-0004-0000-0900-000001000000}"/>
@@ -9770,7 +9709,7 @@
     <hyperlink ref="A9" location="'Lönsamhetskontroll'!A1" display="Lönsamhetskontroll" xr:uid="{00000000-0004-0000-0900-000007000000}"/>
     <hyperlink ref="A10" location="'Beräkningslogik'!A1" display="Beräkningslogik" xr:uid="{00000000-0004-0000-0900-000008000000}"/>
   </hyperlinks>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -9809,16 +9748,16 @@
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
       <c r="A2" s="19"/>
-      <c r="B2" s="179" t="s">
+      <c r="B2" s="180" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="152"/>
-      <c r="D2" s="152"/>
-      <c r="E2" s="152"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
+      <c r="C2" s="153"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="153"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="153"/>
+      <c r="I2" s="153"/>
     </row>
     <row r="3" spans="1:9" ht="30" customHeight="1">
       <c r="A3" s="19" t="s">
@@ -9833,36 +9772,36 @@
       <c r="H3" s="22"/>
       <c r="I3" s="22"/>
     </row>
-    <row r="4" spans="1:9" ht="30" customHeight="1">
+    <row r="4" spans="1:9" ht="56.1" customHeight="1">
       <c r="A4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="187" t="s">
+      <c r="B4" s="188" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="152"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="152"/>
-      <c r="F4" s="152"/>
-      <c r="G4" s="152"/>
-      <c r="H4" s="152"/>
-      <c r="I4" s="152"/>
+      <c r="C4" s="153"/>
+      <c r="D4" s="153"/>
+      <c r="E4" s="153"/>
+      <c r="F4" s="153"/>
+      <c r="G4" s="153"/>
+      <c r="H4" s="153"/>
+      <c r="I4" s="153"/>
     </row>
     <row r="5" spans="1:9" ht="30" customHeight="1">
       <c r="A5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="185" t="str">
+      <c r="B5" s="186" t="str">
         <f>IF(Indata!B26="","(projekt ej namngivet)",Indata!B26&amp;" · "&amp;IF(Indata!C26="Nyb","Nybyggnad",IF(Indata!C26="Omb","Ombyggnad","Befintligt")))</f>
         <v>Skola · Nybyggnad</v>
       </c>
-      <c r="C5" s="152"/>
-      <c r="D5" s="152"/>
-      <c r="E5" s="152"/>
-      <c r="F5" s="152"/>
-      <c r="G5" s="152"/>
-      <c r="H5" s="152"/>
-      <c r="I5" s="152"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="153"/>
+      <c r="H5" s="153"/>
+      <c r="I5" s="153"/>
     </row>
     <row r="6" spans="1:9" ht="30" customHeight="1">
       <c r="A6" s="19" t="s">
@@ -9899,21 +9838,21 @@
       <c r="B8" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="177" t="str">
+      <c r="C8" s="178" t="str">
         <f>Indata!B26</f>
         <v>Skola</v>
       </c>
-      <c r="D8" s="152"/>
-      <c r="E8" s="152"/>
+      <c r="D8" s="153"/>
+      <c r="E8" s="153"/>
       <c r="F8" s="20"/>
       <c r="G8" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="186">
+      <c r="H8" s="187">
         <f>Indata!C5</f>
         <v>2026</v>
       </c>
-      <c r="I8" s="152"/>
+      <c r="I8" s="153"/>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1">
       <c r="A9" s="19" t="s">
@@ -9922,20 +9861,20 @@
       <c r="B9" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="168" t="s">
+      <c r="C9" s="169" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="152"/>
-      <c r="E9" s="152"/>
+      <c r="D9" s="153"/>
+      <c r="E9" s="153"/>
       <c r="F9" s="20"/>
       <c r="G9" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="166">
+      <c r="H9" s="167">
         <f>Indata!C16</f>
         <v>20</v>
       </c>
-      <c r="I9" s="152"/>
+      <c r="I9" s="153"/>
     </row>
     <row r="10" spans="1:9" ht="30" customHeight="1">
       <c r="A10" s="19" t="s">
@@ -9944,20 +9883,20 @@
       <c r="B10" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="168" t="s">
+      <c r="C10" s="169" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="152"/>
-      <c r="E10" s="152"/>
+      <c r="D10" s="153"/>
+      <c r="E10" s="153"/>
       <c r="F10" s="20"/>
       <c r="G10" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="H10" s="165">
+      <c r="H10" s="166">
         <f>Indata!R31</f>
         <v>200000000</v>
       </c>
-      <c r="I10" s="152"/>
+      <c r="I10" s="153"/>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1">
       <c r="A11" s="19" t="s">
@@ -9966,61 +9905,61 @@
       <c r="B11" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="168" t="s">
+      <c r="C11" s="169" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="152"/>
-      <c r="E11" s="152"/>
+      <c r="D11" s="153"/>
+      <c r="E11" s="153"/>
       <c r="F11" s="20"/>
       <c r="G11" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="181">
+      <c r="H11" s="182">
         <f>Indata!F31</f>
         <v>5000</v>
       </c>
-      <c r="I11" s="152"/>
+      <c r="I11" s="153"/>
     </row>
     <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="19"/>
       <c r="B12" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="168" t="s">
+      <c r="C12" s="169" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="152"/>
-      <c r="E12" s="152"/>
+      <c r="D12" s="153"/>
+      <c r="E12" s="153"/>
       <c r="F12" s="20"/>
       <c r="G12" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="H12" s="177" t="str">
+      <c r="H12" s="178" t="str">
         <f>IF(Indata!C26="Nyb","Nybyggnad",IF(Indata!C26="Omb","Ombyggnad","Befintligt"))</f>
         <v>Nybyggnad</v>
       </c>
-      <c r="I12" s="152"/>
+      <c r="I12" s="153"/>
     </row>
     <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="19"/>
       <c r="B13" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="171">
+      <c r="C13" s="172">
         <f>Indata!C12</f>
         <v>1</v>
       </c>
-      <c r="D13" s="152"/>
-      <c r="E13" s="152"/>
+      <c r="D13" s="153"/>
+      <c r="E13" s="153"/>
       <c r="F13" s="20"/>
       <c r="G13" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="H13" s="171">
+      <c r="H13" s="172">
         <f>Indata!C13</f>
         <v>1</v>
       </c>
-      <c r="I13" s="152"/>
+      <c r="I13" s="153"/>
     </row>
     <row r="14" spans="1:9" ht="16.5" customHeight="1">
       <c r="A14" s="19"/>
@@ -10198,12 +10137,12 @@
     </row>
     <row r="24" spans="1:9" ht="18" customHeight="1">
       <c r="A24" s="19"/>
-      <c r="B24" s="172" t="s">
+      <c r="B24" s="173" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="152"/>
-      <c r="D24" s="152"/>
-      <c r="E24" s="152"/>
+      <c r="C24" s="153"/>
+      <c r="D24" s="153"/>
+      <c r="E24" s="153"/>
       <c r="F24" s="20"/>
       <c r="G24" s="20"/>
       <c r="H24" s="20"/>
@@ -10211,38 +10150,38 @@
     </row>
     <row r="25" spans="1:9" ht="21.95" customHeight="1">
       <c r="A25" s="19"/>
-      <c r="B25" s="167" t="s">
+      <c r="B25" s="168" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="152"/>
-      <c r="D25" s="152"/>
-      <c r="E25" s="152"/>
-      <c r="F25" s="152"/>
-      <c r="G25" s="152"/>
-      <c r="H25" s="152"/>
-      <c r="I25" s="152"/>
+      <c r="C25" s="153"/>
+      <c r="D25" s="153"/>
+      <c r="E25" s="153"/>
+      <c r="F25" s="153"/>
+      <c r="G25" s="153"/>
+      <c r="H25" s="153"/>
+      <c r="I25" s="153"/>
     </row>
     <row r="26" spans="1:9" ht="21.95" customHeight="1">
       <c r="A26" s="19"/>
-      <c r="B26" s="152"/>
-      <c r="C26" s="152"/>
-      <c r="D26" s="152"/>
-      <c r="E26" s="152"/>
-      <c r="F26" s="152"/>
-      <c r="G26" s="152"/>
-      <c r="H26" s="152"/>
-      <c r="I26" s="152"/>
+      <c r="B26" s="153"/>
+      <c r="C26" s="153"/>
+      <c r="D26" s="153"/>
+      <c r="E26" s="153"/>
+      <c r="F26" s="153"/>
+      <c r="G26" s="153"/>
+      <c r="H26" s="153"/>
+      <c r="I26" s="153"/>
     </row>
     <row r="27" spans="1:9" ht="21.95" customHeight="1">
       <c r="A27" s="19"/>
-      <c r="B27" s="152"/>
-      <c r="C27" s="152"/>
-      <c r="D27" s="152"/>
-      <c r="E27" s="152"/>
-      <c r="F27" s="152"/>
-      <c r="G27" s="152"/>
-      <c r="H27" s="152"/>
-      <c r="I27" s="152"/>
+      <c r="B27" s="153"/>
+      <c r="C27" s="153"/>
+      <c r="D27" s="153"/>
+      <c r="E27" s="153"/>
+      <c r="F27" s="153"/>
+      <c r="G27" s="153"/>
+      <c r="H27" s="153"/>
+      <c r="I27" s="153"/>
     </row>
     <row r="28" spans="1:9" ht="15.95" customHeight="1">
       <c r="A28" s="19"/>
@@ -10270,95 +10209,95 @@
     </row>
     <row r="30" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A30" s="19"/>
-      <c r="B30" s="169" t="s">
+      <c r="B30" s="170" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="152"/>
-      <c r="D30" s="152"/>
-      <c r="E30" s="152"/>
+      <c r="C30" s="153"/>
+      <c r="D30" s="153"/>
+      <c r="E30" s="153"/>
       <c r="F30" s="20"/>
-      <c r="G30" s="169" t="s">
+      <c r="G30" s="170" t="s">
         <v>64</v>
       </c>
-      <c r="H30" s="152"/>
-      <c r="I30" s="152"/>
+      <c r="H30" s="153"/>
+      <c r="I30" s="153"/>
     </row>
     <row r="31" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A31" s="19"/>
-      <c r="B31" s="152"/>
-      <c r="C31" s="152"/>
-      <c r="D31" s="152"/>
-      <c r="E31" s="152"/>
+      <c r="B31" s="153"/>
+      <c r="C31" s="153"/>
+      <c r="D31" s="153"/>
+      <c r="E31" s="153"/>
       <c r="F31" s="20"/>
-      <c r="G31" s="152"/>
-      <c r="H31" s="152"/>
-      <c r="I31" s="152"/>
+      <c r="G31" s="153"/>
+      <c r="H31" s="153"/>
+      <c r="I31" s="153"/>
     </row>
     <row r="32" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A32" s="19"/>
-      <c r="B32" s="152"/>
-      <c r="C32" s="152"/>
-      <c r="D32" s="152"/>
-      <c r="E32" s="152"/>
+      <c r="B32" s="153"/>
+      <c r="C32" s="153"/>
+      <c r="D32" s="153"/>
+      <c r="E32" s="153"/>
       <c r="F32" s="20"/>
-      <c r="G32" s="152"/>
-      <c r="H32" s="152"/>
-      <c r="I32" s="152"/>
+      <c r="G32" s="153"/>
+      <c r="H32" s="153"/>
+      <c r="I32" s="153"/>
     </row>
     <row r="33" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A33" s="19"/>
-      <c r="B33" s="152"/>
-      <c r="C33" s="152"/>
-      <c r="D33" s="152"/>
-      <c r="E33" s="152"/>
+      <c r="B33" s="153"/>
+      <c r="C33" s="153"/>
+      <c r="D33" s="153"/>
+      <c r="E33" s="153"/>
       <c r="F33" s="20"/>
-      <c r="G33" s="152"/>
-      <c r="H33" s="152"/>
-      <c r="I33" s="152"/>
+      <c r="G33" s="153"/>
+      <c r="H33" s="153"/>
+      <c r="I33" s="153"/>
     </row>
     <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A34" s="19"/>
-      <c r="B34" s="152"/>
-      <c r="C34" s="152"/>
-      <c r="D34" s="152"/>
-      <c r="E34" s="152"/>
+      <c r="B34" s="153"/>
+      <c r="C34" s="153"/>
+      <c r="D34" s="153"/>
+      <c r="E34" s="153"/>
       <c r="F34" s="20"/>
-      <c r="G34" s="152"/>
-      <c r="H34" s="152"/>
-      <c r="I34" s="152"/>
+      <c r="G34" s="153"/>
+      <c r="H34" s="153"/>
+      <c r="I34" s="153"/>
     </row>
     <row r="35" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A35" s="19"/>
-      <c r="B35" s="152"/>
-      <c r="C35" s="152"/>
-      <c r="D35" s="152"/>
-      <c r="E35" s="152"/>
+      <c r="B35" s="153"/>
+      <c r="C35" s="153"/>
+      <c r="D35" s="153"/>
+      <c r="E35" s="153"/>
       <c r="F35" s="20"/>
-      <c r="G35" s="152"/>
-      <c r="H35" s="152"/>
-      <c r="I35" s="152"/>
+      <c r="G35" s="153"/>
+      <c r="H35" s="153"/>
+      <c r="I35" s="153"/>
     </row>
     <row r="36" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A36" s="19"/>
-      <c r="B36" s="152"/>
-      <c r="C36" s="152"/>
-      <c r="D36" s="152"/>
-      <c r="E36" s="152"/>
+      <c r="B36" s="153"/>
+      <c r="C36" s="153"/>
+      <c r="D36" s="153"/>
+      <c r="E36" s="153"/>
       <c r="F36" s="20"/>
-      <c r="G36" s="152"/>
-      <c r="H36" s="152"/>
-      <c r="I36" s="152"/>
+      <c r="G36" s="153"/>
+      <c r="H36" s="153"/>
+      <c r="I36" s="153"/>
     </row>
     <row r="37" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A37" s="19"/>
-      <c r="B37" s="152"/>
-      <c r="C37" s="152"/>
-      <c r="D37" s="152"/>
-      <c r="E37" s="152"/>
+      <c r="B37" s="153"/>
+      <c r="C37" s="153"/>
+      <c r="D37" s="153"/>
+      <c r="E37" s="153"/>
       <c r="F37" s="20"/>
-      <c r="G37" s="152"/>
-      <c r="H37" s="152"/>
-      <c r="I37" s="152"/>
+      <c r="G37" s="153"/>
+      <c r="H37" s="153"/>
+      <c r="I37" s="153"/>
     </row>
     <row r="38" spans="1:9" ht="15.95" customHeight="1">
       <c r="A38" s="19"/>
@@ -10389,19 +10328,19 @@
       <c r="B40" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="C40" s="168" t="s">
+      <c r="C40" s="169" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="152"/>
-      <c r="E40" s="152"/>
+      <c r="D40" s="153"/>
+      <c r="E40" s="153"/>
       <c r="F40" s="20"/>
       <c r="G40" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="H40" s="168" t="s">
+      <c r="H40" s="169" t="s">
         <v>42</v>
       </c>
-      <c r="I40" s="152"/>
+      <c r="I40" s="153"/>
     </row>
     <row r="41" spans="1:9" ht="16.5" customHeight="1">
       <c r="A41" s="19"/>
@@ -10494,63 +10433,63 @@
       <c r="B47" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C47" s="166">
+      <c r="C47" s="167">
         <f>Indata!C16</f>
         <v>20</v>
       </c>
-      <c r="D47" s="152"/>
-      <c r="E47" s="152"/>
+      <c r="D47" s="153"/>
+      <c r="E47" s="153"/>
       <c r="F47" s="20"/>
       <c r="G47" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="H47" s="166">
+      <c r="H47" s="167">
         <f>Indata!C19</f>
         <v>33</v>
       </c>
-      <c r="I47" s="152"/>
+      <c r="I47" s="153"/>
     </row>
     <row r="48" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A48" s="19"/>
       <c r="B48" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="C48" s="171">
+      <c r="C48" s="172">
         <f>Indata!$D$81</f>
         <v>0.05</v>
       </c>
-      <c r="D48" s="152"/>
-      <c r="E48" s="152"/>
+      <c r="D48" s="153"/>
+      <c r="E48" s="153"/>
       <c r="F48" s="20"/>
       <c r="G48" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="H48" s="171">
+      <c r="H48" s="172">
         <f>Indata!C7</f>
         <v>0.04</v>
       </c>
-      <c r="I48" s="152"/>
+      <c r="I48" s="153"/>
     </row>
     <row r="49" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A49" s="19"/>
       <c r="B49" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="C49" s="171">
+      <c r="C49" s="172">
         <f>Indata!C9</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D49" s="152"/>
-      <c r="E49" s="152"/>
+      <c r="D49" s="153"/>
+      <c r="E49" s="153"/>
       <c r="F49" s="20"/>
       <c r="G49" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="H49" s="171">
+      <c r="H49" s="172">
         <f>Indata!C8</f>
         <v>0.02</v>
       </c>
-      <c r="I49" s="152"/>
+      <c r="I49" s="153"/>
     </row>
     <row r="50" spans="1:9" ht="16.5" customHeight="1">
       <c r="A50" s="19"/>
@@ -10592,84 +10531,84 @@
       <c r="B53" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="C53" s="182">
+      <c r="C53" s="183">
         <f>Resultat!D14</f>
         <v>11631221.719457014</v>
       </c>
-      <c r="D53" s="152"/>
-      <c r="E53" s="152"/>
+      <c r="D53" s="153"/>
+      <c r="E53" s="153"/>
       <c r="F53" s="20"/>
       <c r="G53" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="H53" s="161">
+      <c r="H53" s="162">
         <f>Resultat!D16</f>
         <v>2326.2443438914029</v>
       </c>
-      <c r="I53" s="152"/>
+      <c r="I53" s="153"/>
     </row>
     <row r="54" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A54" s="19"/>
       <c r="B54" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="C54" s="160">
+      <c r="C54" s="161">
         <f>Resultat!C14</f>
         <v>10726244.343891403</v>
       </c>
-      <c r="D54" s="152"/>
-      <c r="E54" s="152"/>
+      <c r="D54" s="153"/>
+      <c r="E54" s="153"/>
       <c r="F54" s="20"/>
       <c r="G54" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="H54" s="162">
+      <c r="H54" s="163">
         <f>Resultat!C16</f>
         <v>2145.2488687782807</v>
       </c>
-      <c r="I54" s="152"/>
+      <c r="I54" s="153"/>
     </row>
     <row r="55" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A55" s="19"/>
       <c r="B55" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="C55" s="160">
+      <c r="C55" s="161">
         <f>Resultat!E14</f>
         <v>12536199.095022624</v>
       </c>
-      <c r="D55" s="152"/>
-      <c r="E55" s="152"/>
+      <c r="D55" s="153"/>
+      <c r="E55" s="153"/>
       <c r="F55" s="20"/>
       <c r="G55" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="H55" s="162">
+      <c r="H55" s="163">
         <f>Resultat!E16</f>
         <v>2507.2398190045251</v>
       </c>
-      <c r="I55" s="152"/>
+      <c r="I55" s="153"/>
     </row>
     <row r="56" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A56" s="19"/>
       <c r="B56" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="C56" s="171">
+      <c r="C56" s="172">
         <f>Indata!C11</f>
         <v>0</v>
       </c>
-      <c r="D56" s="152"/>
-      <c r="E56" s="152"/>
+      <c r="D56" s="153"/>
+      <c r="E56" s="153"/>
       <c r="F56" s="20"/>
       <c r="G56" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="H56" s="162">
+      <c r="H56" s="163">
         <f>Indata!C41</f>
         <v>0</v>
       </c>
-      <c r="I56" s="152"/>
+      <c r="I56" s="153"/>
     </row>
     <row r="57" spans="1:9" ht="15.95" customHeight="1">
       <c r="A57" s="19"/>
@@ -10700,42 +10639,42 @@
       <c r="B59" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C59" s="173">
+      <c r="C59" s="174">
         <f>Indata!C62</f>
         <v>0.04</v>
       </c>
-      <c r="D59" s="152"/>
-      <c r="E59" s="152"/>
+      <c r="D59" s="153"/>
+      <c r="E59" s="153"/>
       <c r="F59" s="20"/>
       <c r="G59" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="H59" s="171">
+      <c r="H59" s="172">
         <f>Indata!C64</f>
         <v>0.37</v>
       </c>
-      <c r="I59" s="152"/>
+      <c r="I59" s="153"/>
     </row>
     <row r="60" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A60" s="19"/>
       <c r="B60" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="C60" s="173">
+      <c r="C60" s="174">
         <f>Indata!C63</f>
         <v>0.02</v>
       </c>
-      <c r="D60" s="152"/>
-      <c r="E60" s="152"/>
+      <c r="D60" s="153"/>
+      <c r="E60" s="153"/>
       <c r="F60" s="20"/>
       <c r="G60" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="H60" s="173">
+      <c r="H60" s="174">
         <f>Indata!C65</f>
         <v>6.3E-2</v>
       </c>
-      <c r="I60" s="152"/>
+      <c r="I60" s="153"/>
     </row>
     <row r="61" spans="1:9" ht="15.95" customHeight="1">
       <c r="A61" s="19"/>
@@ -10766,11 +10705,11 @@
       <c r="B63" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="C63" s="178">
+      <c r="C63" s="179">
         <f>Lönsamhetskontroll!C45</f>
         <v>7.6451715426456346E-2</v>
       </c>
-      <c r="D63" s="152"/>
+      <c r="D63" s="153"/>
       <c r="E63" s="37" t="str">
         <f>"Krav "&amp;ROUND(Indata!C65*100,1)&amp;" %"</f>
         <v>Krav 6,3 %</v>
@@ -10779,93 +10718,93 @@
       <c r="G63" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="H63" s="170">
+      <c r="H63" s="171">
         <f>Lönsamhetskontroll!C47</f>
         <v>1.3451715426456345E-2</v>
       </c>
-      <c r="I63" s="152"/>
+      <c r="I63" s="153"/>
     </row>
     <row r="64" spans="1:9" ht="21.95" customHeight="1">
       <c r="A64" s="19"/>
       <c r="B64" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="C64" s="165">
+      <c r="C64" s="166">
         <f>Lönsamhetskontroll!C9</f>
         <v>0</v>
       </c>
-      <c r="D64" s="152"/>
-      <c r="E64" s="152"/>
+      <c r="D64" s="153"/>
+      <c r="E64" s="153"/>
       <c r="F64" s="20"/>
       <c r="G64" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="H64" s="177" t="s">
+      <c r="H64" s="178" t="s">
         <v>95</v>
       </c>
-      <c r="I64" s="152"/>
+      <c r="I64" s="153"/>
     </row>
     <row r="65" spans="1:9" ht="21.95" customHeight="1">
       <c r="A65" s="19"/>
       <c r="B65" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="C65" s="165">
+      <c r="C65" s="166">
         <f>Lönsamhetskontroll!C30</f>
         <v>155869728.29851523</v>
       </c>
-      <c r="D65" s="152"/>
-      <c r="E65" s="152"/>
+      <c r="D65" s="153"/>
+      <c r="E65" s="153"/>
       <c r="F65" s="20"/>
       <c r="G65" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="H65" s="177" t="s">
+      <c r="H65" s="178" t="s">
         <v>97</v>
       </c>
-      <c r="I65" s="152"/>
+      <c r="I65" s="153"/>
     </row>
     <row r="66" spans="1:9" ht="21.95" customHeight="1">
       <c r="A66" s="19"/>
       <c r="B66" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="C66" s="165">
+      <c r="C66" s="166">
         <f>Lönsamhetskontroll!C29</f>
         <v>235869728.29851523</v>
       </c>
-      <c r="D66" s="152"/>
-      <c r="E66" s="152"/>
+      <c r="D66" s="153"/>
+      <c r="E66" s="153"/>
       <c r="F66" s="20"/>
       <c r="G66" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="H66" s="165">
+      <c r="H66" s="166">
         <f>Lönsamhetskontroll!C27</f>
         <v>80000000</v>
       </c>
-      <c r="I66" s="152"/>
+      <c r="I66" s="153"/>
     </row>
     <row r="67" spans="1:9" ht="21.95" customHeight="1">
       <c r="A67" s="19"/>
       <c r="B67" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="C67" s="160">
+      <c r="C67" s="161">
         <f>Resultat!D14</f>
         <v>11631221.719457014</v>
       </c>
-      <c r="D67" s="152"/>
-      <c r="E67" s="152"/>
+      <c r="D67" s="153"/>
+      <c r="E67" s="153"/>
       <c r="F67" s="20"/>
       <c r="G67" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="H67" s="162">
+      <c r="H67" s="163">
         <f>Resultat!D16</f>
         <v>2326.2443438914029</v>
       </c>
-      <c r="I67" s="152"/>
+      <c r="I67" s="153"/>
     </row>
     <row r="68" spans="1:9" ht="15.95" customHeight="1">
       <c r="A68" s="19"/>
@@ -10896,12 +10835,12 @@
       <c r="B70" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C70" s="165">
+      <c r="C70" s="166">
         <f>Lönsamhetskontroll!C27</f>
         <v>80000000</v>
       </c>
-      <c r="D70" s="152"/>
-      <c r="E70" s="152"/>
+      <c r="D70" s="153"/>
+      <c r="E70" s="153"/>
       <c r="F70" s="20"/>
       <c r="G70" s="20"/>
       <c r="H70" s="20"/>
@@ -10912,12 +10851,12 @@
       <c r="B71" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="C71" s="165">
+      <c r="C71" s="166">
         <f>Lönsamhetskontroll!C29</f>
         <v>235869728.29851523</v>
       </c>
-      <c r="D71" s="152"/>
-      <c r="E71" s="152"/>
+      <c r="D71" s="153"/>
+      <c r="E71" s="153"/>
       <c r="F71" s="20"/>
       <c r="G71" s="20"/>
       <c r="H71" s="20"/>
@@ -10928,12 +10867,12 @@
       <c r="B72" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="C72" s="180">
+      <c r="C72" s="181">
         <f>Lönsamhetskontroll!C30</f>
         <v>155869728.29851523</v>
       </c>
-      <c r="D72" s="152"/>
-      <c r="E72" s="152"/>
+      <c r="D72" s="153"/>
+      <c r="E72" s="153"/>
       <c r="F72" s="20"/>
       <c r="G72" s="20"/>
       <c r="H72" s="20"/>
@@ -10944,12 +10883,12 @@
       <c r="B73" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="C73" s="184" t="str">
+      <c r="C73" s="185" t="str">
         <f>IF(Indata!D80=0,"Neutral (extern yield rakt av)",IF(Indata!D80&gt;0,"+","")&amp;ROUND(Indata!D80*100,2)&amp;" pp · justerad yield "&amp;ROUND(Indata!D81*100,2)&amp;" %")</f>
         <v>Neutral (extern yield rakt av)</v>
       </c>
-      <c r="D73" s="152"/>
-      <c r="E73" s="152"/>
+      <c r="D73" s="153"/>
+      <c r="E73" s="153"/>
       <c r="F73" s="20"/>
       <c r="G73" s="20"/>
       <c r="H73" s="20"/>
@@ -10984,45 +10923,45 @@
       <c r="B76" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="C76" s="176"/>
-      <c r="D76" s="164"/>
-      <c r="E76" s="164"/>
+      <c r="C76" s="177"/>
+      <c r="D76" s="165"/>
+      <c r="E76" s="165"/>
       <c r="F76" s="20"/>
       <c r="G76" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="H76" s="176"/>
-      <c r="I76" s="164"/>
+      <c r="H76" s="177"/>
+      <c r="I76" s="165"/>
     </row>
     <row r="77" spans="1:9" ht="26.1" customHeight="1">
       <c r="A77" s="19"/>
       <c r="B77" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="C77" s="176"/>
-      <c r="D77" s="164"/>
-      <c r="E77" s="164"/>
+      <c r="C77" s="177"/>
+      <c r="D77" s="165"/>
+      <c r="E77" s="165"/>
       <c r="F77" s="20"/>
       <c r="G77" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="H77" s="176"/>
-      <c r="I77" s="164"/>
+      <c r="H77" s="177"/>
+      <c r="I77" s="165"/>
     </row>
     <row r="78" spans="1:9" ht="32.1" customHeight="1">
       <c r="A78" s="19"/>
       <c r="B78" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="C78" s="163"/>
-      <c r="D78" s="164"/>
-      <c r="E78" s="164"/>
+      <c r="C78" s="164"/>
+      <c r="D78" s="165"/>
+      <c r="E78" s="165"/>
       <c r="F78" s="20"/>
       <c r="G78" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="H78" s="163"/>
-      <c r="I78" s="164"/>
+      <c r="H78" s="164"/>
+      <c r="I78" s="165"/>
     </row>
     <row r="79" spans="1:9" ht="16.5" customHeight="1">
       <c r="A79" s="19"/>
@@ -11080,10 +11019,10 @@
       <c r="E83" s="22"/>
       <c r="F83" s="22"/>
       <c r="G83" s="22"/>
-      <c r="H83" s="174" t="s">
+      <c r="H83" s="175" t="s">
         <v>109</v>
       </c>
-      <c r="I83" s="175"/>
+      <c r="I83" s="176"/>
     </row>
     <row r="84" spans="1:9" ht="21.95" customHeight="1">
       <c r="A84" s="19"/>
@@ -11095,10 +11034,10 @@
       <c r="E84" s="20"/>
       <c r="F84" s="20"/>
       <c r="G84" s="20"/>
-      <c r="H84" s="177" t="s">
+      <c r="H84" s="178" t="s">
         <v>111</v>
       </c>
-      <c r="I84" s="152"/>
+      <c r="I84" s="153"/>
     </row>
     <row r="85" spans="1:9" ht="21.95" customHeight="1">
       <c r="A85" s="19"/>
@@ -11110,10 +11049,10 @@
       <c r="E85" s="20"/>
       <c r="F85" s="20"/>
       <c r="G85" s="20"/>
-      <c r="H85" s="177" t="s">
+      <c r="H85" s="178" t="s">
         <v>113</v>
       </c>
-      <c r="I85" s="152"/>
+      <c r="I85" s="153"/>
     </row>
     <row r="86" spans="1:9" ht="21.95" customHeight="1">
       <c r="A86" s="19"/>
@@ -11125,10 +11064,10 @@
       <c r="E86" s="20"/>
       <c r="F86" s="20"/>
       <c r="G86" s="20"/>
-      <c r="H86" s="177" t="s">
+      <c r="H86" s="178" t="s">
         <v>115</v>
       </c>
-      <c r="I86" s="152"/>
+      <c r="I86" s="153"/>
     </row>
     <row r="87" spans="1:9" ht="21.95" customHeight="1">
       <c r="A87" s="19"/>
@@ -11140,10 +11079,10 @@
       <c r="E87" s="20"/>
       <c r="F87" s="20"/>
       <c r="G87" s="20"/>
-      <c r="H87" s="177" t="s">
+      <c r="H87" s="178" t="s">
         <v>117</v>
       </c>
-      <c r="I87" s="152"/>
+      <c r="I87" s="153"/>
     </row>
     <row r="88" spans="1:9" ht="21.95" customHeight="1">
       <c r="A88" s="19"/>
@@ -11155,10 +11094,10 @@
       <c r="E88" s="20"/>
       <c r="F88" s="20"/>
       <c r="G88" s="20"/>
-      <c r="H88" s="177" t="s">
+      <c r="H88" s="178" t="s">
         <v>119</v>
       </c>
-      <c r="I88" s="152"/>
+      <c r="I88" s="153"/>
     </row>
     <row r="89" spans="1:9" ht="21.95" customHeight="1">
       <c r="A89" s="19"/>
@@ -11170,10 +11109,10 @@
       <c r="E89" s="20"/>
       <c r="F89" s="20"/>
       <c r="G89" s="20"/>
-      <c r="H89" s="177" t="s">
+      <c r="H89" s="178" t="s">
         <v>121</v>
       </c>
-      <c r="I89" s="152"/>
+      <c r="I89" s="153"/>
     </row>
     <row r="90" spans="1:9" ht="21.95" customHeight="1">
       <c r="A90" s="19"/>
@@ -11185,10 +11124,10 @@
       <c r="E90" s="20"/>
       <c r="F90" s="20"/>
       <c r="G90" s="20"/>
-      <c r="H90" s="177" t="s">
+      <c r="H90" s="178" t="s">
         <v>123</v>
       </c>
-      <c r="I90" s="152"/>
+      <c r="I90" s="153"/>
     </row>
     <row r="91" spans="1:9" ht="27.95" customHeight="1">
       <c r="A91" s="19"/>
@@ -11203,16 +11142,16 @@
     </row>
     <row r="92" spans="1:9" ht="16.5" customHeight="1">
       <c r="A92" s="19"/>
-      <c r="B92" s="183" t="s">
+      <c r="B92" s="184" t="s">
         <v>124</v>
       </c>
-      <c r="C92" s="152"/>
-      <c r="D92" s="152"/>
-      <c r="E92" s="152"/>
-      <c r="F92" s="152"/>
-      <c r="G92" s="152"/>
-      <c r="H92" s="152"/>
-      <c r="I92" s="152"/>
+      <c r="C92" s="153"/>
+      <c r="D92" s="153"/>
+      <c r="E92" s="153"/>
+      <c r="F92" s="153"/>
+      <c r="G92" s="153"/>
+      <c r="H92" s="153"/>
+      <c r="I92" s="153"/>
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="39"/>
@@ -11375,6 +11314,9 @@
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="45" max="16383" man="1"/>
+  </rowBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -11756,7 +11698,7 @@
       <c r="R14" s="20"/>
     </row>
     <row r="15" spans="1:18" ht="21.95" customHeight="1">
-      <c r="A15" s="189" t="s">
+      <c r="A15" s="190" t="s">
         <v>142</v>
       </c>
       <c r="B15" s="43" t="s">
@@ -11780,7 +11722,7 @@
       <c r="R15" s="24"/>
     </row>
     <row r="16" spans="1:18" ht="15" customHeight="1">
-      <c r="A16" s="190"/>
+      <c r="A16" s="191"/>
       <c r="B16" s="44" t="s">
         <v>26</v>
       </c>
@@ -11808,7 +11750,7 @@
       <c r="R16" s="20"/>
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1">
-      <c r="A17" s="190"/>
+      <c r="A17" s="191"/>
       <c r="B17" s="44" t="s">
         <v>145</v>
       </c>
@@ -11836,7 +11778,7 @@
       <c r="R17" s="20"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1">
-      <c r="A18" s="190"/>
+      <c r="A18" s="191"/>
       <c r="B18" s="44" t="s">
         <v>148</v>
       </c>
@@ -11862,7 +11804,7 @@
       <c r="R18" s="20"/>
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1">
-      <c r="A19" s="190"/>
+      <c r="A19" s="191"/>
       <c r="B19" s="44" t="s">
         <v>74</v>
       </c>
@@ -11891,7 +11833,7 @@
       <c r="R19" s="20"/>
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1">
-      <c r="A20" s="190"/>
+      <c r="A20" s="191"/>
       <c r="B20" s="44" t="s">
         <v>151</v>
       </c>
@@ -11919,7 +11861,7 @@
       <c r="R20" s="20"/>
     </row>
     <row r="21" spans="1:18" ht="15" customHeight="1">
-      <c r="A21" s="190"/>
+      <c r="A21" s="191"/>
       <c r="B21" s="44" t="s">
         <v>154</v>
       </c>
@@ -11947,7 +11889,7 @@
       <c r="R21" s="20"/>
     </row>
     <row r="22" spans="1:18" ht="15" customHeight="1">
-      <c r="A22" s="190"/>
+      <c r="A22" s="191"/>
       <c r="B22" s="44" t="s">
         <v>156</v>
       </c>
@@ -11976,7 +11918,7 @@
       <c r="R22" s="20"/>
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1">
-      <c r="A23" s="190"/>
+      <c r="A23" s="191"/>
       <c r="B23" s="44" t="s">
         <v>157</v>
       </c>
@@ -12002,7 +11944,7 @@
       <c r="R23" s="20"/>
     </row>
     <row r="24" spans="1:18" ht="21.95" customHeight="1">
-      <c r="A24" s="189" t="s">
+      <c r="A24" s="190" t="s">
         <v>160</v>
       </c>
       <c r="B24" s="43" t="s">
@@ -12026,7 +11968,7 @@
       <c r="R24" s="24"/>
     </row>
     <row r="25" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="190"/>
+      <c r="A25" s="191"/>
       <c r="B25" s="28" t="s">
         <v>162</v>
       </c>
@@ -12080,7 +12022,7 @@
       </c>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1">
-      <c r="A26" s="190"/>
+      <c r="A26" s="191"/>
       <c r="B26" s="44" t="s">
         <v>178</v>
       </c>
@@ -12135,7 +12077,7 @@
       </c>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1">
-      <c r="A27" s="190"/>
+      <c r="A27" s="191"/>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
       <c r="D27" s="51"/>
@@ -12168,7 +12110,7 @@
       </c>
     </row>
     <row r="28" spans="1:18" ht="15" customHeight="1">
-      <c r="A28" s="190"/>
+      <c r="A28" s="191"/>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
       <c r="D28" s="51"/>
@@ -12201,7 +12143,7 @@
       </c>
     </row>
     <row r="29" spans="1:18" ht="15" customHeight="1">
-      <c r="A29" s="190"/>
+      <c r="A29" s="191"/>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
       <c r="D29" s="51"/>
@@ -12234,7 +12176,7 @@
       </c>
     </row>
     <row r="30" spans="1:18" ht="15" customHeight="1">
-      <c r="A30" s="190"/>
+      <c r="A30" s="191"/>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
       <c r="D30" s="51"/>
@@ -12267,7 +12209,7 @@
       </c>
     </row>
     <row r="31" spans="1:18" ht="24" customHeight="1">
-      <c r="A31" s="190"/>
+      <c r="A31" s="191"/>
       <c r="B31" s="58" t="s">
         <v>180</v>
       </c>
@@ -12301,29 +12243,29 @@
       </c>
     </row>
     <row r="32" spans="1:18" ht="15" customHeight="1">
-      <c r="A32" s="190"/>
-      <c r="B32" s="188" t="s">
+      <c r="A32" s="191"/>
+      <c r="B32" s="189" t="s">
         <v>181</v>
       </c>
-      <c r="C32" s="152"/>
-      <c r="D32" s="152"/>
-      <c r="E32" s="152"/>
-      <c r="F32" s="152"/>
-      <c r="G32" s="152"/>
-      <c r="H32" s="152"/>
-      <c r="I32" s="152"/>
-      <c r="J32" s="152"/>
-      <c r="K32" s="152"/>
-      <c r="L32" s="152"/>
-      <c r="M32" s="152"/>
-      <c r="N32" s="152"/>
-      <c r="O32" s="152"/>
-      <c r="P32" s="152"/>
-      <c r="Q32" s="152"/>
-      <c r="R32" s="152"/>
+      <c r="C32" s="153"/>
+      <c r="D32" s="153"/>
+      <c r="E32" s="153"/>
+      <c r="F32" s="153"/>
+      <c r="G32" s="153"/>
+      <c r="H32" s="153"/>
+      <c r="I32" s="153"/>
+      <c r="J32" s="153"/>
+      <c r="K32" s="153"/>
+      <c r="L32" s="153"/>
+      <c r="M32" s="153"/>
+      <c r="N32" s="153"/>
+      <c r="O32" s="153"/>
+      <c r="P32" s="153"/>
+      <c r="Q32" s="153"/>
+      <c r="R32" s="153"/>
     </row>
     <row r="33" spans="1:18" ht="16.5" customHeight="1">
-      <c r="A33" s="190"/>
+      <c r="A33" s="191"/>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
       <c r="D33" s="20"/>
@@ -12343,7 +12285,7 @@
       <c r="R33" s="20"/>
     </row>
     <row r="34" spans="1:18" ht="21.95" customHeight="1">
-      <c r="A34" s="189" t="s">
+      <c r="A34" s="190" t="s">
         <v>182</v>
       </c>
       <c r="B34" s="43" t="s">
@@ -12367,7 +12309,7 @@
       <c r="R34" s="24"/>
     </row>
     <row r="35" spans="1:18" ht="42" customHeight="1">
-      <c r="A35" s="190"/>
+      <c r="A35" s="191"/>
       <c r="B35" s="28" t="s">
         <v>184</v>
       </c>
@@ -12397,7 +12339,7 @@
       <c r="R35" s="20"/>
     </row>
     <row r="36" spans="1:18" ht="15" customHeight="1">
-      <c r="A36" s="190"/>
+      <c r="A36" s="191"/>
       <c r="B36" s="44" t="s">
         <v>187</v>
       </c>
@@ -12427,7 +12369,7 @@
       <c r="R36" s="20"/>
     </row>
     <row r="37" spans="1:18" ht="15" customHeight="1">
-      <c r="A37" s="190"/>
+      <c r="A37" s="191"/>
       <c r="B37" s="44" t="s">
         <v>188</v>
       </c>
@@ -12457,7 +12399,7 @@
       <c r="R37" s="20"/>
     </row>
     <row r="38" spans="1:18" ht="15" customHeight="1">
-      <c r="A38" s="190"/>
+      <c r="A38" s="191"/>
       <c r="B38" s="44" t="s">
         <v>189</v>
       </c>
@@ -12487,7 +12429,7 @@
       <c r="R38" s="20"/>
     </row>
     <row r="39" spans="1:18" ht="15" customHeight="1">
-      <c r="A39" s="190"/>
+      <c r="A39" s="191"/>
       <c r="B39" s="44" t="s">
         <v>190</v>
       </c>
@@ -12517,7 +12459,7 @@
       <c r="R39" s="20"/>
     </row>
     <row r="40" spans="1:18" ht="15" customHeight="1">
-      <c r="A40" s="190"/>
+      <c r="A40" s="191"/>
       <c r="B40" s="44" t="s">
         <v>191</v>
       </c>
@@ -12547,7 +12489,7 @@
       <c r="R40" s="20"/>
     </row>
     <row r="41" spans="1:18" ht="24" customHeight="1">
-      <c r="A41" s="190"/>
+      <c r="A41" s="191"/>
       <c r="B41" s="58" t="s">
         <v>192</v>
       </c>
@@ -12575,7 +12517,7 @@
       <c r="R41" s="20"/>
     </row>
     <row r="42" spans="1:18" ht="16.5" customHeight="1">
-      <c r="A42" s="190"/>
+      <c r="A42" s="191"/>
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
       <c r="D42" s="20"/>
@@ -12595,7 +12537,7 @@
       <c r="R42" s="20"/>
     </row>
     <row r="43" spans="1:18" ht="21.95" customHeight="1">
-      <c r="A43" s="189" t="s">
+      <c r="A43" s="190" t="s">
         <v>193</v>
       </c>
       <c r="B43" s="43" t="s">
@@ -12619,7 +12561,7 @@
       <c r="R43" s="24"/>
     </row>
     <row r="44" spans="1:18" ht="15" customHeight="1">
-      <c r="A44" s="190"/>
+      <c r="A44" s="191"/>
       <c r="B44" s="63" t="s">
         <v>50</v>
       </c>
@@ -12649,7 +12591,7 @@
       <c r="R44" s="20"/>
     </row>
     <row r="45" spans="1:18" ht="15" customHeight="1">
-      <c r="A45" s="190"/>
+      <c r="A45" s="191"/>
       <c r="B45" s="65"/>
       <c r="C45" s="65"/>
       <c r="D45" s="66"/>
@@ -12672,7 +12614,7 @@
       <c r="R45" s="20"/>
     </row>
     <row r="46" spans="1:18" ht="15" customHeight="1">
-      <c r="A46" s="190"/>
+      <c r="A46" s="191"/>
       <c r="B46" s="65"/>
       <c r="C46" s="65"/>
       <c r="D46" s="66"/>
@@ -12695,7 +12637,7 @@
       <c r="R46" s="20"/>
     </row>
     <row r="47" spans="1:18" ht="15" customHeight="1">
-      <c r="A47" s="190"/>
+      <c r="A47" s="191"/>
       <c r="B47" s="65"/>
       <c r="C47" s="65"/>
       <c r="D47" s="66"/>
@@ -12718,7 +12660,7 @@
       <c r="R47" s="20"/>
     </row>
     <row r="48" spans="1:18" ht="15" customHeight="1">
-      <c r="A48" s="190"/>
+      <c r="A48" s="191"/>
       <c r="B48" s="65"/>
       <c r="C48" s="65"/>
       <c r="D48" s="66"/>
@@ -12741,7 +12683,7 @@
       <c r="R48" s="20"/>
     </row>
     <row r="49" spans="1:18" ht="15" customHeight="1">
-      <c r="A49" s="190"/>
+      <c r="A49" s="191"/>
       <c r="B49" s="65"/>
       <c r="C49" s="65"/>
       <c r="D49" s="66"/>
@@ -12764,7 +12706,7 @@
       <c r="R49" s="20"/>
     </row>
     <row r="50" spans="1:18" ht="15" customHeight="1">
-      <c r="A50" s="190"/>
+      <c r="A50" s="191"/>
       <c r="B50" s="65"/>
       <c r="C50" s="65"/>
       <c r="D50" s="66"/>
@@ -12787,7 +12729,7 @@
       <c r="R50" s="20"/>
     </row>
     <row r="51" spans="1:18" ht="16.5" customHeight="1">
-      <c r="A51" s="190"/>
+      <c r="A51" s="191"/>
       <c r="B51" s="20"/>
       <c r="C51" s="20"/>
       <c r="D51" s="20"/>
@@ -12807,7 +12749,7 @@
       <c r="R51" s="20"/>
     </row>
     <row r="52" spans="1:18" ht="21.95" customHeight="1">
-      <c r="A52" s="189" t="s">
+      <c r="A52" s="190" t="s">
         <v>196</v>
       </c>
       <c r="B52" s="43" t="s">
@@ -12831,7 +12773,7 @@
       <c r="R52" s="24"/>
     </row>
     <row r="53" spans="1:18" ht="15" customHeight="1">
-      <c r="A53" s="190"/>
+      <c r="A53" s="191"/>
       <c r="B53" s="44" t="s">
         <v>198</v>
       </c>
@@ -12859,7 +12801,7 @@
       <c r="R53" s="20"/>
     </row>
     <row r="54" spans="1:18" ht="15" customHeight="1">
-      <c r="A54" s="190"/>
+      <c r="A54" s="191"/>
       <c r="B54" s="44" t="s">
         <v>200</v>
       </c>
@@ -12885,7 +12827,7 @@
       <c r="R54" s="20"/>
     </row>
     <row r="55" spans="1:18" ht="15" customHeight="1">
-      <c r="A55" s="190"/>
+      <c r="A55" s="191"/>
       <c r="B55" s="44" t="s">
         <v>202</v>
       </c>
@@ -12913,7 +12855,7 @@
       <c r="R55" s="20"/>
     </row>
     <row r="56" spans="1:18" ht="15" customHeight="1">
-      <c r="A56" s="190"/>
+      <c r="A56" s="191"/>
       <c r="B56" s="44" t="s">
         <v>204</v>
       </c>
@@ -12941,7 +12883,7 @@
       <c r="R56" s="20"/>
     </row>
     <row r="57" spans="1:18" ht="15" customHeight="1">
-      <c r="A57" s="190"/>
+      <c r="A57" s="191"/>
       <c r="B57" s="44" t="s">
         <v>207</v>
       </c>
@@ -12969,7 +12911,7 @@
       <c r="R57" s="20"/>
     </row>
     <row r="58" spans="1:18" ht="15" customHeight="1">
-      <c r="A58" s="190"/>
+      <c r="A58" s="191"/>
       <c r="B58" s="44" t="s">
         <v>209</v>
       </c>
@@ -12997,7 +12939,7 @@
       <c r="R58" s="20"/>
     </row>
     <row r="59" spans="1:18" ht="16.5" customHeight="1">
-      <c r="A59" s="190"/>
+      <c r="A59" s="191"/>
       <c r="B59" s="20"/>
       <c r="C59" s="20"/>
       <c r="D59" s="20"/>
@@ -13017,7 +12959,7 @@
       <c r="R59" s="20"/>
     </row>
     <row r="60" spans="1:18" ht="21.95" customHeight="1">
-      <c r="A60" s="189" t="s">
+      <c r="A60" s="190" t="s">
         <v>211</v>
       </c>
       <c r="B60" s="43" t="s">
@@ -13041,7 +12983,7 @@
       <c r="R60" s="24"/>
     </row>
     <row r="61" spans="1:18" ht="15" customHeight="1">
-      <c r="A61" s="190"/>
+      <c r="A61" s="191"/>
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -13067,7 +13009,7 @@
       <c r="R61" s="20"/>
     </row>
     <row r="62" spans="1:18" ht="15" customHeight="1">
-      <c r="A62" s="190"/>
+      <c r="A62" s="191"/>
       <c r="B62" s="44" t="s">
         <v>88</v>
       </c>
@@ -13093,7 +13035,7 @@
       <c r="R62" s="20"/>
     </row>
     <row r="63" spans="1:18" ht="15" customHeight="1">
-      <c r="A63" s="190"/>
+      <c r="A63" s="191"/>
       <c r="B63" s="44" t="s">
         <v>89</v>
       </c>
@@ -13119,7 +13061,7 @@
       <c r="R63" s="20"/>
     </row>
     <row r="64" spans="1:18" ht="15" customHeight="1">
-      <c r="A64" s="190"/>
+      <c r="A64" s="191"/>
       <c r="B64" s="44" t="s">
         <v>27</v>
       </c>
@@ -13145,7 +13087,7 @@
       <c r="R64" s="20"/>
     </row>
     <row r="65" spans="1:18" ht="15" customHeight="1">
-      <c r="A65" s="190"/>
+      <c r="A65" s="191"/>
       <c r="B65" s="44" t="s">
         <v>218</v>
       </c>
@@ -13171,7 +13113,7 @@
       <c r="R65" s="20"/>
     </row>
     <row r="66" spans="1:18" ht="16.5" customHeight="1">
-      <c r="A66" s="190"/>
+      <c r="A66" s="191"/>
       <c r="B66" s="20"/>
       <c r="C66" s="20"/>
       <c r="D66" s="20"/>
@@ -13259,7 +13201,7 @@
       <c r="R69" s="20"/>
     </row>
     <row r="70" spans="1:18" ht="21.95" customHeight="1">
-      <c r="A70" s="189" t="s">
+      <c r="A70" s="190" t="s">
         <v>223</v>
       </c>
       <c r="B70" s="43" t="s">
@@ -13283,29 +13225,29 @@
       <c r="R70" s="24"/>
     </row>
     <row r="71" spans="1:18" ht="36" customHeight="1">
-      <c r="A71" s="190"/>
-      <c r="B71" s="192" t="s">
+      <c r="A71" s="191"/>
+      <c r="B71" s="193" t="s">
         <v>225</v>
       </c>
-      <c r="C71" s="152"/>
-      <c r="D71" s="152"/>
-      <c r="E71" s="152"/>
-      <c r="F71" s="152"/>
-      <c r="G71" s="152"/>
-      <c r="H71" s="152"/>
-      <c r="I71" s="152"/>
-      <c r="J71" s="152"/>
-      <c r="K71" s="152"/>
-      <c r="L71" s="152"/>
-      <c r="M71" s="152"/>
-      <c r="N71" s="152"/>
-      <c r="O71" s="152"/>
-      <c r="P71" s="152"/>
-      <c r="Q71" s="152"/>
-      <c r="R71" s="152"/>
+      <c r="C71" s="153"/>
+      <c r="D71" s="153"/>
+      <c r="E71" s="153"/>
+      <c r="F71" s="153"/>
+      <c r="G71" s="153"/>
+      <c r="H71" s="153"/>
+      <c r="I71" s="153"/>
+      <c r="J71" s="153"/>
+      <c r="K71" s="153"/>
+      <c r="L71" s="153"/>
+      <c r="M71" s="153"/>
+      <c r="N71" s="153"/>
+      <c r="O71" s="153"/>
+      <c r="P71" s="153"/>
+      <c r="Q71" s="153"/>
+      <c r="R71" s="153"/>
     </row>
     <row r="72" spans="1:18" ht="27.95" customHeight="1">
-      <c r="A72" s="190"/>
+      <c r="A72" s="191"/>
       <c r="B72" s="38" t="s">
         <v>226</v>
       </c>
@@ -13314,48 +13256,48 @@
         <v>1</v>
       </c>
       <c r="D72" s="20"/>
-      <c r="E72" s="192" t="str">
+      <c r="E72" s="193" t="str">
         <f>IF(C72&lt;0.2,"Befintlig fastighet — extern värdering fångar objektet, justering ej rekommenderad",IF(C72&lt;0.6,"Större ombyggnad — värderingen är delvis pre-investering, kalibrering kan vara motiverad","Nybyggnation/motsvarande omfattning — kalibrera mot jämförelseobjekt"))</f>
         <v>Nybyggnation/motsvarande omfattning — kalibrera mot jämförelseobjekt</v>
       </c>
-      <c r="F72" s="152"/>
-      <c r="G72" s="152"/>
-      <c r="H72" s="152"/>
-      <c r="I72" s="152"/>
-      <c r="J72" s="152"/>
-      <c r="K72" s="152"/>
-      <c r="L72" s="152"/>
-      <c r="M72" s="152"/>
-      <c r="N72" s="152"/>
-      <c r="O72" s="152"/>
-      <c r="P72" s="152"/>
-      <c r="Q72" s="152"/>
-      <c r="R72" s="152"/>
+      <c r="F72" s="153"/>
+      <c r="G72" s="153"/>
+      <c r="H72" s="153"/>
+      <c r="I72" s="153"/>
+      <c r="J72" s="153"/>
+      <c r="K72" s="153"/>
+      <c r="L72" s="153"/>
+      <c r="M72" s="153"/>
+      <c r="N72" s="153"/>
+      <c r="O72" s="153"/>
+      <c r="P72" s="153"/>
+      <c r="Q72" s="153"/>
+      <c r="R72" s="153"/>
     </row>
     <row r="73" spans="1:18" ht="18" customHeight="1">
-      <c r="A73" s="190"/>
-      <c r="B73" s="194" t="s">
+      <c r="A73" s="191"/>
+      <c r="B73" s="195" t="s">
         <v>227</v>
       </c>
-      <c r="C73" s="152"/>
-      <c r="D73" s="152"/>
-      <c r="E73" s="152"/>
-      <c r="F73" s="152"/>
-      <c r="G73" s="152"/>
-      <c r="H73" s="152"/>
-      <c r="I73" s="152"/>
-      <c r="J73" s="152"/>
-      <c r="K73" s="152"/>
-      <c r="L73" s="152"/>
-      <c r="M73" s="152"/>
-      <c r="N73" s="152"/>
-      <c r="O73" s="152"/>
-      <c r="P73" s="152"/>
-      <c r="Q73" s="152"/>
-      <c r="R73" s="152"/>
+      <c r="C73" s="153"/>
+      <c r="D73" s="153"/>
+      <c r="E73" s="153"/>
+      <c r="F73" s="153"/>
+      <c r="G73" s="153"/>
+      <c r="H73" s="153"/>
+      <c r="I73" s="153"/>
+      <c r="J73" s="153"/>
+      <c r="K73" s="153"/>
+      <c r="L73" s="153"/>
+      <c r="M73" s="153"/>
+      <c r="N73" s="153"/>
+      <c r="O73" s="153"/>
+      <c r="P73" s="153"/>
+      <c r="Q73" s="153"/>
+      <c r="R73" s="153"/>
     </row>
     <row r="74" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="190"/>
+      <c r="A74" s="191"/>
       <c r="B74" s="28" t="s">
         <v>228</v>
       </c>
@@ -13365,25 +13307,25 @@
       <c r="D74" s="29" t="s">
         <v>230</v>
       </c>
-      <c r="E74" s="193" t="s">
+      <c r="E74" s="194" t="s">
         <v>231</v>
       </c>
-      <c r="F74" s="175"/>
-      <c r="G74" s="175"/>
-      <c r="H74" s="175"/>
-      <c r="I74" s="175"/>
-      <c r="J74" s="175"/>
-      <c r="K74" s="175"/>
-      <c r="L74" s="175"/>
-      <c r="M74" s="175"/>
-      <c r="N74" s="175"/>
-      <c r="O74" s="175"/>
-      <c r="P74" s="175"/>
-      <c r="Q74" s="175"/>
-      <c r="R74" s="175"/>
+      <c r="F74" s="176"/>
+      <c r="G74" s="176"/>
+      <c r="H74" s="176"/>
+      <c r="I74" s="176"/>
+      <c r="J74" s="176"/>
+      <c r="K74" s="176"/>
+      <c r="L74" s="176"/>
+      <c r="M74" s="176"/>
+      <c r="N74" s="176"/>
+      <c r="O74" s="176"/>
+      <c r="P74" s="176"/>
+      <c r="Q74" s="176"/>
+      <c r="R74" s="176"/>
     </row>
     <row r="75" spans="1:18" ht="21.95" customHeight="1">
-      <c r="A75" s="190"/>
+      <c r="A75" s="191"/>
       <c r="B75" s="38" t="s">
         <v>232</v>
       </c>
@@ -13394,25 +13336,25 @@
         <f>IF(C75="Mycket positivt",-0.005,IF(C75="Något positivt",-0.0025,IF(C75="Något negativt",0.0025,IF(C75="Mycket negativt",0.005,0))))</f>
         <v>0</v>
       </c>
-      <c r="E75" s="191"/>
-      <c r="F75" s="183" t="s">
+      <c r="E75" s="192"/>
+      <c r="F75" s="184" t="s">
         <v>234</v>
       </c>
-      <c r="G75" s="152"/>
-      <c r="H75" s="152"/>
-      <c r="I75" s="152"/>
-      <c r="J75" s="152"/>
-      <c r="K75" s="152"/>
-      <c r="L75" s="152"/>
-      <c r="M75" s="152"/>
-      <c r="N75" s="152"/>
-      <c r="O75" s="152"/>
-      <c r="P75" s="152"/>
-      <c r="Q75" s="152"/>
-      <c r="R75" s="152"/>
+      <c r="G75" s="153"/>
+      <c r="H75" s="153"/>
+      <c r="I75" s="153"/>
+      <c r="J75" s="153"/>
+      <c r="K75" s="153"/>
+      <c r="L75" s="153"/>
+      <c r="M75" s="153"/>
+      <c r="N75" s="153"/>
+      <c r="O75" s="153"/>
+      <c r="P75" s="153"/>
+      <c r="Q75" s="153"/>
+      <c r="R75" s="153"/>
     </row>
     <row r="76" spans="1:18" ht="21.95" customHeight="1">
-      <c r="A76" s="190"/>
+      <c r="A76" s="191"/>
       <c r="B76" s="38" t="s">
         <v>85</v>
       </c>
@@ -13423,25 +13365,25 @@
         <f>IF(C76="Mycket positivt",-0.005,IF(C76="Något positivt",-0.0025,IF(C76="Något negativt",0.0025,IF(C76="Mycket negativt",0.005,0))))</f>
         <v>0</v>
       </c>
-      <c r="E76" s="191"/>
-      <c r="F76" s="183" t="s">
+      <c r="E76" s="192"/>
+      <c r="F76" s="184" t="s">
         <v>235</v>
       </c>
-      <c r="G76" s="152"/>
-      <c r="H76" s="152"/>
-      <c r="I76" s="152"/>
-      <c r="J76" s="152"/>
-      <c r="K76" s="152"/>
-      <c r="L76" s="152"/>
-      <c r="M76" s="152"/>
-      <c r="N76" s="152"/>
-      <c r="O76" s="152"/>
-      <c r="P76" s="152"/>
-      <c r="Q76" s="152"/>
-      <c r="R76" s="152"/>
+      <c r="G76" s="153"/>
+      <c r="H76" s="153"/>
+      <c r="I76" s="153"/>
+      <c r="J76" s="153"/>
+      <c r="K76" s="153"/>
+      <c r="L76" s="153"/>
+      <c r="M76" s="153"/>
+      <c r="N76" s="153"/>
+      <c r="O76" s="153"/>
+      <c r="P76" s="153"/>
+      <c r="Q76" s="153"/>
+      <c r="R76" s="153"/>
     </row>
     <row r="77" spans="1:18" ht="21.95" customHeight="1">
-      <c r="A77" s="190"/>
+      <c r="A77" s="191"/>
       <c r="B77" s="38" t="s">
         <v>236</v>
       </c>
@@ -13452,25 +13394,25 @@
         <f>IF(C77="Mycket positivt",-0.005,IF(C77="Något positivt",-0.0025,IF(C77="Något negativt",0.0025,IF(C77="Mycket negativt",0.005,0))))</f>
         <v>0</v>
       </c>
-      <c r="E77" s="191"/>
-      <c r="F77" s="183" t="s">
+      <c r="E77" s="192"/>
+      <c r="F77" s="184" t="s">
         <v>237</v>
       </c>
-      <c r="G77" s="152"/>
-      <c r="H77" s="152"/>
-      <c r="I77" s="152"/>
-      <c r="J77" s="152"/>
-      <c r="K77" s="152"/>
-      <c r="L77" s="152"/>
-      <c r="M77" s="152"/>
-      <c r="N77" s="152"/>
-      <c r="O77" s="152"/>
-      <c r="P77" s="152"/>
-      <c r="Q77" s="152"/>
-      <c r="R77" s="152"/>
+      <c r="G77" s="153"/>
+      <c r="H77" s="153"/>
+      <c r="I77" s="153"/>
+      <c r="J77" s="153"/>
+      <c r="K77" s="153"/>
+      <c r="L77" s="153"/>
+      <c r="M77" s="153"/>
+      <c r="N77" s="153"/>
+      <c r="O77" s="153"/>
+      <c r="P77" s="153"/>
+      <c r="Q77" s="153"/>
+      <c r="R77" s="153"/>
     </row>
     <row r="78" spans="1:18" ht="21.95" customHeight="1">
-      <c r="A78" s="190"/>
+      <c r="A78" s="191"/>
       <c r="B78" s="38" t="s">
         <v>238</v>
       </c>
@@ -13481,25 +13423,25 @@
         <f>IF(C78="Mycket positivt",-0.005,IF(C78="Något positivt",-0.0025,IF(C78="Något negativt",0.0025,IF(C78="Mycket negativt",0.005,0))))</f>
         <v>0</v>
       </c>
-      <c r="E78" s="191"/>
-      <c r="F78" s="183" t="s">
+      <c r="E78" s="192"/>
+      <c r="F78" s="184" t="s">
         <v>239</v>
       </c>
-      <c r="G78" s="152"/>
-      <c r="H78" s="152"/>
-      <c r="I78" s="152"/>
-      <c r="J78" s="152"/>
-      <c r="K78" s="152"/>
-      <c r="L78" s="152"/>
-      <c r="M78" s="152"/>
-      <c r="N78" s="152"/>
-      <c r="O78" s="152"/>
-      <c r="P78" s="152"/>
-      <c r="Q78" s="152"/>
-      <c r="R78" s="152"/>
+      <c r="G78" s="153"/>
+      <c r="H78" s="153"/>
+      <c r="I78" s="153"/>
+      <c r="J78" s="153"/>
+      <c r="K78" s="153"/>
+      <c r="L78" s="153"/>
+      <c r="M78" s="153"/>
+      <c r="N78" s="153"/>
+      <c r="O78" s="153"/>
+      <c r="P78" s="153"/>
+      <c r="Q78" s="153"/>
+      <c r="R78" s="153"/>
     </row>
     <row r="79" spans="1:18" ht="16.5" customHeight="1">
-      <c r="A79" s="190"/>
+      <c r="A79" s="191"/>
       <c r="B79" s="20"/>
       <c r="C79" s="20"/>
       <c r="D79" s="20"/>
@@ -13519,7 +13461,7 @@
       <c r="R79" s="20"/>
     </row>
     <row r="80" spans="1:18" ht="24" customHeight="1">
-      <c r="A80" s="190"/>
+      <c r="A80" s="191"/>
       <c r="B80" s="32" t="s">
         <v>240</v>
       </c>
@@ -13546,7 +13488,7 @@
       <c r="R80" s="20"/>
     </row>
     <row r="81" spans="1:18" ht="26.1" customHeight="1">
-      <c r="A81" s="190"/>
+      <c r="A81" s="191"/>
       <c r="B81" s="74" t="s">
         <v>242</v>
       </c>
@@ -13555,22 +13497,22 @@
         <f>C6+D80</f>
         <v>0.05</v>
       </c>
-      <c r="E81" s="194" t="s">
+      <c r="E81" s="195" t="s">
         <v>243</v>
       </c>
-      <c r="F81" s="152"/>
-      <c r="G81" s="152"/>
-      <c r="H81" s="152"/>
-      <c r="I81" s="152"/>
-      <c r="J81" s="152"/>
-      <c r="K81" s="152"/>
-      <c r="L81" s="152"/>
-      <c r="M81" s="152"/>
-      <c r="N81" s="152"/>
-      <c r="O81" s="152"/>
-      <c r="P81" s="152"/>
-      <c r="Q81" s="152"/>
-      <c r="R81" s="152"/>
+      <c r="F81" s="153"/>
+      <c r="G81" s="153"/>
+      <c r="H81" s="153"/>
+      <c r="I81" s="153"/>
+      <c r="J81" s="153"/>
+      <c r="K81" s="153"/>
+      <c r="L81" s="153"/>
+      <c r="M81" s="153"/>
+      <c r="N81" s="153"/>
+      <c r="O81" s="153"/>
+      <c r="P81" s="153"/>
+      <c r="Q81" s="153"/>
+      <c r="R81" s="153"/>
     </row>
     <row r="82" spans="1:18">
       <c r="A82" s="39"/>
@@ -14484,12 +14426,12 @@
       <c r="A10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="195" t="s">
+      <c r="B10" s="196" t="s">
         <v>251</v>
       </c>
-      <c r="C10" s="164"/>
-      <c r="D10" s="164"/>
-      <c r="E10" s="164"/>
+      <c r="C10" s="165"/>
+      <c r="D10" s="165"/>
+      <c r="E10" s="165"/>
       <c r="F10" s="24"/>
       <c r="G10" s="24"/>
       <c r="H10" s="20"/>
@@ -14514,24 +14456,14 @@
       <c r="AA10" s="20"/>
       <c r="AB10" s="20"/>
     </row>
-    <row r="11" spans="1:28" ht="30" customHeight="1">
+    <row r="11" spans="1:28" ht="60" customHeight="1">
       <c r="A11" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="196" t="s">
+      <c r="B11" s="197" t="s">
         <v>252</v>
       </c>
-      <c r="C11" s="152"/>
-      <c r="D11" s="152"/>
-      <c r="E11" s="152"/>
-      <c r="F11" s="152"/>
-      <c r="G11" s="152"/>
-      <c r="H11" s="152"/>
-      <c r="I11" s="152"/>
-      <c r="J11" s="152"/>
-      <c r="K11" s="152"/>
-      <c r="L11" s="152"/>
-      <c r="M11" s="152"/>
+      <c r="C11" s="153"/>
       <c r="N11" s="20"/>
       <c r="O11" s="20"/>
       <c r="P11" s="20"/>
@@ -15596,12 +15528,12 @@
     </row>
     <row r="26" spans="1:28" ht="21.95" customHeight="1">
       <c r="A26" s="19"/>
-      <c r="B26" s="195" t="s">
+      <c r="B26" s="196" t="s">
         <v>263</v>
       </c>
-      <c r="C26" s="164"/>
-      <c r="D26" s="164"/>
-      <c r="E26" s="164"/>
+      <c r="C26" s="165"/>
+      <c r="D26" s="165"/>
+      <c r="E26" s="165"/>
       <c r="F26" s="24"/>
       <c r="G26" s="24"/>
       <c r="H26" s="24"/>
@@ -15626,22 +15558,12 @@
       <c r="AA26" s="20"/>
       <c r="AB26" s="20"/>
     </row>
-    <row r="27" spans="1:28" ht="15" customHeight="1">
+    <row r="27" spans="1:28" ht="32.1" customHeight="1">
       <c r="A27" s="19"/>
-      <c r="B27" s="196" t="s">
+      <c r="B27" s="197" t="s">
         <v>264</v>
       </c>
-      <c r="C27" s="152"/>
-      <c r="D27" s="152"/>
-      <c r="E27" s="152"/>
-      <c r="F27" s="152"/>
-      <c r="G27" s="152"/>
-      <c r="H27" s="152"/>
-      <c r="I27" s="152"/>
-      <c r="J27" s="152"/>
-      <c r="K27" s="152"/>
-      <c r="L27" s="152"/>
-      <c r="M27" s="152"/>
+      <c r="C27" s="153"/>
       <c r="N27" s="20"/>
       <c r="O27" s="20"/>
       <c r="P27" s="20"/>
@@ -19956,10 +19878,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B11:M11"/>
-    <mergeCell ref="B27:M27"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" location="'Försättsblad'!A1" display="Försättsblad" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
@@ -19973,7 +19895,7 @@
     <hyperlink ref="A11" location="'Dokumentation'!A1" display="Dokumentation" xr:uid="{00000000-0004-0000-0300-000008000000}"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" fitToWidth="2" fitToHeight="0" orientation="landscape"/>
+  <pageSetup paperSize="9" fitToWidth="2" orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -20395,12 +20317,12 @@
       <c r="A7" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="195" t="s">
+      <c r="B7" s="196" t="s">
         <v>268</v>
       </c>
-      <c r="C7" s="164"/>
-      <c r="D7" s="164"/>
-      <c r="E7" s="164"/>
+      <c r="C7" s="165"/>
+      <c r="D7" s="165"/>
+      <c r="E7" s="165"/>
       <c r="F7" s="24"/>
       <c r="G7" s="24"/>
       <c r="H7" s="24"/>
@@ -20425,24 +20347,14 @@
       <c r="AA7" s="24"/>
       <c r="AB7" s="24"/>
     </row>
-    <row r="8" spans="1:28" ht="30" customHeight="1">
+    <row r="8" spans="1:28" ht="60" customHeight="1">
       <c r="A8" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="196" t="s">
+      <c r="B8" s="197" t="s">
         <v>269</v>
       </c>
-      <c r="C8" s="152"/>
-      <c r="D8" s="152"/>
-      <c r="E8" s="152"/>
-      <c r="F8" s="152"/>
-      <c r="G8" s="152"/>
-      <c r="H8" s="152"/>
-      <c r="I8" s="152"/>
-      <c r="J8" s="152"/>
-      <c r="K8" s="152"/>
-      <c r="L8" s="152"/>
-      <c r="M8" s="152"/>
+      <c r="C8" s="153"/>
       <c r="N8" s="20"/>
       <c r="O8" s="20"/>
       <c r="P8" s="20"/>
@@ -21548,7 +21460,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B8:M8"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="B7:E7"/>
   </mergeCells>
   <hyperlinks>
@@ -21563,7 +21475,7 @@
     <hyperlink ref="A11" location="'Dokumentation'!A1" display="Dokumentation" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" fitToWidth="2" fitToHeight="0" orientation="landscape"/>
+  <pageSetup paperSize="9" fitToWidth="2" orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -21579,7 +21491,7 @@
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="4" width="18" customWidth="1"/>
+    <col min="3" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -21645,13 +21557,13 @@
       <c r="A4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="195" t="s">
+      <c r="B4" s="196" t="s">
         <v>278</v>
       </c>
-      <c r="C4" s="164"/>
-      <c r="D4" s="164"/>
-      <c r="E4" s="164"/>
-      <c r="F4" s="164"/>
+      <c r="C4" s="165"/>
+      <c r="D4" s="165"/>
+      <c r="E4" s="165"/>
+      <c r="F4" s="165"/>
       <c r="G4" s="24"/>
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
@@ -21984,12 +21896,12 @@
       <c r="B18" s="47" t="s">
         <v>288</v>
       </c>
-      <c r="C18" s="197" t="s">
+      <c r="C18" s="198" t="s">
         <v>289</v>
       </c>
-      <c r="D18" s="152"/>
-      <c r="E18" s="152"/>
-      <c r="F18" s="152"/>
+      <c r="D18" s="153"/>
+      <c r="E18" s="153"/>
+      <c r="F18" s="153"/>
       <c r="G18" s="20"/>
       <c r="H18" s="20"/>
       <c r="I18" s="20"/>
@@ -21999,17 +21911,17 @@
       <c r="M18" s="20"/>
       <c r="N18" s="20"/>
     </row>
-    <row r="19" spans="1:14" ht="27.75" customHeight="1">
+    <row r="19" spans="1:14" ht="48" customHeight="1">
       <c r="A19" s="19"/>
       <c r="B19" s="81" t="s">
         <v>290</v>
       </c>
-      <c r="C19" s="198" t="s">
+      <c r="C19" s="199" t="s">
         <v>291</v>
       </c>
-      <c r="D19" s="152"/>
-      <c r="E19" s="152"/>
-      <c r="F19" s="152"/>
+      <c r="D19" s="153"/>
+      <c r="E19" s="153"/>
+      <c r="F19" s="153"/>
       <c r="G19" s="20"/>
       <c r="H19" s="20"/>
       <c r="I19" s="20"/>
@@ -22053,13 +21965,13 @@
     </row>
     <row r="22" spans="1:14" ht="21.95" customHeight="1">
       <c r="A22" s="19"/>
-      <c r="B22" s="195" t="s">
+      <c r="B22" s="196" t="s">
         <v>292</v>
       </c>
-      <c r="C22" s="164"/>
-      <c r="D22" s="164"/>
-      <c r="E22" s="164"/>
-      <c r="F22" s="164"/>
+      <c r="C22" s="165"/>
+      <c r="D22" s="165"/>
+      <c r="E22" s="165"/>
+      <c r="F22" s="165"/>
       <c r="G22" s="24"/>
       <c r="H22" s="20"/>
       <c r="I22" s="20"/>
@@ -22324,13 +22236,13 @@
     </row>
     <row r="33" spans="1:14" ht="21.95" customHeight="1">
       <c r="A33" s="19"/>
-      <c r="B33" s="195" t="s">
+      <c r="B33" s="196" t="s">
         <v>297</v>
       </c>
-      <c r="C33" s="164"/>
-      <c r="D33" s="164"/>
-      <c r="E33" s="164"/>
-      <c r="F33" s="164"/>
+      <c r="C33" s="165"/>
+      <c r="D33" s="165"/>
+      <c r="E33" s="165"/>
+      <c r="F33" s="165"/>
       <c r="G33" s="24"/>
       <c r="H33" s="20"/>
       <c r="I33" s="20"/>
@@ -22342,13 +22254,13 @@
     </row>
     <row r="34" spans="1:14" ht="32.1" customHeight="1">
       <c r="A34" s="19"/>
-      <c r="B34" s="192" t="s">
+      <c r="B34" s="193" t="s">
         <v>298</v>
       </c>
-      <c r="C34" s="152"/>
-      <c r="D34" s="152"/>
-      <c r="E34" s="152"/>
-      <c r="F34" s="152"/>
+      <c r="C34" s="153"/>
+      <c r="D34" s="153"/>
+      <c r="E34" s="153"/>
+      <c r="F34" s="153"/>
       <c r="G34" s="20"/>
       <c r="H34" s="20"/>
       <c r="I34" s="20"/>
@@ -22694,7 +22606,7 @@
     <hyperlink ref="A11" location="'Dokumentation'!A1" display="Dokumentation" xr:uid="{00000000-0004-0000-0500-000008000000}"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -22709,6 +22621,7 @@
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="5" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="8.1" customHeight="1">
@@ -23414,14 +23327,14 @@
       <c r="A4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="195" t="s">
+      <c r="B4" s="196" t="s">
         <v>318</v>
       </c>
-      <c r="C4" s="164"/>
-      <c r="D4" s="164"/>
-      <c r="E4" s="164"/>
-      <c r="F4" s="164"/>
-      <c r="G4" s="164"/>
+      <c r="C4" s="165"/>
+      <c r="D4" s="165"/>
+      <c r="E4" s="165"/>
+      <c r="F4" s="165"/>
+      <c r="G4" s="165"/>
       <c r="H4" s="20"/>
       <c r="I4" s="20"/>
       <c r="J4" s="20"/>
@@ -23709,14 +23622,14 @@
     </row>
     <row r="12" spans="1:30" ht="21.95" customHeight="1">
       <c r="A12" s="19"/>
-      <c r="B12" s="195" t="s">
+      <c r="B12" s="196" t="s">
         <v>323</v>
       </c>
-      <c r="C12" s="164"/>
-      <c r="D12" s="164"/>
-      <c r="E12" s="164"/>
-      <c r="F12" s="164"/>
-      <c r="G12" s="164"/>
+      <c r="C12" s="165"/>
+      <c r="D12" s="165"/>
+      <c r="E12" s="165"/>
+      <c r="F12" s="165"/>
+      <c r="G12" s="165"/>
       <c r="H12" s="20"/>
       <c r="I12" s="20"/>
       <c r="J12" s="20"/>
@@ -24029,14 +23942,14 @@
     </row>
     <row r="21" spans="1:30" ht="21.95" customHeight="1">
       <c r="A21" s="19"/>
-      <c r="B21" s="195" t="s">
+      <c r="B21" s="196" t="s">
         <v>327</v>
       </c>
-      <c r="C21" s="164"/>
-      <c r="D21" s="164"/>
-      <c r="E21" s="164"/>
-      <c r="F21" s="164"/>
-      <c r="G21" s="164"/>
+      <c r="C21" s="165"/>
+      <c r="D21" s="165"/>
+      <c r="E21" s="165"/>
+      <c r="F21" s="165"/>
+      <c r="G21" s="165"/>
       <c r="H21" s="20"/>
       <c r="I21" s="20"/>
       <c r="J21" s="20"/>
@@ -24750,14 +24663,14 @@
     </row>
     <row r="42" spans="1:30" ht="21.95" customHeight="1">
       <c r="A42" s="19"/>
-      <c r="B42" s="195" t="s">
+      <c r="B42" s="196" t="s">
         <v>336</v>
       </c>
-      <c r="C42" s="164"/>
-      <c r="D42" s="164"/>
-      <c r="E42" s="164"/>
-      <c r="F42" s="164"/>
-      <c r="G42" s="164"/>
+      <c r="C42" s="165"/>
+      <c r="D42" s="165"/>
+      <c r="E42" s="165"/>
+      <c r="F42" s="165"/>
+      <c r="G42" s="165"/>
       <c r="H42" s="24"/>
       <c r="I42" s="24"/>
       <c r="J42" s="24"/>
@@ -25103,14 +25016,14 @@
     </row>
     <row r="50" spans="1:30" ht="21.95" customHeight="1">
       <c r="A50" s="19"/>
-      <c r="B50" s="195" t="s">
+      <c r="B50" s="196" t="s">
         <v>340</v>
       </c>
-      <c r="C50" s="164"/>
-      <c r="D50" s="164"/>
-      <c r="E50" s="164"/>
-      <c r="F50" s="164"/>
-      <c r="G50" s="164"/>
+      <c r="C50" s="165"/>
+      <c r="D50" s="165"/>
+      <c r="E50" s="165"/>
+      <c r="F50" s="165"/>
+      <c r="G50" s="165"/>
       <c r="H50" s="20"/>
       <c r="I50" s="20"/>
       <c r="J50" s="20"/>
@@ -25135,17 +25048,17 @@
       <c r="AC50" s="20"/>
       <c r="AD50" s="20"/>
     </row>
-    <row r="51" spans="1:30" ht="30" customHeight="1">
+    <row r="51" spans="1:30" ht="33.950000000000003" customHeight="1">
       <c r="A51" s="19"/>
-      <c r="B51" s="200" t="s">
+      <c r="B51" s="201" t="s">
         <v>341</v>
       </c>
-      <c r="C51" s="152"/>
-      <c r="D51" s="152"/>
-      <c r="E51" s="152"/>
-      <c r="F51" s="152"/>
-      <c r="G51" s="152"/>
-      <c r="H51" s="152"/>
+      <c r="C51" s="153"/>
+      <c r="D51" s="153"/>
+      <c r="E51" s="153"/>
+      <c r="F51" s="153"/>
+      <c r="G51" s="153"/>
+      <c r="H51" s="153"/>
       <c r="I51" s="20"/>
       <c r="J51" s="20"/>
       <c r="K51" s="20"/>
@@ -26478,14 +26391,14 @@
     </row>
     <row r="73" spans="1:30" ht="21.95" customHeight="1">
       <c r="A73" s="19"/>
-      <c r="B73" s="195" t="s">
+      <c r="B73" s="196" t="s">
         <v>355</v>
       </c>
-      <c r="C73" s="164"/>
-      <c r="D73" s="164"/>
-      <c r="E73" s="164"/>
-      <c r="F73" s="164"/>
-      <c r="G73" s="164"/>
+      <c r="C73" s="165"/>
+      <c r="D73" s="165"/>
+      <c r="E73" s="165"/>
+      <c r="F73" s="165"/>
+      <c r="G73" s="165"/>
       <c r="H73" s="20"/>
       <c r="I73" s="20"/>
       <c r="J73" s="20"/>
@@ -26512,14 +26425,14 @@
     </row>
     <row r="74" spans="1:30" ht="32.1" customHeight="1">
       <c r="A74" s="19"/>
-      <c r="B74" s="199" t="s">
+      <c r="B74" s="200" t="s">
         <v>356</v>
       </c>
-      <c r="C74" s="152"/>
-      <c r="D74" s="152"/>
-      <c r="E74" s="152"/>
-      <c r="F74" s="152"/>
-      <c r="G74" s="152"/>
+      <c r="C74" s="153"/>
+      <c r="D74" s="153"/>
+      <c r="E74" s="153"/>
+      <c r="F74" s="153"/>
+      <c r="G74" s="153"/>
       <c r="H74" s="20"/>
       <c r="I74" s="20"/>
       <c r="J74" s="20"/>
@@ -27041,14 +26954,14 @@
     </row>
     <row r="87" spans="1:30" ht="42" customHeight="1">
       <c r="A87" s="19"/>
-      <c r="B87" s="192" t="s">
+      <c r="B87" s="193" t="s">
         <v>367</v>
       </c>
-      <c r="C87" s="152"/>
-      <c r="D87" s="152"/>
-      <c r="E87" s="152"/>
-      <c r="F87" s="152"/>
-      <c r="G87" s="152"/>
+      <c r="C87" s="153"/>
+      <c r="D87" s="153"/>
+      <c r="E87" s="153"/>
+      <c r="F87" s="153"/>
+      <c r="G87" s="153"/>
       <c r="H87" s="20"/>
       <c r="I87" s="20"/>
       <c r="J87" s="20"/>
@@ -27281,10 +27194,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor rgb="FF10313E"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AD238"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -28074,12 +27988,12 @@
     </row>
     <row r="23" spans="1:30" ht="21.95" customHeight="1">
       <c r="A23" s="19"/>
-      <c r="B23" s="195" t="s">
+      <c r="B23" s="196" t="s">
         <v>386</v>
       </c>
-      <c r="C23" s="164"/>
-      <c r="D23" s="164"/>
-      <c r="E23" s="164"/>
+      <c r="C23" s="165"/>
+      <c r="D23" s="165"/>
+      <c r="E23" s="165"/>
       <c r="F23" s="24"/>
       <c r="G23" s="24"/>
       <c r="H23" s="20"/>
@@ -28430,12 +28344,12 @@
     </row>
     <row r="33" spans="1:30" ht="21.95" customHeight="1">
       <c r="A33" s="19"/>
-      <c r="B33" s="195" t="s">
+      <c r="B33" s="196" t="s">
         <v>396</v>
       </c>
-      <c r="C33" s="164"/>
-      <c r="D33" s="164"/>
-      <c r="E33" s="164"/>
+      <c r="C33" s="165"/>
+      <c r="D33" s="165"/>
+      <c r="E33" s="165"/>
       <c r="F33" s="24"/>
       <c r="G33" s="24"/>
       <c r="H33" s="20"/>
@@ -28496,12 +28410,12 @@
     </row>
     <row r="35" spans="1:30" ht="60" customHeight="1">
       <c r="A35" s="19"/>
-      <c r="B35" s="198" t="s">
+      <c r="B35" s="199" t="s">
         <v>397</v>
       </c>
-      <c r="C35" s="152"/>
-      <c r="D35" s="152"/>
-      <c r="E35" s="152"/>
+      <c r="C35" s="153"/>
+      <c r="D35" s="153"/>
+      <c r="E35" s="153"/>
       <c r="F35" s="20"/>
       <c r="G35" s="20"/>
       <c r="H35" s="20"/>
@@ -28562,12 +28476,12 @@
     </row>
     <row r="37" spans="1:30" ht="60" customHeight="1">
       <c r="A37" s="19"/>
-      <c r="B37" s="198" t="s">
+      <c r="B37" s="199" t="s">
         <v>398</v>
       </c>
-      <c r="C37" s="152"/>
-      <c r="D37" s="152"/>
-      <c r="E37" s="152"/>
+      <c r="C37" s="153"/>
+      <c r="D37" s="153"/>
+      <c r="E37" s="153"/>
       <c r="F37" s="20"/>
       <c r="G37" s="20"/>
       <c r="H37" s="20"/>
@@ -28862,18 +28776,18 @@
     </row>
     <row r="46" spans="1:30" ht="21.95" customHeight="1">
       <c r="A46" s="19"/>
-      <c r="B46" s="202" t="s">
+      <c r="B46" s="203" t="s">
         <v>404</v>
       </c>
-      <c r="C46" s="164"/>
-      <c r="D46" s="164"/>
-      <c r="E46" s="164"/>
-      <c r="F46" s="164"/>
-      <c r="G46" s="164"/>
-      <c r="H46" s="164"/>
-      <c r="I46" s="164"/>
-      <c r="J46" s="164"/>
-      <c r="K46" s="164"/>
+      <c r="C46" s="165"/>
+      <c r="D46" s="165"/>
+      <c r="E46" s="165"/>
+      <c r="F46" s="165"/>
+      <c r="G46" s="165"/>
+      <c r="H46" s="165"/>
+      <c r="I46" s="165"/>
+      <c r="J46" s="165"/>
+      <c r="K46" s="165"/>
       <c r="L46" s="20"/>
       <c r="M46" s="20"/>
       <c r="N46" s="20"/>
@@ -28894,20 +28808,20 @@
       <c r="AC46" s="20"/>
       <c r="AD46" s="20"/>
     </row>
-    <row r="47" spans="1:30" ht="15" customHeight="1">
+    <row r="47" spans="1:30" ht="33.950000000000003" customHeight="1" collapsed="1">
       <c r="A47" s="19"/>
-      <c r="B47" s="196" t="s">
+      <c r="B47" s="197" t="s">
         <v>405</v>
       </c>
-      <c r="C47" s="152"/>
-      <c r="D47" s="152"/>
-      <c r="E47" s="152"/>
-      <c r="F47" s="152"/>
-      <c r="G47" s="152"/>
-      <c r="H47" s="152"/>
-      <c r="I47" s="152"/>
-      <c r="J47" s="152"/>
-      <c r="K47" s="152"/>
+      <c r="C47" s="153"/>
+      <c r="D47" s="153"/>
+      <c r="E47" s="153"/>
+      <c r="F47" s="153"/>
+      <c r="G47" s="153"/>
+      <c r="H47" s="153"/>
+      <c r="I47" s="153"/>
+      <c r="J47" s="153"/>
+      <c r="K47" s="153"/>
       <c r="L47" s="20"/>
       <c r="M47" s="20"/>
       <c r="N47" s="20"/>
@@ -28928,7 +28842,7 @@
       <c r="AC47" s="20"/>
       <c r="AD47" s="20"/>
     </row>
-    <row r="48" spans="1:30" ht="16.5" customHeight="1">
+    <row r="48" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A48" s="19"/>
       <c r="B48" s="20"/>
       <c r="C48" s="20"/>
@@ -28960,7 +28874,7 @@
       <c r="AC48" s="20"/>
       <c r="AD48" s="20"/>
     </row>
-    <row r="49" spans="1:30" ht="16.5" customHeight="1">
+    <row r="49" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A49" s="19"/>
       <c r="B49" s="20"/>
       <c r="C49" s="20"/>
@@ -28992,7 +28906,7 @@
       <c r="AC49" s="20"/>
       <c r="AD49" s="20"/>
     </row>
-    <row r="50" spans="1:30" ht="16.5" customHeight="1">
+    <row r="50" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A50" s="19"/>
       <c r="B50" s="20"/>
       <c r="C50" s="20"/>
@@ -29024,7 +28938,7 @@
       <c r="AC50" s="20"/>
       <c r="AD50" s="20"/>
     </row>
-    <row r="51" spans="1:30" ht="16.5" customHeight="1">
+    <row r="51" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A51" s="19"/>
       <c r="B51" s="20"/>
       <c r="C51" s="20"/>
@@ -29056,7 +28970,7 @@
       <c r="AC51" s="20"/>
       <c r="AD51" s="20"/>
     </row>
-    <row r="52" spans="1:30" ht="20.100000000000001" customHeight="1">
+    <row r="52" spans="1:30" ht="20.100000000000001" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A52" s="19"/>
       <c r="B52" s="86" t="s">
         <v>310</v>
@@ -29165,7 +29079,7 @@
       <c r="AC52" s="20"/>
       <c r="AD52" s="20"/>
     </row>
-    <row r="53" spans="1:30" ht="15" customHeight="1">
+    <row r="53" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A53" s="19"/>
       <c r="B53" s="47" t="s">
         <v>246</v>
@@ -29249,7 +29163,7 @@
       <c r="AC53" s="20"/>
       <c r="AD53" s="20"/>
     </row>
-    <row r="54" spans="1:30" ht="15" customHeight="1">
+    <row r="54" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A54" s="19"/>
       <c r="B54" s="47" t="s">
         <v>247</v>
@@ -29358,7 +29272,7 @@
       <c r="AC54" s="20"/>
       <c r="AD54" s="20"/>
     </row>
-    <row r="55" spans="1:30" ht="15" customHeight="1">
+    <row r="55" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A55" s="19"/>
       <c r="B55" s="47" t="s">
         <v>248</v>
@@ -29467,7 +29381,7 @@
       <c r="AC55" s="20"/>
       <c r="AD55" s="20"/>
     </row>
-    <row r="56" spans="1:30" ht="15" customHeight="1">
+    <row r="56" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A56" s="19"/>
       <c r="B56" s="47" t="s">
         <v>249</v>
@@ -29576,7 +29490,7 @@
       <c r="AC56" s="20"/>
       <c r="AD56" s="20"/>
     </row>
-    <row r="57" spans="1:30" ht="15" customHeight="1">
+    <row r="57" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A57" s="19"/>
       <c r="B57" s="47" t="s">
         <v>250</v>
@@ -29685,7 +29599,7 @@
       <c r="AC57" s="20"/>
       <c r="AD57" s="20"/>
     </row>
-    <row r="58" spans="1:30" ht="16.5" customHeight="1">
+    <row r="58" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A58" s="19"/>
       <c r="B58" s="20"/>
       <c r="C58" s="20"/>
@@ -29717,7 +29631,7 @@
       <c r="AC58" s="20"/>
       <c r="AD58" s="20"/>
     </row>
-    <row r="59" spans="1:30" ht="15" customHeight="1">
+    <row r="59" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A59" s="19"/>
       <c r="B59" s="139" t="s">
         <v>406</v>
@@ -29751,7 +29665,7 @@
       <c r="AC59" s="20"/>
       <c r="AD59" s="20"/>
     </row>
-    <row r="60" spans="1:30" ht="15" customHeight="1">
+    <row r="60" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A60" s="19"/>
       <c r="B60" s="20" t="s">
         <v>407</v>
@@ -29860,7 +29774,7 @@
       <c r="AC60" s="20"/>
       <c r="AD60" s="20"/>
     </row>
-    <row r="61" spans="1:30" ht="15" customHeight="1">
+    <row r="61" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A61" s="19"/>
       <c r="B61" s="20" t="s">
         <v>408</v>
@@ -29969,7 +29883,7 @@
       <c r="AC61" s="20"/>
       <c r="AD61" s="20"/>
     </row>
-    <row r="62" spans="1:30" ht="15" customHeight="1">
+    <row r="62" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A62" s="19"/>
       <c r="B62" s="20" t="s">
         <v>409</v>
@@ -30078,7 +29992,7 @@
       <c r="AC62" s="20"/>
       <c r="AD62" s="20"/>
     </row>
-    <row r="63" spans="1:30" ht="15" customHeight="1">
+    <row r="63" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A63" s="19"/>
       <c r="B63" s="20" t="s">
         <v>410</v>
@@ -30187,7 +30101,7 @@
       <c r="AC63" s="20"/>
       <c r="AD63" s="20"/>
     </row>
-    <row r="64" spans="1:30" ht="15" customHeight="1">
+    <row r="64" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A64" s="19"/>
       <c r="B64" s="20" t="s">
         <v>411</v>
@@ -30296,7 +30210,7 @@
       <c r="AC64" s="20"/>
       <c r="AD64" s="20"/>
     </row>
-    <row r="65" spans="1:30" ht="16.5" customHeight="1">
+    <row r="65" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A65" s="19"/>
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
@@ -30328,7 +30242,7 @@
       <c r="AC65" s="20"/>
       <c r="AD65" s="20"/>
     </row>
-    <row r="66" spans="1:30" ht="15" customHeight="1">
+    <row r="66" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A66" s="19"/>
       <c r="B66" s="81" t="s">
         <v>255</v>
@@ -30437,7 +30351,7 @@
       <c r="AC66" s="20"/>
       <c r="AD66" s="20"/>
     </row>
-    <row r="67" spans="1:30" ht="15" customHeight="1">
+    <row r="67" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A67" s="19"/>
       <c r="B67" s="20" t="s">
         <v>412</v>
@@ -30546,7 +30460,7 @@
       <c r="AC67" s="20"/>
       <c r="AD67" s="20"/>
     </row>
-    <row r="68" spans="1:30" ht="15" customHeight="1">
+    <row r="68" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A68" s="19"/>
       <c r="B68" s="81" t="s">
         <v>257</v>
@@ -30655,7 +30569,7 @@
       <c r="AC68" s="20"/>
       <c r="AD68" s="20"/>
     </row>
-    <row r="69" spans="1:30" ht="16.5" customHeight="1">
+    <row r="69" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A69" s="19"/>
       <c r="B69" s="20"/>
       <c r="C69" s="20"/>
@@ -30687,7 +30601,7 @@
       <c r="AC69" s="20"/>
       <c r="AD69" s="20"/>
     </row>
-    <row r="70" spans="1:30" ht="21.95" customHeight="1">
+    <row r="70" spans="1:30" ht="21.95" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A70" s="19"/>
       <c r="B70" s="43" t="s">
         <v>413</v>
@@ -30721,7 +30635,7 @@
       <c r="AC70" s="20"/>
       <c r="AD70" s="20"/>
     </row>
-    <row r="71" spans="1:30" ht="15" customHeight="1">
+    <row r="71" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A71" s="19"/>
       <c r="B71" s="20" t="s">
         <v>187</v>
@@ -30830,7 +30744,7 @@
       <c r="AC71" s="20"/>
       <c r="AD71" s="20"/>
     </row>
-    <row r="72" spans="1:30" ht="15" customHeight="1">
+    <row r="72" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A72" s="19"/>
       <c r="B72" s="20" t="s">
         <v>188</v>
@@ -30939,7 +30853,7 @@
       <c r="AC72" s="20"/>
       <c r="AD72" s="20"/>
     </row>
-    <row r="73" spans="1:30" ht="15" customHeight="1">
+    <row r="73" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A73" s="19"/>
       <c r="B73" s="20" t="s">
         <v>189</v>
@@ -31048,7 +30962,7 @@
       <c r="AC73" s="20"/>
       <c r="AD73" s="20"/>
     </row>
-    <row r="74" spans="1:30" ht="15" customHeight="1">
+    <row r="74" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A74" s="19"/>
       <c r="B74" s="20" t="s">
         <v>190</v>
@@ -31157,7 +31071,7 @@
       <c r="AC74" s="20"/>
       <c r="AD74" s="20"/>
     </row>
-    <row r="75" spans="1:30" ht="15" customHeight="1">
+    <row r="75" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A75" s="19"/>
       <c r="B75" s="20" t="s">
         <v>414</v>
@@ -31266,7 +31180,7 @@
       <c r="AC75" s="20"/>
       <c r="AD75" s="20"/>
     </row>
-    <row r="76" spans="1:30" ht="15" customHeight="1">
+    <row r="76" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A76" s="19"/>
       <c r="B76" s="20" t="s">
         <v>415</v>
@@ -31375,7 +31289,7 @@
       <c r="AC76" s="20"/>
       <c r="AD76" s="20"/>
     </row>
-    <row r="77" spans="1:30" ht="15" customHeight="1">
+    <row r="77" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A77" s="19"/>
       <c r="B77" s="81" t="s">
         <v>416</v>
@@ -31484,7 +31398,7 @@
       <c r="AC77" s="20"/>
       <c r="AD77" s="20"/>
     </row>
-    <row r="78" spans="1:30" ht="16.5" customHeight="1">
+    <row r="78" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A78" s="19"/>
       <c r="B78" s="20"/>
       <c r="C78" s="20"/>
@@ -31516,7 +31430,7 @@
       <c r="AC78" s="20"/>
       <c r="AD78" s="20"/>
     </row>
-    <row r="79" spans="1:30" ht="15" customHeight="1">
+    <row r="79" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A79" s="19"/>
       <c r="B79" s="20" t="s">
         <v>417</v>
@@ -31625,7 +31539,7 @@
       <c r="AC79" s="20"/>
       <c r="AD79" s="20"/>
     </row>
-    <row r="80" spans="1:30" ht="15" customHeight="1">
+    <row r="80" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A80" s="19"/>
       <c r="B80" s="20" t="s">
         <v>204</v>
@@ -31734,7 +31648,7 @@
       <c r="AC80" s="20"/>
       <c r="AD80" s="20"/>
     </row>
-    <row r="81" spans="1:30" ht="16.5" customHeight="1">
+    <row r="81" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A81" s="19"/>
       <c r="B81" s="20"/>
       <c r="C81" s="20"/>
@@ -31766,7 +31680,7 @@
       <c r="AC81" s="20"/>
       <c r="AD81" s="20"/>
     </row>
-    <row r="82" spans="1:30" ht="15" customHeight="1">
+    <row r="82" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A82" s="19"/>
       <c r="B82" s="142" t="s">
         <v>418</v>
@@ -31875,7 +31789,7 @@
       <c r="AC82" s="20"/>
       <c r="AD82" s="20"/>
     </row>
-    <row r="83" spans="1:30" ht="15" customHeight="1">
+    <row r="83" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A83" s="19"/>
       <c r="B83" s="144" t="s">
         <v>419</v>
@@ -31984,7 +31898,7 @@
       <c r="AC83" s="20"/>
       <c r="AD83" s="20"/>
     </row>
-    <row r="84" spans="1:30" ht="16.5" customHeight="1">
+    <row r="84" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A84" s="19"/>
       <c r="B84" s="20"/>
       <c r="C84" s="20"/>
@@ -32016,7 +31930,7 @@
       <c r="AC84" s="20"/>
       <c r="AD84" s="20"/>
     </row>
-    <row r="85" spans="1:30" ht="15" customHeight="1">
+    <row r="85" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A85" s="19"/>
       <c r="B85" s="47" t="s">
         <v>420</v>
@@ -32125,7 +32039,7 @@
       <c r="AC85" s="20"/>
       <c r="AD85" s="20"/>
     </row>
-    <row r="86" spans="1:30" ht="16.5" customHeight="1">
+    <row r="86" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A86" s="19"/>
       <c r="B86" s="20"/>
       <c r="C86" s="20"/>
@@ -32157,7 +32071,7 @@
       <c r="AC86" s="20"/>
       <c r="AD86" s="20"/>
     </row>
-    <row r="87" spans="1:30" ht="15" customHeight="1">
+    <row r="87" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A87" s="19"/>
       <c r="B87" s="20" t="s">
         <v>421</v>
@@ -32266,7 +32180,7 @@
       <c r="AC87" s="20"/>
       <c r="AD87" s="20"/>
     </row>
-    <row r="88" spans="1:30" ht="16.5" customHeight="1">
+    <row r="88" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A88" s="19"/>
       <c r="B88" s="20"/>
       <c r="C88" s="20"/>
@@ -32298,7 +32212,7 @@
       <c r="AC88" s="20"/>
       <c r="AD88" s="20"/>
     </row>
-    <row r="89" spans="1:30" ht="16.5" customHeight="1">
+    <row r="89" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A89" s="19"/>
       <c r="B89" s="20"/>
       <c r="C89" s="20"/>
@@ -32330,7 +32244,7 @@
       <c r="AC89" s="20"/>
       <c r="AD89" s="20"/>
     </row>
-    <row r="90" spans="1:30" ht="16.5" customHeight="1">
+    <row r="90" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A90" s="19"/>
       <c r="B90" s="20"/>
       <c r="C90" s="20"/>
@@ -32362,7 +32276,7 @@
       <c r="AC90" s="20"/>
       <c r="AD90" s="20"/>
     </row>
-    <row r="91" spans="1:30" ht="16.5" customHeight="1">
+    <row r="91" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A91" s="19"/>
       <c r="B91" s="20"/>
       <c r="C91" s="20"/>
@@ -32394,7 +32308,7 @@
       <c r="AC91" s="20"/>
       <c r="AD91" s="20"/>
     </row>
-    <row r="92" spans="1:30" ht="16.5" customHeight="1">
+    <row r="92" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A92" s="19"/>
       <c r="B92" s="20"/>
       <c r="C92" s="20"/>
@@ -32426,7 +32340,7 @@
       <c r="AC92" s="20"/>
       <c r="AD92" s="20"/>
     </row>
-    <row r="93" spans="1:30" ht="16.5" customHeight="1">
+    <row r="93" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A93" s="19"/>
       <c r="B93" s="20"/>
       <c r="C93" s="20"/>
@@ -32458,7 +32372,7 @@
       <c r="AC93" s="20"/>
       <c r="AD93" s="20"/>
     </row>
-    <row r="94" spans="1:30" ht="16.5" customHeight="1">
+    <row r="94" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A94" s="19"/>
       <c r="B94" s="20"/>
       <c r="C94" s="20"/>
@@ -32490,7 +32404,7 @@
       <c r="AC94" s="20"/>
       <c r="AD94" s="20"/>
     </row>
-    <row r="95" spans="1:30" ht="16.5" customHeight="1">
+    <row r="95" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A95" s="19"/>
       <c r="B95" s="20"/>
       <c r="C95" s="20"/>
@@ -32522,7 +32436,7 @@
       <c r="AC95" s="20"/>
       <c r="AD95" s="20"/>
     </row>
-    <row r="96" spans="1:30" ht="16.5" customHeight="1">
+    <row r="96" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A96" s="19"/>
       <c r="B96" s="20"/>
       <c r="C96" s="20"/>
@@ -32554,7 +32468,7 @@
       <c r="AC96" s="20"/>
       <c r="AD96" s="20"/>
     </row>
-    <row r="97" spans="1:30" ht="16.5" customHeight="1">
+    <row r="97" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A97" s="19"/>
       <c r="B97" s="20"/>
       <c r="C97" s="20"/>
@@ -32586,7 +32500,7 @@
       <c r="AC97" s="20"/>
       <c r="AD97" s="20"/>
     </row>
-    <row r="98" spans="1:30" ht="16.5" customHeight="1">
+    <row r="98" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A98" s="19"/>
       <c r="B98" s="20"/>
       <c r="C98" s="20"/>
@@ -32618,7 +32532,7 @@
       <c r="AC98" s="20"/>
       <c r="AD98" s="20"/>
     </row>
-    <row r="99" spans="1:30" ht="16.5" customHeight="1">
+    <row r="99" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A99" s="19"/>
       <c r="B99" s="20"/>
       <c r="C99" s="20"/>
@@ -32650,7 +32564,7 @@
       <c r="AC99" s="20"/>
       <c r="AD99" s="20"/>
     </row>
-    <row r="100" spans="1:30" ht="16.5" customHeight="1">
+    <row r="100" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A100" s="19"/>
       <c r="B100" s="20"/>
       <c r="C100" s="20"/>
@@ -32682,7 +32596,7 @@
       <c r="AC100" s="20"/>
       <c r="AD100" s="20"/>
     </row>
-    <row r="101" spans="1:30" ht="16.5" customHeight="1">
+    <row r="101" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A101" s="19"/>
       <c r="B101" s="20"/>
       <c r="C101" s="20"/>
@@ -32714,7 +32628,7 @@
       <c r="AC101" s="20"/>
       <c r="AD101" s="20"/>
     </row>
-    <row r="102" spans="1:30" ht="16.5" customHeight="1">
+    <row r="102" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A102" s="19"/>
       <c r="B102" s="20"/>
       <c r="C102" s="20"/>
@@ -32746,7 +32660,7 @@
       <c r="AC102" s="20"/>
       <c r="AD102" s="20"/>
     </row>
-    <row r="103" spans="1:30" ht="16.5" customHeight="1">
+    <row r="103" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A103" s="19"/>
       <c r="B103" s="20"/>
       <c r="C103" s="20"/>
@@ -32778,7 +32692,7 @@
       <c r="AC103" s="20"/>
       <c r="AD103" s="20"/>
     </row>
-    <row r="104" spans="1:30" ht="16.5" customHeight="1">
+    <row r="104" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A104" s="19"/>
       <c r="B104" s="20"/>
       <c r="C104" s="20"/>
@@ -32810,7 +32724,7 @@
       <c r="AC104" s="20"/>
       <c r="AD104" s="20"/>
     </row>
-    <row r="105" spans="1:30" ht="16.5" customHeight="1">
+    <row r="105" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A105" s="19"/>
       <c r="B105" s="20"/>
       <c r="C105" s="20"/>
@@ -32842,7 +32756,7 @@
       <c r="AC105" s="20"/>
       <c r="AD105" s="20"/>
     </row>
-    <row r="106" spans="1:30" ht="16.5" customHeight="1">
+    <row r="106" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A106" s="19"/>
       <c r="B106" s="20"/>
       <c r="C106" s="20"/>
@@ -32874,7 +32788,7 @@
       <c r="AC106" s="20"/>
       <c r="AD106" s="20"/>
     </row>
-    <row r="107" spans="1:30" ht="16.5" customHeight="1">
+    <row r="107" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A107" s="19"/>
       <c r="B107" s="20"/>
       <c r="C107" s="20"/>
@@ -32906,7 +32820,7 @@
       <c r="AC107" s="20"/>
       <c r="AD107" s="20"/>
     </row>
-    <row r="108" spans="1:30" ht="16.5" customHeight="1">
+    <row r="108" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A108" s="19"/>
       <c r="B108" s="20"/>
       <c r="C108" s="20"/>
@@ -32938,7 +32852,7 @@
       <c r="AC108" s="20"/>
       <c r="AD108" s="20"/>
     </row>
-    <row r="109" spans="1:30" ht="15" customHeight="1">
+    <row r="109" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A109" s="19"/>
       <c r="B109" s="139" t="s">
         <v>422</v>
@@ -32972,7 +32886,7 @@
       <c r="AC109" s="20"/>
       <c r="AD109" s="20"/>
     </row>
-    <row r="110" spans="1:30" ht="16.5" customHeight="1">
+    <row r="110" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A110" s="19"/>
       <c r="B110" s="20"/>
       <c r="C110" s="20"/>
@@ -33004,7 +32918,7 @@
       <c r="AC110" s="20"/>
       <c r="AD110" s="20"/>
     </row>
-    <row r="111" spans="1:30" ht="15" customHeight="1">
+    <row r="111" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A111" s="19"/>
       <c r="B111" s="20" t="s">
         <v>26</v>
@@ -33041,7 +32955,7 @@
       <c r="AC111" s="20"/>
       <c r="AD111" s="20"/>
     </row>
-    <row r="112" spans="1:30" ht="15" customHeight="1">
+    <row r="112" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A112" s="19"/>
       <c r="B112" s="20" t="s">
         <v>19</v>
@@ -33078,7 +32992,7 @@
       <c r="AC112" s="20"/>
       <c r="AD112" s="20"/>
     </row>
-    <row r="113" spans="1:30" ht="15" customHeight="1">
+    <row r="113" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A113" s="19"/>
       <c r="B113" s="20" t="s">
         <v>423</v>
@@ -33115,7 +33029,7 @@
       <c r="AC113" s="20"/>
       <c r="AD113" s="20"/>
     </row>
-    <row r="114" spans="1:30" ht="16.5" customHeight="1">
+    <row r="114" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A114" s="19"/>
       <c r="B114" s="20"/>
       <c r="C114" s="20"/>
@@ -33147,7 +33061,7 @@
       <c r="AC114" s="20"/>
       <c r="AD114" s="20"/>
     </row>
-    <row r="115" spans="1:30" ht="15" customHeight="1">
+    <row r="115" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A115" s="19"/>
       <c r="B115" s="81" t="s">
         <v>424</v>
@@ -33184,7 +33098,7 @@
       <c r="AC115" s="20"/>
       <c r="AD115" s="20"/>
     </row>
-    <row r="116" spans="1:30" ht="15" customHeight="1">
+    <row r="116" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A116" s="19"/>
       <c r="B116" s="20" t="s">
         <v>425</v>
@@ -33221,7 +33135,7 @@
       <c r="AC116" s="20"/>
       <c r="AD116" s="20"/>
     </row>
-    <row r="117" spans="1:30" ht="15" customHeight="1">
+    <row r="117" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A117" s="19"/>
       <c r="B117" s="81" t="s">
         <v>426</v>
@@ -33258,7 +33172,7 @@
       <c r="AC117" s="20"/>
       <c r="AD117" s="20"/>
     </row>
-    <row r="118" spans="1:30" ht="15" customHeight="1">
+    <row r="118" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A118" s="19"/>
       <c r="B118" s="81" t="s">
         <v>427</v>
@@ -33295,7 +33209,7 @@
       <c r="AC118" s="20"/>
       <c r="AD118" s="20"/>
     </row>
-    <row r="119" spans="1:30" ht="15" customHeight="1">
+    <row r="119" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A119" s="19"/>
       <c r="B119" s="142" t="s">
         <v>428</v>
@@ -33332,7 +33246,7 @@
       <c r="AC119" s="20"/>
       <c r="AD119" s="20"/>
     </row>
-    <row r="120" spans="1:30" ht="16.5" customHeight="1">
+    <row r="120" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A120" s="19"/>
       <c r="B120" s="20"/>
       <c r="C120" s="20"/>
@@ -33364,7 +33278,7 @@
       <c r="AC120" s="20"/>
       <c r="AD120" s="20"/>
     </row>
-    <row r="121" spans="1:30" ht="15" customHeight="1">
+    <row r="121" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A121" s="19"/>
       <c r="B121" s="139" t="s">
         <v>429</v>
@@ -33398,7 +33312,7 @@
       <c r="AC121" s="20"/>
       <c r="AD121" s="20"/>
     </row>
-    <row r="122" spans="1:30" ht="16.5" customHeight="1">
+    <row r="122" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A122" s="19"/>
       <c r="B122" s="20"/>
       <c r="C122" s="20"/>
@@ -33430,7 +33344,7 @@
       <c r="AC122" s="20"/>
       <c r="AD122" s="20"/>
     </row>
-    <row r="123" spans="1:30" ht="15" customHeight="1">
+    <row r="123" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A123" s="19"/>
       <c r="B123" s="20" t="s">
         <v>430</v>
@@ -33539,7 +33453,7 @@
       <c r="AC123" s="20"/>
       <c r="AD123" s="20"/>
     </row>
-    <row r="124" spans="1:30" ht="15" customHeight="1">
+    <row r="124" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A124" s="19"/>
       <c r="B124" s="20" t="s">
         <v>431</v>
@@ -33648,7 +33562,7 @@
       <c r="AC124" s="20"/>
       <c r="AD124" s="20"/>
     </row>
-    <row r="125" spans="1:30" ht="15" customHeight="1">
+    <row r="125" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A125" s="19"/>
       <c r="B125" s="20" t="s">
         <v>432</v>
@@ -33757,7 +33671,7 @@
       <c r="AC125" s="20"/>
       <c r="AD125" s="20"/>
     </row>
-    <row r="126" spans="1:30" ht="15" customHeight="1">
+    <row r="126" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A126" s="19"/>
       <c r="B126" s="20" t="s">
         <v>433</v>
@@ -33866,7 +33780,7 @@
       <c r="AC126" s="20"/>
       <c r="AD126" s="20"/>
     </row>
-    <row r="127" spans="1:30" ht="15" customHeight="1">
+    <row r="127" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A127" s="19"/>
       <c r="B127" s="20" t="s">
         <v>434</v>
@@ -33975,7 +33889,7 @@
       <c r="AC127" s="20"/>
       <c r="AD127" s="20"/>
     </row>
-    <row r="128" spans="1:30" ht="16.5" customHeight="1">
+    <row r="128" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A128" s="19"/>
       <c r="B128" s="20"/>
       <c r="C128" s="20"/>
@@ -34007,7 +33921,7 @@
       <c r="AC128" s="20"/>
       <c r="AD128" s="20"/>
     </row>
-    <row r="129" spans="1:30" ht="15" customHeight="1">
+    <row r="129" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A129" s="19"/>
       <c r="B129" s="20" t="s">
         <v>435</v>
@@ -34116,7 +34030,7 @@
       <c r="AC129" s="20"/>
       <c r="AD129" s="20"/>
     </row>
-    <row r="130" spans="1:30" ht="15" customHeight="1">
+    <row r="130" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A130" s="19"/>
       <c r="B130" s="20" t="s">
         <v>436</v>
@@ -34225,7 +34139,7 @@
       <c r="AC130" s="20"/>
       <c r="AD130" s="20"/>
     </row>
-    <row r="131" spans="1:30" ht="15" customHeight="1">
+    <row r="131" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A131" s="19"/>
       <c r="B131" s="20" t="s">
         <v>437</v>
@@ -34334,7 +34248,7 @@
       <c r="AC131" s="20"/>
       <c r="AD131" s="20"/>
     </row>
-    <row r="132" spans="1:30" ht="15" customHeight="1">
+    <row r="132" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A132" s="19"/>
       <c r="B132" s="20" t="s">
         <v>438</v>
@@ -34443,7 +34357,7 @@
       <c r="AC132" s="20"/>
       <c r="AD132" s="20"/>
     </row>
-    <row r="133" spans="1:30" ht="15" customHeight="1">
+    <row r="133" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A133" s="19"/>
       <c r="B133" s="20" t="s">
         <v>439</v>
@@ -34552,7 +34466,7 @@
       <c r="AC133" s="20"/>
       <c r="AD133" s="20"/>
     </row>
-    <row r="134" spans="1:30" ht="15" customHeight="1">
+    <row r="134" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A134" s="19"/>
       <c r="B134" s="20" t="s">
         <v>440</v>
@@ -34661,7 +34575,7 @@
       <c r="AC134" s="20"/>
       <c r="AD134" s="20"/>
     </row>
-    <row r="135" spans="1:30" ht="16.5" customHeight="1">
+    <row r="135" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A135" s="19"/>
       <c r="B135" s="20"/>
       <c r="C135" s="20"/>
@@ -34693,7 +34607,7 @@
       <c r="AC135" s="20"/>
       <c r="AD135" s="20"/>
     </row>
-    <row r="136" spans="1:30" ht="15" customHeight="1">
+    <row r="136" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A136" s="19"/>
       <c r="B136" s="20" t="s">
         <v>441</v>
@@ -34730,7 +34644,7 @@
       <c r="AC136" s="20"/>
       <c r="AD136" s="20"/>
     </row>
-    <row r="137" spans="1:30" ht="15" customHeight="1">
+    <row r="137" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A137" s="19"/>
       <c r="B137" s="20" t="s">
         <v>442</v>
@@ -34767,7 +34681,7 @@
       <c r="AC137" s="20"/>
       <c r="AD137" s="20"/>
     </row>
-    <row r="138" spans="1:30" ht="15" customHeight="1">
+    <row r="138" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A138" s="19"/>
       <c r="B138" s="20" t="s">
         <v>443</v>
@@ -34804,7 +34718,7 @@
       <c r="AC138" s="20"/>
       <c r="AD138" s="20"/>
     </row>
-    <row r="139" spans="1:30" ht="15" customHeight="1">
+    <row r="139" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A139" s="19"/>
       <c r="B139" s="81" t="s">
         <v>444</v>
@@ -34841,7 +34755,7 @@
       <c r="AC139" s="20"/>
       <c r="AD139" s="20"/>
     </row>
-    <row r="140" spans="1:30" ht="15" customHeight="1">
+    <row r="140" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A140" s="19"/>
       <c r="B140" s="81" t="s">
         <v>445</v>
@@ -34878,7 +34792,7 @@
       <c r="AC140" s="20"/>
       <c r="AD140" s="20"/>
     </row>
-    <row r="141" spans="1:30" ht="16.5" customHeight="1">
+    <row r="141" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A141" s="19"/>
       <c r="B141" s="20"/>
       <c r="C141" s="20"/>
@@ -34910,7 +34824,7 @@
       <c r="AC141" s="20"/>
       <c r="AD141" s="20"/>
     </row>
-    <row r="142" spans="1:30" ht="16.5" customHeight="1">
+    <row r="142" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A142" s="19"/>
       <c r="B142" s="20"/>
       <c r="C142" s="20"/>
@@ -34942,7 +34856,7 @@
       <c r="AC142" s="20"/>
       <c r="AD142" s="20"/>
     </row>
-    <row r="143" spans="1:30" ht="16.5" customHeight="1">
+    <row r="143" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A143" s="19"/>
       <c r="B143" s="20"/>
       <c r="C143" s="20"/>
@@ -34974,7 +34888,7 @@
       <c r="AC143" s="20"/>
       <c r="AD143" s="20"/>
     </row>
-    <row r="144" spans="1:30" ht="16.5" customHeight="1">
+    <row r="144" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A144" s="19"/>
       <c r="B144" s="20"/>
       <c r="C144" s="20"/>
@@ -35006,7 +34920,7 @@
       <c r="AC144" s="20"/>
       <c r="AD144" s="20"/>
     </row>
-    <row r="145" spans="1:30" ht="16.5" customHeight="1">
+    <row r="145" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A145" s="19"/>
       <c r="B145" s="20"/>
       <c r="C145" s="20"/>
@@ -35038,7 +34952,7 @@
       <c r="AC145" s="20"/>
       <c r="AD145" s="20"/>
     </row>
-    <row r="146" spans="1:30" ht="16.5" customHeight="1">
+    <row r="146" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A146" s="19"/>
       <c r="B146" s="20"/>
       <c r="C146" s="20"/>
@@ -35070,7 +34984,7 @@
       <c r="AC146" s="20"/>
       <c r="AD146" s="20"/>
     </row>
-    <row r="147" spans="1:30" ht="16.5" customHeight="1">
+    <row r="147" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A147" s="19"/>
       <c r="B147" s="20"/>
       <c r="C147" s="20"/>
@@ -35102,7 +35016,7 @@
       <c r="AC147" s="20"/>
       <c r="AD147" s="20"/>
     </row>
-    <row r="148" spans="1:30" ht="16.5" customHeight="1">
+    <row r="148" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A148" s="19"/>
       <c r="B148" s="20"/>
       <c r="C148" s="20"/>
@@ -35134,7 +35048,7 @@
       <c r="AC148" s="20"/>
       <c r="AD148" s="20"/>
     </row>
-    <row r="149" spans="1:30" ht="16.5" customHeight="1">
+    <row r="149" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A149" s="19"/>
       <c r="B149" s="20"/>
       <c r="C149" s="20"/>
@@ -35166,7 +35080,7 @@
       <c r="AC149" s="20"/>
       <c r="AD149" s="20"/>
     </row>
-    <row r="150" spans="1:30" ht="16.5" customHeight="1">
+    <row r="150" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A150" s="19"/>
       <c r="B150" s="20"/>
       <c r="C150" s="20"/>
@@ -35198,7 +35112,7 @@
       <c r="AC150" s="20"/>
       <c r="AD150" s="20"/>
     </row>
-    <row r="151" spans="1:30" ht="16.5" customHeight="1">
+    <row r="151" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A151" s="19"/>
       <c r="B151" s="20"/>
       <c r="C151" s="20"/>
@@ -35230,7 +35144,7 @@
       <c r="AC151" s="20"/>
       <c r="AD151" s="20"/>
     </row>
-    <row r="152" spans="1:30" ht="16.5" customHeight="1">
+    <row r="152" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A152" s="19"/>
       <c r="B152" s="20"/>
       <c r="C152" s="20"/>
@@ -35262,7 +35176,7 @@
       <c r="AC152" s="20"/>
       <c r="AD152" s="20"/>
     </row>
-    <row r="153" spans="1:30" ht="16.5" customHeight="1">
+    <row r="153" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A153" s="19"/>
       <c r="B153" s="20"/>
       <c r="C153" s="20"/>
@@ -35294,7 +35208,7 @@
       <c r="AC153" s="20"/>
       <c r="AD153" s="20"/>
     </row>
-    <row r="154" spans="1:30" ht="16.5" customHeight="1">
+    <row r="154" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A154" s="19"/>
       <c r="B154" s="20"/>
       <c r="C154" s="20"/>
@@ -35326,7 +35240,7 @@
       <c r="AC154" s="20"/>
       <c r="AD154" s="20"/>
     </row>
-    <row r="155" spans="1:30" ht="16.5" customHeight="1">
+    <row r="155" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A155" s="19"/>
       <c r="B155" s="20"/>
       <c r="C155" s="20"/>
@@ -35358,7 +35272,7 @@
       <c r="AC155" s="20"/>
       <c r="AD155" s="20"/>
     </row>
-    <row r="156" spans="1:30" ht="16.5" customHeight="1">
+    <row r="156" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A156" s="19"/>
       <c r="B156" s="20"/>
       <c r="C156" s="20"/>
@@ -35390,7 +35304,7 @@
       <c r="AC156" s="20"/>
       <c r="AD156" s="20"/>
     </row>
-    <row r="157" spans="1:30" ht="16.5" customHeight="1">
+    <row r="157" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A157" s="19"/>
       <c r="B157" s="20"/>
       <c r="C157" s="20"/>
@@ -35422,7 +35336,7 @@
       <c r="AC157" s="20"/>
       <c r="AD157" s="20"/>
     </row>
-    <row r="158" spans="1:30" ht="16.5" customHeight="1">
+    <row r="158" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A158" s="19"/>
       <c r="B158" s="20"/>
       <c r="C158" s="20"/>
@@ -35454,7 +35368,7 @@
       <c r="AC158" s="20"/>
       <c r="AD158" s="20"/>
     </row>
-    <row r="159" spans="1:30" ht="16.5" customHeight="1">
+    <row r="159" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A159" s="19"/>
       <c r="B159" s="20"/>
       <c r="C159" s="20"/>
@@ -35486,7 +35400,7 @@
       <c r="AC159" s="20"/>
       <c r="AD159" s="20"/>
     </row>
-    <row r="160" spans="1:30" ht="16.5" customHeight="1">
+    <row r="160" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A160" s="19"/>
       <c r="B160" s="20"/>
       <c r="C160" s="20"/>
@@ -35518,7 +35432,7 @@
       <c r="AC160" s="20"/>
       <c r="AD160" s="20"/>
     </row>
-    <row r="161" spans="1:30" ht="16.5" customHeight="1">
+    <row r="161" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A161" s="19"/>
       <c r="B161" s="20"/>
       <c r="C161" s="20"/>
@@ -35550,7 +35464,7 @@
       <c r="AC161" s="20"/>
       <c r="AD161" s="20"/>
     </row>
-    <row r="162" spans="1:30" ht="16.5" customHeight="1">
+    <row r="162" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A162" s="19"/>
       <c r="B162" s="20"/>
       <c r="C162" s="20"/>
@@ -35582,7 +35496,7 @@
       <c r="AC162" s="20"/>
       <c r="AD162" s="20"/>
     </row>
-    <row r="163" spans="1:30" ht="16.5" customHeight="1">
+    <row r="163" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A163" s="19"/>
       <c r="B163" s="20"/>
       <c r="C163" s="20"/>
@@ -35614,7 +35528,7 @@
       <c r="AC163" s="20"/>
       <c r="AD163" s="20"/>
     </row>
-    <row r="164" spans="1:30" ht="15" customHeight="1">
+    <row r="164" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A164" s="19"/>
       <c r="B164" s="139" t="s">
         <v>446</v>
@@ -35648,7 +35562,7 @@
       <c r="AC164" s="20"/>
       <c r="AD164" s="20"/>
     </row>
-    <row r="165" spans="1:30" ht="16.5" customHeight="1">
+    <row r="165" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A165" s="19"/>
       <c r="B165" s="20"/>
       <c r="C165" s="20"/>
@@ -35680,7 +35594,7 @@
       <c r="AC165" s="20"/>
       <c r="AD165" s="20"/>
     </row>
-    <row r="166" spans="1:30" ht="15" customHeight="1">
+    <row r="166" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A166" s="19"/>
       <c r="B166" s="20" t="s">
         <v>447</v>
@@ -35789,7 +35703,7 @@
       <c r="AC166" s="20"/>
       <c r="AD166" s="20"/>
     </row>
-    <row r="167" spans="1:30" ht="15" customHeight="1">
+    <row r="167" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A167" s="19"/>
       <c r="B167" s="20" t="s">
         <v>448</v>
@@ -35898,7 +35812,7 @@
       <c r="AC167" s="20"/>
       <c r="AD167" s="20"/>
     </row>
-    <row r="168" spans="1:30" ht="15" customHeight="1">
+    <row r="168" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A168" s="19"/>
       <c r="B168" s="20" t="s">
         <v>449</v>
@@ -36007,7 +35921,7 @@
       <c r="AC168" s="20"/>
       <c r="AD168" s="20"/>
     </row>
-    <row r="169" spans="1:30" ht="15" customHeight="1">
+    <row r="169" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A169" s="19"/>
       <c r="B169" s="20" t="s">
         <v>450</v>
@@ -36116,7 +36030,7 @@
       <c r="AC169" s="20"/>
       <c r="AD169" s="20"/>
     </row>
-    <row r="170" spans="1:30" ht="16.5" customHeight="1">
+    <row r="170" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A170" s="19"/>
       <c r="B170" s="20"/>
       <c r="C170" s="20"/>
@@ -36148,7 +36062,7 @@
       <c r="AC170" s="20"/>
       <c r="AD170" s="20"/>
     </row>
-    <row r="171" spans="1:30" ht="15" customHeight="1">
+    <row r="171" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A171" s="19"/>
       <c r="B171" s="20" t="s">
         <v>451</v>
@@ -36257,7 +36171,7 @@
       <c r="AC171" s="20"/>
       <c r="AD171" s="20"/>
     </row>
-    <row r="172" spans="1:30" ht="15" customHeight="1">
+    <row r="172" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A172" s="19"/>
       <c r="B172" s="20" t="s">
         <v>452</v>
@@ -36366,7 +36280,7 @@
       <c r="AC172" s="20"/>
       <c r="AD172" s="20"/>
     </row>
-    <row r="173" spans="1:30" ht="15" customHeight="1">
+    <row r="173" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A173" s="19"/>
       <c r="B173" s="81" t="s">
         <v>453</v>
@@ -36475,7 +36389,7 @@
       <c r="AC173" s="20"/>
       <c r="AD173" s="20"/>
     </row>
-    <row r="174" spans="1:30" ht="16.5" customHeight="1">
+    <row r="174" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A174" s="19"/>
       <c r="B174" s="20"/>
       <c r="C174" s="20"/>
@@ -36507,7 +36421,7 @@
       <c r="AC174" s="20"/>
       <c r="AD174" s="20"/>
     </row>
-    <row r="175" spans="1:30" ht="15" customHeight="1">
+    <row r="175" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A175" s="19"/>
       <c r="B175" s="20" t="s">
         <v>454</v>
@@ -36616,7 +36530,7 @@
       <c r="AC175" s="20"/>
       <c r="AD175" s="20"/>
     </row>
-    <row r="176" spans="1:30" ht="16.5" customHeight="1">
+    <row r="176" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A176" s="19"/>
       <c r="B176" s="20"/>
       <c r="C176" s="20"/>
@@ -36648,7 +36562,7 @@
       <c r="AC176" s="20"/>
       <c r="AD176" s="20"/>
     </row>
-    <row r="177" spans="1:30" ht="15" customHeight="1">
+    <row r="177" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A177" s="19"/>
       <c r="B177" s="81" t="s">
         <v>455</v>
@@ -36685,7 +36599,7 @@
       <c r="AC177" s="20"/>
       <c r="AD177" s="20"/>
     </row>
-    <row r="178" spans="1:30" ht="16.5" customHeight="1">
+    <row r="178" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A178" s="19"/>
       <c r="B178" s="20"/>
       <c r="C178" s="20"/>
@@ -36717,7 +36631,7 @@
       <c r="AC178" s="20"/>
       <c r="AD178" s="20"/>
     </row>
-    <row r="179" spans="1:30" ht="15" customHeight="1">
+    <row r="179" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A179" s="19"/>
       <c r="B179" s="139" t="s">
         <v>456</v>
@@ -36751,7 +36665,7 @@
       <c r="AC179" s="20"/>
       <c r="AD179" s="20"/>
     </row>
-    <row r="180" spans="1:30" ht="16.5" customHeight="1">
+    <row r="180" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A180" s="19"/>
       <c r="B180" s="20"/>
       <c r="C180" s="20"/>
@@ -36783,7 +36697,7 @@
       <c r="AC180" s="20"/>
       <c r="AD180" s="20"/>
     </row>
-    <row r="181" spans="1:30" ht="15" customHeight="1">
+    <row r="181" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A181" s="19"/>
       <c r="B181" s="20" t="s">
         <v>457</v>
@@ -36892,7 +36806,7 @@
       <c r="AC181" s="20"/>
       <c r="AD181" s="20"/>
     </row>
-    <row r="182" spans="1:30" ht="15" customHeight="1">
+    <row r="182" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A182" s="19"/>
       <c r="B182" s="20" t="s">
         <v>458</v>
@@ -37001,7 +36915,7 @@
       <c r="AC182" s="20"/>
       <c r="AD182" s="20"/>
     </row>
-    <row r="183" spans="1:30" ht="15" customHeight="1">
+    <row r="183" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A183" s="19"/>
       <c r="B183" s="20" t="s">
         <v>459</v>
@@ -37110,7 +37024,7 @@
       <c r="AC183" s="20"/>
       <c r="AD183" s="20"/>
     </row>
-    <row r="184" spans="1:30" ht="15" customHeight="1">
+    <row r="184" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A184" s="19"/>
       <c r="B184" s="20" t="s">
         <v>460</v>
@@ -37219,7 +37133,7 @@
       <c r="AC184" s="20"/>
       <c r="AD184" s="20"/>
     </row>
-    <row r="185" spans="1:30" ht="16.5" customHeight="1">
+    <row r="185" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A185" s="19"/>
       <c r="B185" s="20"/>
       <c r="C185" s="20"/>
@@ -37251,7 +37165,7 @@
       <c r="AC185" s="20"/>
       <c r="AD185" s="20"/>
     </row>
-    <row r="186" spans="1:30" ht="15" customHeight="1">
+    <row r="186" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A186" s="19"/>
       <c r="B186" s="20" t="s">
         <v>461</v>
@@ -37360,7 +37274,7 @@
       <c r="AC186" s="20"/>
       <c r="AD186" s="20"/>
     </row>
-    <row r="187" spans="1:30" ht="15" customHeight="1">
+    <row r="187" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A187" s="19"/>
       <c r="B187" s="20" t="s">
         <v>462</v>
@@ -37469,7 +37383,7 @@
       <c r="AC187" s="20"/>
       <c r="AD187" s="20"/>
     </row>
-    <row r="188" spans="1:30" ht="15" customHeight="1">
+    <row r="188" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A188" s="19"/>
       <c r="B188" s="81" t="s">
         <v>463</v>
@@ -37578,7 +37492,7 @@
       <c r="AC188" s="20"/>
       <c r="AD188" s="20"/>
     </row>
-    <row r="189" spans="1:30" ht="16.5" customHeight="1">
+    <row r="189" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A189" s="19"/>
       <c r="B189" s="20"/>
       <c r="C189" s="20"/>
@@ -37610,7 +37524,7 @@
       <c r="AC189" s="20"/>
       <c r="AD189" s="20"/>
     </row>
-    <row r="190" spans="1:30" ht="15" customHeight="1">
+    <row r="190" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A190" s="19"/>
       <c r="B190" s="20" t="s">
         <v>464</v>
@@ -37719,7 +37633,7 @@
       <c r="AC190" s="20"/>
       <c r="AD190" s="20"/>
     </row>
-    <row r="191" spans="1:30" ht="16.5" customHeight="1">
+    <row r="191" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A191" s="19"/>
       <c r="B191" s="20"/>
       <c r="C191" s="20"/>
@@ -37751,7 +37665,7 @@
       <c r="AC191" s="20"/>
       <c r="AD191" s="20"/>
     </row>
-    <row r="192" spans="1:30" ht="15" customHeight="1">
+    <row r="192" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A192" s="19"/>
       <c r="B192" s="81" t="s">
         <v>465</v>
@@ -37788,7 +37702,7 @@
       <c r="AC192" s="20"/>
       <c r="AD192" s="20"/>
     </row>
-    <row r="193" spans="1:30" ht="15" customHeight="1">
+    <row r="193" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A193" s="19"/>
       <c r="B193" s="81" t="s">
         <v>466</v>
@@ -37825,7 +37739,7 @@
       <c r="AC193" s="20"/>
       <c r="AD193" s="20"/>
     </row>
-    <row r="194" spans="1:30" ht="16.5" customHeight="1">
+    <row r="194" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A194" s="19"/>
       <c r="B194" s="20"/>
       <c r="C194" s="20"/>
@@ -37857,7 +37771,7 @@
       <c r="AC194" s="20"/>
       <c r="AD194" s="20"/>
     </row>
-    <row r="195" spans="1:30" ht="16.5" customHeight="1">
+    <row r="195" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A195" s="19"/>
       <c r="B195" s="20"/>
       <c r="C195" s="20"/>
@@ -37889,7 +37803,7 @@
       <c r="AC195" s="20"/>
       <c r="AD195" s="20"/>
     </row>
-    <row r="196" spans="1:30" ht="16.5" customHeight="1">
+    <row r="196" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A196" s="19"/>
       <c r="B196" s="20"/>
       <c r="C196" s="20"/>
@@ -37921,7 +37835,7 @@
       <c r="AC196" s="20"/>
       <c r="AD196" s="20"/>
     </row>
-    <row r="197" spans="1:30" ht="15" customHeight="1">
+    <row r="197" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A197" s="19"/>
       <c r="B197" s="139" t="s">
         <v>467</v>
@@ -37955,7 +37869,7 @@
       <c r="AC197" s="20"/>
       <c r="AD197" s="20"/>
     </row>
-    <row r="198" spans="1:30" ht="16.5" customHeight="1">
+    <row r="198" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A198" s="19"/>
       <c r="B198" s="20"/>
       <c r="C198" s="20"/>
@@ -37987,7 +37901,7 @@
       <c r="AC198" s="20"/>
       <c r="AD198" s="20"/>
     </row>
-    <row r="199" spans="1:30" ht="15" customHeight="1">
+    <row r="199" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A199" s="19"/>
       <c r="B199" s="20" t="s">
         <v>468</v>
@@ -38024,7 +37938,7 @@
       <c r="AC199" s="20"/>
       <c r="AD199" s="20"/>
     </row>
-    <row r="200" spans="1:30" ht="15" customHeight="1">
+    <row r="200" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A200" s="19"/>
       <c r="B200" s="20" t="s">
         <v>469</v>
@@ -38061,7 +37975,7 @@
       <c r="AC200" s="20"/>
       <c r="AD200" s="20"/>
     </row>
-    <row r="201" spans="1:30" ht="15" customHeight="1">
+    <row r="201" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A201" s="19"/>
       <c r="B201" s="20" t="s">
         <v>470</v>
@@ -38098,7 +38012,7 @@
       <c r="AC201" s="20"/>
       <c r="AD201" s="20"/>
     </row>
-    <row r="202" spans="1:30" ht="15" customHeight="1">
+    <row r="202" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A202" s="19"/>
       <c r="B202" s="20" t="s">
         <v>471</v>
@@ -38135,7 +38049,7 @@
       <c r="AC202" s="20"/>
       <c r="AD202" s="20"/>
     </row>
-    <row r="203" spans="1:30" ht="15" customHeight="1">
+    <row r="203" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A203" s="19"/>
       <c r="B203" s="20" t="s">
         <v>472</v>
@@ -38172,7 +38086,7 @@
       <c r="AC203" s="20"/>
       <c r="AD203" s="20"/>
     </row>
-    <row r="204" spans="1:30" ht="15" customHeight="1">
+    <row r="204" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A204" s="19"/>
       <c r="B204" s="20" t="s">
         <v>473</v>
@@ -38209,7 +38123,7 @@
       <c r="AC204" s="20"/>
       <c r="AD204" s="20"/>
     </row>
-    <row r="205" spans="1:30" ht="15" customHeight="1">
+    <row r="205" spans="1:30" ht="15" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A205" s="19"/>
       <c r="B205" s="81" t="s">
         <v>474</v>
@@ -38246,7 +38160,7 @@
       <c r="AC205" s="20"/>
       <c r="AD205" s="20"/>
     </row>
-    <row r="206" spans="1:30" ht="16.5" customHeight="1">
+    <row r="206" spans="1:30" ht="16.5" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A206" s="19"/>
       <c r="B206" s="20"/>
       <c r="C206" s="20"/>
@@ -38376,27 +38290,20 @@
       <c r="AC209" s="20"/>
       <c r="AD209" s="20"/>
     </row>
-    <row r="210" spans="1:30" ht="60" customHeight="1">
+    <row r="210" spans="1:30" ht="49.5" customHeight="1">
       <c r="A210" s="19"/>
-      <c r="B210" s="201" t="s">
+      <c r="B210" s="202" t="s">
         <v>476</v>
       </c>
-      <c r="C210" s="152"/>
-      <c r="D210" s="152"/>
-      <c r="E210" s="152"/>
-      <c r="F210" s="152"/>
-      <c r="G210" s="152"/>
-      <c r="H210" s="152"/>
-      <c r="I210" s="152"/>
-      <c r="J210" s="152"/>
-      <c r="K210" s="152"/>
-      <c r="L210" s="152"/>
-      <c r="M210" s="152"/>
-      <c r="N210" s="152"/>
-      <c r="O210" s="152"/>
-      <c r="P210" s="152"/>
-      <c r="Q210" s="152"/>
-      <c r="R210" s="152"/>
+      <c r="C210" s="153"/>
+      <c r="D210" s="153"/>
+      <c r="E210" s="153"/>
+      <c r="F210" s="153"/>
+      <c r="G210" s="153"/>
+      <c r="H210" s="153"/>
+      <c r="I210" s="153"/>
+      <c r="J210" s="153"/>
+      <c r="K210" s="153"/>
       <c r="S210" s="20"/>
       <c r="T210" s="20"/>
       <c r="U210" s="20"/>
@@ -38442,27 +38349,20 @@
       <c r="AC211" s="20"/>
       <c r="AD211" s="20"/>
     </row>
-    <row r="212" spans="1:30" ht="21.95" customHeight="1">
+    <row r="212" spans="1:30" ht="20.45" customHeight="1">
       <c r="A212" s="19"/>
-      <c r="B212" s="195" t="s">
+      <c r="B212" s="196" t="s">
         <v>477</v>
       </c>
-      <c r="C212" s="164"/>
-      <c r="D212" s="164"/>
-      <c r="E212" s="164"/>
-      <c r="F212" s="164"/>
-      <c r="G212" s="164"/>
-      <c r="H212" s="164"/>
-      <c r="I212" s="164"/>
-      <c r="J212" s="164"/>
-      <c r="K212" s="164"/>
-      <c r="L212" s="164"/>
-      <c r="M212" s="164"/>
-      <c r="N212" s="164"/>
-      <c r="O212" s="164"/>
-      <c r="P212" s="164"/>
-      <c r="Q212" s="164"/>
-      <c r="R212" s="164"/>
+      <c r="C212" s="165"/>
+      <c r="D212" s="165"/>
+      <c r="E212" s="165"/>
+      <c r="F212" s="165"/>
+      <c r="G212" s="165"/>
+      <c r="H212" s="165"/>
+      <c r="I212" s="165"/>
+      <c r="J212" s="165"/>
+      <c r="K212" s="165"/>
       <c r="S212" s="20"/>
       <c r="T212" s="20"/>
       <c r="U212" s="20"/>
@@ -38476,27 +38376,20 @@
       <c r="AC212" s="20"/>
       <c r="AD212" s="20"/>
     </row>
-    <row r="213" spans="1:30" ht="56.1" customHeight="1">
+    <row r="213" spans="1:30" ht="49.5" customHeight="1">
       <c r="A213" s="19"/>
-      <c r="B213" s="201" t="s">
+      <c r="B213" s="202" t="s">
         <v>478</v>
       </c>
-      <c r="C213" s="152"/>
-      <c r="D213" s="152"/>
-      <c r="E213" s="152"/>
-      <c r="F213" s="152"/>
-      <c r="G213" s="152"/>
-      <c r="H213" s="152"/>
-      <c r="I213" s="152"/>
-      <c r="J213" s="152"/>
-      <c r="K213" s="152"/>
-      <c r="L213" s="152"/>
-      <c r="M213" s="152"/>
-      <c r="N213" s="152"/>
-      <c r="O213" s="152"/>
-      <c r="P213" s="152"/>
-      <c r="Q213" s="152"/>
-      <c r="R213" s="152"/>
+      <c r="C213" s="153"/>
+      <c r="D213" s="153"/>
+      <c r="E213" s="153"/>
+      <c r="F213" s="153"/>
+      <c r="G213" s="153"/>
+      <c r="H213" s="153"/>
+      <c r="I213" s="153"/>
+      <c r="J213" s="153"/>
+      <c r="K213" s="153"/>
       <c r="S213" s="20"/>
       <c r="T213" s="20"/>
       <c r="U213" s="20"/>
@@ -38542,27 +38435,20 @@
       <c r="AC214" s="20"/>
       <c r="AD214" s="20"/>
     </row>
-    <row r="215" spans="1:30" ht="21.95" customHeight="1">
+    <row r="215" spans="1:30" ht="20.45" customHeight="1">
       <c r="A215" s="19"/>
-      <c r="B215" s="195" t="s">
+      <c r="B215" s="196" t="s">
         <v>479</v>
       </c>
-      <c r="C215" s="164"/>
-      <c r="D215" s="164"/>
-      <c r="E215" s="164"/>
-      <c r="F215" s="164"/>
-      <c r="G215" s="164"/>
-      <c r="H215" s="164"/>
-      <c r="I215" s="164"/>
-      <c r="J215" s="164"/>
-      <c r="K215" s="164"/>
-      <c r="L215" s="164"/>
-      <c r="M215" s="164"/>
-      <c r="N215" s="164"/>
-      <c r="O215" s="164"/>
-      <c r="P215" s="164"/>
-      <c r="Q215" s="164"/>
-      <c r="R215" s="164"/>
+      <c r="C215" s="165"/>
+      <c r="D215" s="165"/>
+      <c r="E215" s="165"/>
+      <c r="F215" s="165"/>
+      <c r="G215" s="165"/>
+      <c r="H215" s="165"/>
+      <c r="I215" s="165"/>
+      <c r="J215" s="165"/>
+      <c r="K215" s="165"/>
       <c r="S215" s="20"/>
       <c r="T215" s="20"/>
       <c r="U215" s="20"/>
@@ -38576,27 +38462,20 @@
       <c r="AC215" s="20"/>
       <c r="AD215" s="20"/>
     </row>
-    <row r="216" spans="1:30" ht="56.1" customHeight="1">
+    <row r="216" spans="1:30" ht="35.1" customHeight="1">
       <c r="A216" s="19"/>
-      <c r="B216" s="201" t="s">
+      <c r="B216" s="202" t="s">
         <v>480</v>
       </c>
-      <c r="C216" s="152"/>
-      <c r="D216" s="152"/>
-      <c r="E216" s="152"/>
-      <c r="F216" s="152"/>
-      <c r="G216" s="152"/>
-      <c r="H216" s="152"/>
-      <c r="I216" s="152"/>
-      <c r="J216" s="152"/>
-      <c r="K216" s="152"/>
-      <c r="L216" s="152"/>
-      <c r="M216" s="152"/>
-      <c r="N216" s="152"/>
-      <c r="O216" s="152"/>
-      <c r="P216" s="152"/>
-      <c r="Q216" s="152"/>
-      <c r="R216" s="152"/>
+      <c r="C216" s="153"/>
+      <c r="D216" s="153"/>
+      <c r="E216" s="153"/>
+      <c r="F216" s="153"/>
+      <c r="G216" s="153"/>
+      <c r="H216" s="153"/>
+      <c r="I216" s="153"/>
+      <c r="J216" s="153"/>
+      <c r="K216" s="153"/>
       <c r="S216" s="20"/>
       <c r="T216" s="20"/>
       <c r="U216" s="20"/>
@@ -38642,27 +38521,20 @@
       <c r="AC217" s="20"/>
       <c r="AD217" s="20"/>
     </row>
-    <row r="218" spans="1:30" ht="21.95" customHeight="1">
+    <row r="218" spans="1:30" ht="20.45" customHeight="1">
       <c r="A218" s="19"/>
-      <c r="B218" s="195" t="s">
+      <c r="B218" s="196" t="s">
         <v>481</v>
       </c>
-      <c r="C218" s="164"/>
-      <c r="D218" s="164"/>
-      <c r="E218" s="164"/>
-      <c r="F218" s="164"/>
-      <c r="G218" s="164"/>
-      <c r="H218" s="164"/>
-      <c r="I218" s="164"/>
-      <c r="J218" s="164"/>
-      <c r="K218" s="164"/>
-      <c r="L218" s="164"/>
-      <c r="M218" s="164"/>
-      <c r="N218" s="164"/>
-      <c r="O218" s="164"/>
-      <c r="P218" s="164"/>
-      <c r="Q218" s="164"/>
-      <c r="R218" s="164"/>
+      <c r="C218" s="165"/>
+      <c r="D218" s="165"/>
+      <c r="E218" s="165"/>
+      <c r="F218" s="165"/>
+      <c r="G218" s="165"/>
+      <c r="H218" s="165"/>
+      <c r="I218" s="165"/>
+      <c r="J218" s="165"/>
+      <c r="K218" s="165"/>
       <c r="S218" s="20"/>
       <c r="T218" s="20"/>
       <c r="U218" s="20"/>
@@ -38676,27 +38548,20 @@
       <c r="AC218" s="20"/>
       <c r="AD218" s="20"/>
     </row>
-    <row r="219" spans="1:30" ht="56.1" customHeight="1">
+    <row r="219" spans="1:30" ht="35.1" customHeight="1">
       <c r="A219" s="19"/>
-      <c r="B219" s="201" t="s">
+      <c r="B219" s="202" t="s">
         <v>482</v>
       </c>
-      <c r="C219" s="152"/>
-      <c r="D219" s="152"/>
-      <c r="E219" s="152"/>
-      <c r="F219" s="152"/>
-      <c r="G219" s="152"/>
-      <c r="H219" s="152"/>
-      <c r="I219" s="152"/>
-      <c r="J219" s="152"/>
-      <c r="K219" s="152"/>
-      <c r="L219" s="152"/>
-      <c r="M219" s="152"/>
-      <c r="N219" s="152"/>
-      <c r="O219" s="152"/>
-      <c r="P219" s="152"/>
-      <c r="Q219" s="152"/>
-      <c r="R219" s="152"/>
+      <c r="C219" s="153"/>
+      <c r="D219" s="153"/>
+      <c r="E219" s="153"/>
+      <c r="F219" s="153"/>
+      <c r="G219" s="153"/>
+      <c r="H219" s="153"/>
+      <c r="I219" s="153"/>
+      <c r="J219" s="153"/>
+      <c r="K219" s="153"/>
       <c r="S219" s="20"/>
       <c r="T219" s="20"/>
       <c r="U219" s="20"/>
@@ -38742,27 +38607,20 @@
       <c r="AC220" s="20"/>
       <c r="AD220" s="20"/>
     </row>
-    <row r="221" spans="1:30" ht="21.95" customHeight="1">
+    <row r="221" spans="1:30" ht="20.45" customHeight="1">
       <c r="A221" s="19"/>
-      <c r="B221" s="195" t="s">
+      <c r="B221" s="196" t="s">
         <v>483</v>
       </c>
-      <c r="C221" s="164"/>
-      <c r="D221" s="164"/>
-      <c r="E221" s="164"/>
-      <c r="F221" s="164"/>
-      <c r="G221" s="164"/>
-      <c r="H221" s="164"/>
-      <c r="I221" s="164"/>
-      <c r="J221" s="164"/>
-      <c r="K221" s="164"/>
-      <c r="L221" s="164"/>
-      <c r="M221" s="164"/>
-      <c r="N221" s="164"/>
-      <c r="O221" s="164"/>
-      <c r="P221" s="164"/>
-      <c r="Q221" s="164"/>
-      <c r="R221" s="164"/>
+      <c r="C221" s="165"/>
+      <c r="D221" s="165"/>
+      <c r="E221" s="165"/>
+      <c r="F221" s="165"/>
+      <c r="G221" s="165"/>
+      <c r="H221" s="165"/>
+      <c r="I221" s="165"/>
+      <c r="J221" s="165"/>
+      <c r="K221" s="165"/>
       <c r="S221" s="20"/>
       <c r="T221" s="20"/>
       <c r="U221" s="20"/>
@@ -38776,27 +38634,20 @@
       <c r="AC221" s="20"/>
       <c r="AD221" s="20"/>
     </row>
-    <row r="222" spans="1:30" ht="56.1" customHeight="1">
+    <row r="222" spans="1:30" ht="35.1" customHeight="1">
       <c r="A222" s="19"/>
-      <c r="B222" s="201" t="s">
+      <c r="B222" s="202" t="s">
         <v>484</v>
       </c>
-      <c r="C222" s="152"/>
-      <c r="D222" s="152"/>
-      <c r="E222" s="152"/>
-      <c r="F222" s="152"/>
-      <c r="G222" s="152"/>
-      <c r="H222" s="152"/>
-      <c r="I222" s="152"/>
-      <c r="J222" s="152"/>
-      <c r="K222" s="152"/>
-      <c r="L222" s="152"/>
-      <c r="M222" s="152"/>
-      <c r="N222" s="152"/>
-      <c r="O222" s="152"/>
-      <c r="P222" s="152"/>
-      <c r="Q222" s="152"/>
-      <c r="R222" s="152"/>
+      <c r="C222" s="153"/>
+      <c r="D222" s="153"/>
+      <c r="E222" s="153"/>
+      <c r="F222" s="153"/>
+      <c r="G222" s="153"/>
+      <c r="H222" s="153"/>
+      <c r="I222" s="153"/>
+      <c r="J222" s="153"/>
+      <c r="K222" s="153"/>
       <c r="S222" s="20"/>
       <c r="T222" s="20"/>
       <c r="U222" s="20"/>
@@ -38842,27 +38693,20 @@
       <c r="AC223" s="20"/>
       <c r="AD223" s="20"/>
     </row>
-    <row r="224" spans="1:30" ht="21.95" customHeight="1">
+    <row r="224" spans="1:30" ht="20.45" customHeight="1">
       <c r="A224" s="19"/>
-      <c r="B224" s="195" t="s">
+      <c r="B224" s="196" t="s">
         <v>485</v>
       </c>
-      <c r="C224" s="164"/>
-      <c r="D224" s="164"/>
-      <c r="E224" s="164"/>
-      <c r="F224" s="164"/>
-      <c r="G224" s="164"/>
-      <c r="H224" s="164"/>
-      <c r="I224" s="164"/>
-      <c r="J224" s="164"/>
-      <c r="K224" s="164"/>
-      <c r="L224" s="164"/>
-      <c r="M224" s="164"/>
-      <c r="N224" s="164"/>
-      <c r="O224" s="164"/>
-      <c r="P224" s="164"/>
-      <c r="Q224" s="164"/>
-      <c r="R224" s="164"/>
+      <c r="C224" s="165"/>
+      <c r="D224" s="165"/>
+      <c r="E224" s="165"/>
+      <c r="F224" s="165"/>
+      <c r="G224" s="165"/>
+      <c r="H224" s="165"/>
+      <c r="I224" s="165"/>
+      <c r="J224" s="165"/>
+      <c r="K224" s="165"/>
       <c r="S224" s="20"/>
       <c r="T224" s="20"/>
       <c r="U224" s="20"/>
@@ -38876,27 +38720,20 @@
       <c r="AC224" s="20"/>
       <c r="AD224" s="20"/>
     </row>
-    <row r="225" spans="1:30" ht="56.1" customHeight="1">
+    <row r="225" spans="1:30" ht="35.1" customHeight="1">
       <c r="A225" s="19"/>
-      <c r="B225" s="201" t="s">
+      <c r="B225" s="202" t="s">
         <v>486</v>
       </c>
-      <c r="C225" s="152"/>
-      <c r="D225" s="152"/>
-      <c r="E225" s="152"/>
-      <c r="F225" s="152"/>
-      <c r="G225" s="152"/>
-      <c r="H225" s="152"/>
-      <c r="I225" s="152"/>
-      <c r="J225" s="152"/>
-      <c r="K225" s="152"/>
-      <c r="L225" s="152"/>
-      <c r="M225" s="152"/>
-      <c r="N225" s="152"/>
-      <c r="O225" s="152"/>
-      <c r="P225" s="152"/>
-      <c r="Q225" s="152"/>
-      <c r="R225" s="152"/>
+      <c r="C225" s="153"/>
+      <c r="D225" s="153"/>
+      <c r="E225" s="153"/>
+      <c r="F225" s="153"/>
+      <c r="G225" s="153"/>
+      <c r="H225" s="153"/>
+      <c r="I225" s="153"/>
+      <c r="J225" s="153"/>
+      <c r="K225" s="153"/>
       <c r="S225" s="20"/>
       <c r="T225" s="20"/>
       <c r="U225" s="20"/>
@@ -38942,27 +38779,20 @@
       <c r="AC226" s="20"/>
       <c r="AD226" s="20"/>
     </row>
-    <row r="227" spans="1:30" ht="21.95" customHeight="1">
+    <row r="227" spans="1:30" ht="20.45" customHeight="1">
       <c r="A227" s="19"/>
-      <c r="B227" s="195" t="s">
+      <c r="B227" s="196" t="s">
         <v>487</v>
       </c>
-      <c r="C227" s="164"/>
-      <c r="D227" s="164"/>
-      <c r="E227" s="164"/>
-      <c r="F227" s="164"/>
-      <c r="G227" s="164"/>
-      <c r="H227" s="164"/>
-      <c r="I227" s="164"/>
-      <c r="J227" s="164"/>
-      <c r="K227" s="164"/>
-      <c r="L227" s="164"/>
-      <c r="M227" s="164"/>
-      <c r="N227" s="164"/>
-      <c r="O227" s="164"/>
-      <c r="P227" s="164"/>
-      <c r="Q227" s="164"/>
-      <c r="R227" s="164"/>
+      <c r="C227" s="165"/>
+      <c r="D227" s="165"/>
+      <c r="E227" s="165"/>
+      <c r="F227" s="165"/>
+      <c r="G227" s="165"/>
+      <c r="H227" s="165"/>
+      <c r="I227" s="165"/>
+      <c r="J227" s="165"/>
+      <c r="K227" s="165"/>
       <c r="S227" s="20"/>
       <c r="T227" s="20"/>
       <c r="U227" s="20"/>
@@ -38976,27 +38806,20 @@
       <c r="AC227" s="20"/>
       <c r="AD227" s="20"/>
     </row>
-    <row r="228" spans="1:30" ht="56.1" customHeight="1">
+    <row r="228" spans="1:30" ht="20.45" customHeight="1">
       <c r="A228" s="19"/>
-      <c r="B228" s="201" t="s">
+      <c r="B228" s="202" t="s">
         <v>488</v>
       </c>
-      <c r="C228" s="152"/>
-      <c r="D228" s="152"/>
-      <c r="E228" s="152"/>
-      <c r="F228" s="152"/>
-      <c r="G228" s="152"/>
-      <c r="H228" s="152"/>
-      <c r="I228" s="152"/>
-      <c r="J228" s="152"/>
-      <c r="K228" s="152"/>
-      <c r="L228" s="152"/>
-      <c r="M228" s="152"/>
-      <c r="N228" s="152"/>
-      <c r="O228" s="152"/>
-      <c r="P228" s="152"/>
-      <c r="Q228" s="152"/>
-      <c r="R228" s="152"/>
+      <c r="C228" s="153"/>
+      <c r="D228" s="153"/>
+      <c r="E228" s="153"/>
+      <c r="F228" s="153"/>
+      <c r="G228" s="153"/>
+      <c r="H228" s="153"/>
+      <c r="I228" s="153"/>
+      <c r="J228" s="153"/>
+      <c r="K228" s="153"/>
       <c r="S228" s="20"/>
       <c r="T228" s="20"/>
       <c r="U228" s="20"/>
@@ -39187,25 +39010,25 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B228:K228"/>
+    <mergeCell ref="B210:K210"/>
     <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B222:R222"/>
+    <mergeCell ref="B225:K225"/>
     <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B213:R213"/>
-    <mergeCell ref="B216:R216"/>
-    <mergeCell ref="B212:R212"/>
-    <mergeCell ref="B228:R228"/>
-    <mergeCell ref="B210:R210"/>
+    <mergeCell ref="B227:K227"/>
     <mergeCell ref="B47:K47"/>
-    <mergeCell ref="B225:R225"/>
+    <mergeCell ref="B218:K218"/>
+    <mergeCell ref="B224:K224"/>
     <mergeCell ref="B46:K46"/>
-    <mergeCell ref="B221:R221"/>
-    <mergeCell ref="B227:R227"/>
-    <mergeCell ref="B218:R218"/>
-    <mergeCell ref="B224:R224"/>
+    <mergeCell ref="B215:K215"/>
+    <mergeCell ref="B219:K219"/>
     <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B215:R215"/>
+    <mergeCell ref="B222:K222"/>
+    <mergeCell ref="B213:K213"/>
+    <mergeCell ref="B216:K216"/>
+    <mergeCell ref="B212:K212"/>
     <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B219:R219"/>
+    <mergeCell ref="B221:K221"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" location="'Försättsblad'!A1" display="Försättsblad" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
@@ -39219,11 +39042,7 @@
     <hyperlink ref="A11" location="'Dokumentation'!A1" display="Dokumentation" xr:uid="{00000000-0004-0000-0800-000008000000}"/>
   </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" fitToWidth="2" fitToHeight="0" orientation="landscape"/>
-  <rowBreaks count="2" manualBreakCount="2">
-    <brk id="45" max="16383" man="1"/>
-    <brk id="207" max="16383" man="1"/>
-  </rowBreaks>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/build/oneshot/Investeringskalkyl_v2.xlsx
+++ b/build/oneshot/Investeringskalkyl_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaki\Documents\GitHub\investeringskalkyl\build\oneshot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5E5AF6-260E-4CEF-9A2E-AEFDC472A58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A1DA65-7EBD-4967-85BB-6DE2CABA4478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9615" yWindow="1875" windowWidth="28785" windowHeight="16065" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Översikt" sheetId="1" r:id="rId1"/>
@@ -3213,7 +3213,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E1BA-4AC6-8C67-057259410037}"/>
+              <c16:uniqueId val="{00000000-BA3E-44C0-A48A-A8A7229A56CD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3464,7 +3464,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-96BF-4404-8F02-4336DFA6D3D3}"/>
+              <c16:uniqueId val="{00000000-EE40-445F-8553-8368271BCCDF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3626,7 +3626,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-96BF-4404-8F02-4336DFA6D3D3}"/>
+              <c16:uniqueId val="{00000001-EE40-445F-8553-8368271BCCDF}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3787,7 +3787,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-177F-4CB4-9A25-CB72A8E74FC3}"/>
+              <c16:uniqueId val="{00000000-92EF-48FF-A3CE-371148E22CAD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3863,6 +3863,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
@@ -3872,7 +3873,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3896,6 +3897,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Image 2" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
@@ -3905,7 +3907,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3929,6 +3931,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Image 3" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
@@ -3938,7 +3941,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3962,6 +3965,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Image 4" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
@@ -3971,7 +3975,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3995,6 +3999,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="6" name="Image 5" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
@@ -4004,7 +4009,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4028,6 +4033,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="7" name="Image 6" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
@@ -4037,7 +4043,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4061,6 +4067,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="8" name="Image 7" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
@@ -4070,7 +4077,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4094,6 +4101,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="9" name="Image 8" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
@@ -4103,7 +4111,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4127,6 +4135,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="10" name="Image 9" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
@@ -4136,7 +4145,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4160,6 +4169,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="11" name="Image 10" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B000000}"/>
@@ -4169,7 +4179,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4198,6 +4208,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000002000000}"/>
@@ -4207,7 +4218,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4231,6 +4242,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Image 2" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000003000000}"/>
@@ -4240,7 +4252,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4264,6 +4276,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Image 3" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000004000000}"/>
@@ -4273,7 +4286,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4297,6 +4310,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Image 4" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000005000000}"/>
@@ -4306,7 +4320,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4330,6 +4344,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="6" name="Image 5" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000006000000}"/>
@@ -4339,7 +4354,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4363,6 +4378,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="7" name="Image 6" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000007000000}"/>
@@ -4372,7 +4388,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4396,6 +4412,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="8" name="Image 7" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000008000000}"/>
@@ -4405,7 +4422,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4429,6 +4446,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="9" name="Image 8" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000009000000}"/>
@@ -4438,7 +4456,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4462,6 +4480,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="10" name="Image 9" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-00000A000000}"/>
@@ -4471,7 +4490,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4495,6 +4514,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="11" name="Image 10" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-00000B000000}"/>
@@ -4504,7 +4524,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4533,6 +4553,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
@@ -4542,7 +4563,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4566,6 +4587,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Image 2" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
@@ -4575,7 +4597,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4599,6 +4621,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Image 3" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
@@ -4608,7 +4631,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4632,6 +4655,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Image 4" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000005000000}"/>
@@ -4641,7 +4665,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4665,6 +4689,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="6" name="Image 5" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000006000000}"/>
@@ -4674,7 +4699,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4698,6 +4723,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="7" name="Image 6" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000007000000}"/>
@@ -4707,7 +4733,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4731,6 +4757,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="8" name="Image 7" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000008000000}"/>
@@ -4740,7 +4767,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4764,6 +4791,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="9" name="Image 8" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000009000000}"/>
@@ -4773,7 +4801,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4797,6 +4825,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="10" name="Image 9" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
@@ -4806,7 +4835,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4830,6 +4859,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="11" name="Image 10" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000B000000}"/>
@@ -4839,7 +4869,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4868,6 +4898,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
@@ -4877,7 +4908,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4901,6 +4932,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Image 2" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
@@ -4910,7 +4942,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4934,6 +4966,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Image 3" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000004000000}"/>
@@ -4943,7 +4976,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4967,6 +5000,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Image 4" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000005000000}"/>
@@ -4976,7 +5010,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5000,6 +5034,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="6" name="Image 5" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000006000000}"/>
@@ -5009,7 +5044,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5033,6 +5068,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="7" name="Image 6" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000007000000}"/>
@@ -5042,7 +5078,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5066,6 +5102,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="8" name="Image 7" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000008000000}"/>
@@ -5075,7 +5112,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5099,6 +5136,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="9" name="Image 8" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000009000000}"/>
@@ -5108,7 +5146,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5132,6 +5170,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="10" name="Image 9" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000A000000}"/>
@@ -5141,7 +5180,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5165,6 +5204,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="11" name="Image 10" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-00000B000000}"/>
@@ -5174,7 +5214,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5203,6 +5243,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
@@ -5212,7 +5253,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5236,6 +5277,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Image 2" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
@@ -5245,7 +5287,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5269,6 +5311,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Image 3" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004000000}"/>
@@ -5278,7 +5321,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5302,6 +5345,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Image 4" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000005000000}"/>
@@ -5311,7 +5355,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5335,6 +5379,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="6" name="Image 5" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000006000000}"/>
@@ -5344,7 +5389,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5368,6 +5413,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="7" name="Image 6" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000007000000}"/>
@@ -5377,7 +5423,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5401,6 +5447,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="8" name="Image 7" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000008000000}"/>
@@ -5410,7 +5457,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5434,6 +5481,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="9" name="Image 8" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000009000000}"/>
@@ -5443,7 +5491,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5467,6 +5515,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="10" name="Image 9" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000A000000}"/>
@@ -5476,7 +5525,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5500,6 +5549,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="11" name="Image 10" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-00000B000000}"/>
@@ -5509,7 +5559,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5538,6 +5588,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
@@ -5547,7 +5598,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5571,6 +5622,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Image 2" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
@@ -5580,7 +5632,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5604,6 +5656,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Image 3" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000004000000}"/>
@@ -5613,7 +5666,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5637,6 +5690,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Image 4" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000005000000}"/>
@@ -5646,7 +5700,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5670,6 +5724,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="6" name="Image 5" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000006000000}"/>
@@ -5679,7 +5734,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5703,6 +5758,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="7" name="Image 6" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000007000000}"/>
@@ -5712,7 +5768,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5736,6 +5792,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="8" name="Image 7" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000008000000}"/>
@@ -5745,7 +5802,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5769,6 +5826,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="9" name="Image 8" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000009000000}"/>
@@ -5778,7 +5836,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5802,6 +5860,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="10" name="Image 9" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000A000000}"/>
@@ -5811,7 +5870,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5835,6 +5894,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="11" name="Image 10" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000B000000}"/>
@@ -5844,7 +5904,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5873,6 +5933,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
@@ -5882,7 +5943,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5906,6 +5967,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Image 2" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
@@ -5915,7 +5977,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5939,6 +6001,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Image 3" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000004000000}"/>
@@ -5948,7 +6011,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5972,6 +6035,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Image 4" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000005000000}"/>
@@ -5981,7 +6045,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6005,6 +6069,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="6" name="Image 5" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000006000000}"/>
@@ -6014,7 +6079,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6038,6 +6103,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="7" name="Image 6" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000007000000}"/>
@@ -6047,7 +6113,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6071,6 +6137,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="8" name="Image 7" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000008000000}"/>
@@ -6080,7 +6147,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6104,6 +6171,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="9" name="Image 8" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000009000000}"/>
@@ -6113,7 +6181,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6137,6 +6205,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="10" name="Image 9" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-00000A000000}"/>
@@ -6146,7 +6215,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6170,6 +6239,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="11" name="Image 10" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-00000B000000}"/>
@@ -6179,7 +6249,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6301,9 +6371,389 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Image 4" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1600200" cy="361950"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Image 5" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1600200" cy="361950"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Image 6" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1600200" cy="361950"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Image 7" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1600200" cy="361950"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Image 8" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1600200" cy="361950"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Image 9" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId14"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1600200" cy="361950"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Image 10" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId16"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId17" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1600200" cy="361950"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Image 11" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1600200" cy="361950"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Image 12" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId20"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId21" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1600200" cy="361950"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Image 13" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId22"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId23" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1600200" cy="361950"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 1" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1600200" cy="361950"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Image 2" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6327,49 +6777,17 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1600200" cy="361950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Image 5" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1600200" cy="361950"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Image 6" descr="Picture">
+        <xdr:cNvPr id="4" name="Image 3" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000007000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6399,43 +6817,11 @@
     <xdr:ext cx="1600200" cy="361950"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Image 7" descr="Picture">
+        <xdr:cNvPr id="5" name="Image 4" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1600200" cy="361950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Image 8" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000009000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6459,49 +6845,17 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1600200" cy="361950"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Image 9" descr="Picture">
+        <xdr:cNvPr id="6" name="Image 5" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1600200" cy="361950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Image 10" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000B000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000006000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6525,49 +6879,17 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1600200" cy="361950"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Image 11" descr="Picture">
+        <xdr:cNvPr id="7" name="Image 6" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1600200" cy="361950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Image 12" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000D000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6591,242 +6913,6 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1600200" cy="361950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Image 13" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1600200" cy="361950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1600200" cy="361950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Image 2" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1600200" cy="361950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Image 3" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1600200" cy="361950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Image 4" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1600200" cy="361950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Image 5" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1600200" cy="361950"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Image 6" descr="Picture">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -6834,6 +6920,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="8" name="Image 7" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000008000000}"/>
@@ -6843,7 +6930,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6867,6 +6954,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="9" name="Image 8" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000009000000}"/>
@@ -6876,7 +6964,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6900,6 +6988,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="10" name="Image 9" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00000A000000}"/>
@@ -6909,7 +6998,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6933,6 +7022,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="11" name="Image 10" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00000B000000}"/>
@@ -6942,7 +7032,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6971,6 +7061,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000002000000}"/>
@@ -6980,7 +7071,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7004,6 +7095,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Image 2" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000003000000}"/>
@@ -7013,7 +7105,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7037,6 +7129,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Image 3" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000004000000}"/>
@@ -7046,7 +7139,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7070,6 +7163,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Image 4" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000005000000}"/>
@@ -7079,7 +7173,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7103,6 +7197,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="6" name="Image 5" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000006000000}"/>
@@ -7112,7 +7207,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7136,6 +7231,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="7" name="Image 6" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000007000000}"/>
@@ -7145,7 +7241,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7169,6 +7265,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="8" name="Image 7" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000008000000}"/>
@@ -7178,7 +7275,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7202,6 +7299,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="9" name="Image 8" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-000009000000}"/>
@@ -7211,7 +7309,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7235,6 +7333,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="10" name="Image 9" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-00000A000000}"/>
@@ -7244,7 +7343,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7268,6 +7367,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="11" name="Image 10" descr="Picture">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0800-00000B000000}"/>
@@ -7277,7 +7377,7 @@
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId20" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
